--- a/tame_output/ON/bt/strategyON_20240723.xlsx
+++ b/tame_output/ON/bt/strategyON_20240723.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>56.7%</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.7%</t>
+          <t>-48.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>455.8%</t>
+          <t>456.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-47.4%</t>
+          <t>-47.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-150.4%</t>
+          <t>-150.3%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>70.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.8%</t>
+          <t>-24.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-123.1%</t>
+          <t>-121.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-151.4%</t>
+          <t>-152.4%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>84.4%</t>
+          <t>84.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>76.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-17.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-20.5%</t>
+          <t>-21.1%</t>
         </is>
       </c>
     </row>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392308</v>
+        <v>3.419979433923082</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297743</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737164</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539458</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587859441027</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158919</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940716</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615281</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848438238121</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646214</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611565</v>
+        <v>3.768951674611567</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955325</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232409</v>
+        <v>3.747702660232411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388728</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85616175162647</v>
+        <v>3.856161751626474</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291811</v>
+        <v>3.787330429291814</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.80163712278579</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960984</v>
+        <v>3.753882571960988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607642</v>
+        <v>3.692931855607646</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704225839879</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710815</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409207</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.729969716098112</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493423</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792045</v>
+        <v>3.828052928792048</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919905</v>
+        <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.74832840831809</v>
+        <v>3.748328408318094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279183</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011495</v>
+        <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392983</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632778</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074779</v>
+        <v>3.798814771074783</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.79769488424229</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367683</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879961</v>
+        <v>3.822326997879965</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502333</v>
+        <v>3.848616626502337</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675933</v>
+        <v>3.818668951675938</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539945</v>
+        <v>3.84327452753995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496258</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576995</v>
+        <v>3.791273551576999</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.7358392229421</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674511</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430689</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003597</v>
+        <v>3.743220196003601</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508365</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417699</v>
+        <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205894</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225439</v>
+        <v>3.765024323225443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.699073469306011</v>
+        <v>-3.688206545411863</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.446719533012502</v>
+        <v>1.451066302570161</v>
       </c>
       <c r="F1940" t="n">
         <v>0.529497988488952</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111296</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.665409923833729</v>
+        <v>-3.654542999939581</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.388723264602864</v>
+        <v>1.393070034160523</v>
       </c>
       <c r="F1941" t="n">
         <v>0.5631615339612339</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.605557304630006</v>
+        <v>-3.594690380735858</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.422836698716486</v>
+        <v>1.427183468274145</v>
       </c>
       <c r="F1942" t="n">
         <v>0.5631615339612339</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.786949957742302</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.519313841603629</v>
+        <v>-3.50844691770948</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.452280354500897</v>
+        <v>1.456627124058556</v>
       </c>
       <c r="F1943" t="n">
         <v>0.5631615339612339</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316049</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.564620661002609</v>
+        <v>-3.55375373710846</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.425933402185831</v>
+        <v>1.43028017174349</v>
       </c>
       <c r="F1944" t="n">
         <v>0.5223513709520031</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803194</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.59365376570491</v>
+        <v>-3.582786841810762</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.414872033338011</v>
+        <v>1.419218802895671</v>
       </c>
       <c r="F1945" t="n">
         <v>0.5223513709520031</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.733390600809502</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.500843284254051</v>
+        <v>-3.489976360359902</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.381268917809721</v>
+        <v>1.38561568736738</v>
       </c>
       <c r="F1946" t="n">
         <v>0.6151618524028625</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560428</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.545232753583479</v>
+        <v>-3.53436582968933</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.365386606002551</v>
+        <v>1.36973337556021</v>
       </c>
       <c r="F1947" t="n">
         <v>0.5707723830734348</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.432561535347229</v>
+        <v>-3.42169461145308</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.405530801808774</v>
+        <v>1.409877571366433</v>
       </c>
       <c r="F1948" t="n">
         <v>0.683443601309685</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.320184534164556</v>
+        <v>-3.309317610270407</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.45597289811251</v>
+        <v>1.46031966767017</v>
       </c>
       <c r="F1949" t="n">
         <v>0.683443601309685</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.347964932065909</v>
+        <v>-3.33709800817176</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.456357940720508</v>
+        <v>1.460704710278167</v>
       </c>
       <c r="F1950" t="n">
         <v>0.6556632034083318</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705323</v>
+        <v>3.643069621705327</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.466345604796047</v>
+        <v>-3.455478680901899</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.247361391629106</v>
+        <v>1.251708161186765</v>
       </c>
       <c r="F1951" t="n">
         <v>0.5884453512573556</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729267</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.574959683239379</v>
+        <v>-3.56409275934523</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.324065420970979</v>
+        <v>1.328412190528638</v>
       </c>
       <c r="F1952" t="n">
         <v>0.5884453512573556</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.73301244119077</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.539550644991236</v>
+        <v>-3.528683721097087</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.352742062372559</v>
+        <v>1.357088831930219</v>
       </c>
       <c r="F1953" t="n">
         <v>0.5884453512573556</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913427</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.501166982433085</v>
+        <v>-3.490300058538936</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.365514968738188</v>
+        <v>1.369861738295848</v>
       </c>
       <c r="F1954" t="n">
         <v>0.6268290138155068</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532488</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.324050652397919</v>
+        <v>-3.31318372850377</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.433090529597556</v>
+        <v>1.437437299155216</v>
       </c>
       <c r="F1955" t="n">
         <v>0.6268290138155068</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.369142897231464</v>
+        <v>-3.358275973337316</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.415737023426051</v>
+        <v>1.420083792983711</v>
       </c>
       <c r="F1956" t="n">
         <v>0.564932970646117</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.189767475992697</v>
+        <v>-3.178900552098548</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.481274167227973</v>
+        <v>1.485620936785632</v>
       </c>
       <c r="F1957" t="n">
         <v>0.7217097288168357</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982231</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.234781689513303</v>
+        <v>-3.223914765619154</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.44407593715132</v>
+        <v>1.448422706708979</v>
       </c>
       <c r="F1958" t="n">
         <v>0.6913608335022311</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.73702660850954</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.501786199785738</v>
+        <v>-3.490919275891589</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.342965695381292</v>
+        <v>1.347312464938951</v>
       </c>
       <c r="F1959" t="n">
         <v>0.4969977954592826</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760811</v>
+        <v>3.702309454760815</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.602983981222911</v>
+        <v>-3.592117057328762</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.301690504702924</v>
+        <v>1.306037274260583</v>
       </c>
       <c r="F1960" t="n">
         <v>0.4285889819139634</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.70557166181546</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.596473014608598</v>
+        <v>-3.58560609071445</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.301894852902966</v>
+        <v>1.306241622460625</v>
       </c>
       <c r="F1961" t="n">
         <v>0.4285889819139634</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378105</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.577434886901301</v>
+        <v>-3.566567963007152</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.306034823194129</v>
+        <v>1.310381592751789</v>
       </c>
       <c r="F1962" t="n">
         <v>0.3704053705827688</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131249</v>
+        <v>3.731064473131254</v>
       </c>
       <c r="C1963" t="n">
         <v>2.914947071207078</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.608561518051919</v>
+        <v>-3.59769459415777</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.471166039672563</v>
+        <v>1.475512809230222</v>
       </c>
       <c r="F1963" t="n">
         <v>0.3704053705827688</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067869</v>
       </c>
       <c r="C1964" t="n">
         <v>2.915780400193211</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.622428279385836</v>
+        <v>-3.611561355491688</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.466452664125129</v>
+        <v>1.470799433682789</v>
       </c>
       <c r="F1964" t="n">
         <v>0.3325474538489459</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789126</v>
       </c>
       <c r="C1965" t="n">
         <v>2.921788930590137</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.577624107845907</v>
+        <v>-3.566757183951758</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.490382863138027</v>
+        <v>1.494729632695687</v>
       </c>
       <c r="F1965" t="n">
         <v>0.3325474538489459</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519913</v>
       </c>
       <c r="C1966" t="n">
         <v>2.819739151867337</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.429881137610904</v>
+        <v>-3.419014213716756</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.447430272509228</v>
+        <v>1.451777042066887</v>
       </c>
       <c r="F1966" t="n">
         <v>0.5003548110838291</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181175</v>
       </c>
       <c r="C1967" t="n">
         <v>2.822532773398818</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.531895820142125</v>
+        <v>-3.521028896247977</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.40941802102822</v>
+        <v>1.41376479058588</v>
       </c>
       <c r="F1967" t="n">
         <v>0.5003548110838291</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394729</v>
+        <v>3.805608985394734</v>
       </c>
       <c r="C1968" t="n">
         <v>2.823195121790476</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.525743114089341</v>
+        <v>-3.514876190195192</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.412541451840992</v>
+        <v>1.416888221398652</v>
       </c>
       <c r="F1968" t="n">
         <v>0.5065075171366133</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890616</v>
       </c>
       <c r="C1969" t="n">
         <v>2.822275598530586</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.542552412239842</v>
+        <v>-3.531685488345694</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.404898209320902</v>
+        <v>1.409244978878561</v>
       </c>
       <c r="F1969" t="n">
         <v>0.4896982189861117</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798431</v>
       </c>
       <c r="C1970" t="n">
         <v>2.888611152327407</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.480254413463721</v>
+        <v>-3.469387489569572</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.496152962628172</v>
+        <v>1.500499732185831</v>
       </c>
       <c r="F1970" t="n">
         <v>0.4896982189861117</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992195</v>
       </c>
       <c r="C1971" t="n">
         <v>2.690903154041534</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.278464215798563</v>
+        <v>-3.267597291904414</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.379161043408362</v>
+        <v>1.383507812966021</v>
       </c>
       <c r="F1971" t="n">
         <v>0.687716411155266</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852429</v>
       </c>
       <c r="C1972" t="n">
         <v>2.761193386363709</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.329350928484757</v>
+        <v>-3.318484004590609</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.429096590656059</v>
+        <v>1.433443360213719</v>
       </c>
       <c r="F1972" t="n">
         <v>0.6368296984690716</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.81906330031955</v>
       </c>
       <c r="C1973" t="n">
         <v>2.775821122479753</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.427091473109732</v>
+        <v>-3.416224549215583</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.404628108922113</v>
+        <v>1.408974878479773</v>
       </c>
       <c r="F1973" t="n">
         <v>0.6209404203360913</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489389</v>
       </c>
       <c r="C1974" t="n">
         <v>2.774357103304425</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.603429233232661</v>
+        <v>-3.592562309338512</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.332628985697613</v>
+        <v>1.336975755255273</v>
       </c>
       <c r="F1974" t="n">
         <v>0.4446026602131619</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397799</v>
       </c>
       <c r="C1975" t="n">
         <v>2.772848721344353</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.527007186800734</v>
+        <v>-3.516140262906585</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.361689422310312</v>
+        <v>1.366036191867972</v>
       </c>
       <c r="F1975" t="n">
         <v>0.4446026602131619</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316254</v>
       </c>
       <c r="C1976" t="n">
         <v>2.77271158877979</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.482634055162166</v>
+        <v>-3.471767131268017</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.379301542401176</v>
+        <v>1.383648311958836</v>
       </c>
       <c r="F1976" t="n">
         <v>0.4889757918517306</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105971</v>
       </c>
       <c r="C1977" t="n">
         <v>2.76710538291838</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.359799834274998</v>
+        <v>-3.348932910380849</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.422829024894634</v>
+        <v>1.427175794452293</v>
       </c>
       <c r="F1977" t="n">
         <v>0.4889757918517306</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190329</v>
       </c>
       <c r="C1978" t="n">
         <v>2.773487139946185</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.312144103713942</v>
+        <v>-3.301277179819794</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.448273074146861</v>
+        <v>1.45261984370452</v>
       </c>
       <c r="F1978" t="n">
         <v>0.5366315224127862</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569622</v>
       </c>
       <c r="C1979" t="n">
         <v>2.778379513320909</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.211625945215188</v>
+        <v>-3.200759021321039</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.493372710921087</v>
+        <v>1.497719480478747</v>
       </c>
       <c r="F1979" t="n">
         <v>0.6371496809115408</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557292</v>
+        <v>3.828808877557297</v>
       </c>
       <c r="C1980" t="n">
         <v>2.765134185796782</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.272292535617577</v>
+        <v>-3.261425611723428</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.455860747236004</v>
+        <v>1.460207516793663</v>
       </c>
       <c r="F1980" t="n">
         <v>0.5554513641930071</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932773</v>
       </c>
       <c r="C1981" t="n">
         <v>2.76923188840741</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.227454134009179</v>
+        <v>-3.21658721011503</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.477893810489991</v>
+        <v>1.482240580047651</v>
       </c>
       <c r="F1981" t="n">
         <v>0.5599947971378766</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917055</v>
       </c>
       <c r="C1982" t="n">
         <v>2.773392828038488</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.246952590251187</v>
+        <v>-3.236085666357038</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.474255367624266</v>
+        <v>1.478602137181926</v>
       </c>
       <c r="F1982" t="n">
         <v>0.5119101558579723</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405963</v>
       </c>
       <c r="C1983" t="n">
         <v>2.779272430566325</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.202749753165286</v>
+        <v>-3.191882829271138</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.497816104986464</v>
+        <v>1.502162874544123</v>
       </c>
       <c r="F1983" t="n">
         <v>0.5561129929438727</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265648</v>
       </c>
       <c r="C1984" t="n">
         <v>2.777682431035573</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.23972878082873</v>
+        <v>-3.228861856934581</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.481434494390334</v>
+        <v>1.485781263947993</v>
       </c>
       <c r="F1984" t="n">
         <v>0.5930868947352033</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284882</v>
       </c>
       <c r="C1985" t="n">
         <v>2.828930196218613</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.081437363289457</v>
+        <v>-3.070570439395309</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.595998826589082</v>
+        <v>1.600345596146742</v>
       </c>
       <c r="F1985" t="n">
         <v>0.5930868947352033</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321025</v>
       </c>
       <c r="C1986" t="n">
         <v>2.827370900812866</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.873795359654981</v>
+        <v>-2.862928435760832</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.677496332637126</v>
+        <v>1.681843102194785</v>
       </c>
       <c r="F1986" t="n">
         <v>0.8007288983696794</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475142</v>
       </c>
       <c r="C1987" t="n">
         <v>2.822319129051136</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.822763266932453</v>
+        <v>-2.811896343038304</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.692857397964407</v>
+        <v>1.697204167522067</v>
       </c>
       <c r="F1987" t="n">
         <v>0.8517609910922074</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404856</v>
       </c>
       <c r="C1988" t="n">
         <v>2.839506533143841</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.757539085805248</v>
+        <v>-2.746672161911099</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.736134474507994</v>
+        <v>1.740481244065654</v>
       </c>
       <c r="F1988" t="n">
         <v>0.916985172219413</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882555</v>
+        <v>3.84006118688256</v>
       </c>
       <c r="C1989" t="n">
         <v>2.835467505443121</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.720112065734114</v>
+        <v>-2.709245141839965</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.747066254835728</v>
+        <v>1.751413024393388</v>
       </c>
       <c r="F1989" t="n">
         <v>0.9222367102485947</v>
@@ -47315,16 +47315,16 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992658</v>
+        <v>3.845169808992663</v>
       </c>
       <c r="C1990" t="n">
         <v>2.836724297774361</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.740223721768822</v>
+        <v>-2.729356797874674</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.740278384753085</v>
+        <v>1.744625154310745</v>
       </c>
       <c r="F1990" t="n">
         <v>0.9332640552460139</v>
@@ -47338,16 +47338,16 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636285</v>
+        <v>3.82866144563629</v>
       </c>
       <c r="C1991" t="n">
         <v>2.997282068795572</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.686478907341618</v>
+        <v>-2.675611983447469</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.922334081545178</v>
+        <v>1.926680851102837</v>
       </c>
       <c r="F1991" t="n">
         <v>0.9433273646864758</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957623</v>
+        <v>3.813222820957629</v>
       </c>
       <c r="C1992" t="n">
         <v>3.117394978013389</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.611696646316605</v>
+        <v>-2.600829722422456</v>
       </c>
       <c r="E1992" t="n">
-        <v>2.072359895173</v>
+        <v>2.07670666473066</v>
       </c>
       <c r="F1992" t="n">
         <v>1.018109625711488</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998754</v>
+        <v>3.814230727998758</v>
       </c>
       <c r="C1993" t="n">
         <v>3.109102954027248</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.585612562052797</v>
+        <v>-2.574745638158648</v>
       </c>
       <c r="E1993" t="n">
-        <v>2.074501504892382</v>
+        <v>2.078848274450042</v>
       </c>
       <c r="F1993" t="n">
         <v>1.018109625711488</v>
@@ -47407,16 +47407,16 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896932</v>
       </c>
       <c r="C1994" t="n">
         <v>3.107296149611028</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.50748138120385</v>
+        <v>-2.496614457309701</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.103947172815741</v>
+        <v>2.1082939423734</v>
       </c>
       <c r="F1994" t="n">
         <v>1.092286436595173</v>
@@ -47430,16 +47430,16 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.79626414395986</v>
       </c>
       <c r="C1995" t="n">
         <v>3.124850555337819</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.498588919810567</v>
+        <v>-2.487721995916418</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.125058563099845</v>
+        <v>2.129405332657504</v>
       </c>
       <c r="F1995" t="n">
         <v>1.092286436595173</v>
@@ -47453,16 +47453,16 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945368</v>
       </c>
       <c r="C1996" t="n">
         <v>3.116705602742403</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.667065036780445</v>
+        <v>-2.656198112886296</v>
       </c>
       <c r="E1996" t="n">
-        <v>2.049523163716478</v>
+        <v>2.053869933274138</v>
       </c>
       <c r="F1996" t="n">
         <v>1.064338600878592</v>
@@ -47476,16 +47476,16 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.79557406678271</v>
       </c>
       <c r="C1997" t="n">
         <v>3.097975299930265</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.969265507918862</v>
+        <v>-1.958398584024713</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.309912672448973</v>
+        <v>2.314259442006632</v>
       </c>
       <c r="F1997" t="n">
         <v>0.9939905415081816</v>
@@ -47499,16 +47499,16 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632634</v>
+        <v>3.784671345632638</v>
       </c>
       <c r="C1998" t="n">
         <v>3.08863932242717</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.946544404235709</v>
+        <v>-1.93567748034156</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.309665136419139</v>
+        <v>2.314011905976798</v>
       </c>
       <c r="F1998" t="n">
         <v>0.9939905415081816</v>
@@ -47522,16 +47522,16 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777671</v>
+        <v>3.783205696777676</v>
       </c>
       <c r="C1999" t="n">
         <v>3.247545448278339</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.075746217529752</v>
+        <v>-2.064879293635603</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.416890536952691</v>
+        <v>2.42123730651035</v>
       </c>
       <c r="F1999" t="n">
         <v>0.8647887282141393</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.77993372564441</v>
+        <v>3.779933725644415</v>
       </c>
       <c r="C2000" t="n">
         <v>3.284623270771985</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.230527224308007</v>
+        <v>-2.219660300413858</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.392055956735035</v>
+        <v>2.396402726292695</v>
       </c>
       <c r="F2000" t="n">
         <v>0.8314210541596632</v>
@@ -47568,16 +47568,16 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799962</v>
+        <v>3.769443619799967</v>
       </c>
       <c r="C2001" t="n">
         <v>3.28129862676153</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.223472534092834</v>
+        <v>-2.212605610198685</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.39155318881065</v>
+        <v>2.395899958368309</v>
       </c>
       <c r="F2001" t="n">
         <v>0.838475744374837</v>
@@ -47591,16 +47591,16 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331115</v>
+        <v>3.766673496331119</v>
       </c>
       <c r="C2002" t="n">
         <v>3.291304780406272</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.196521309766346</v>
+        <v>-2.185654385872197</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.412339832185986</v>
+        <v>2.416686601743646</v>
       </c>
       <c r="F2002" t="n">
         <v>0.8533560904025561</v>
@@ -47614,16 +47614,16 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.76805206778411</v>
       </c>
       <c r="C2003" t="n">
         <v>3.475407912551232</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.332474317822662</v>
+        <v>-2.321607393928513</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.54206176110842</v>
+        <v>2.546408530666079</v>
       </c>
       <c r="F2003" t="n">
         <v>0.8533560904025561</v>
@@ -47637,16 +47637,16 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714429</v>
       </c>
       <c r="C2004" t="n">
         <v>3.467524607454225</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.354882435627534</v>
+        <v>-2.344015511733385</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.525215208889464</v>
+        <v>2.529561978447123</v>
       </c>
       <c r="F2004" t="n">
         <v>0.8533560904025561</v>
@@ -47660,16 +47660,16 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155031</v>
+        <v>3.719118627155035</v>
       </c>
       <c r="C2005" t="n">
         <v>3.469578607003862</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.502888203106933</v>
+        <v>-2.492021279212785</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.468066901447342</v>
+        <v>2.472413671005001</v>
       </c>
       <c r="F2005" t="n">
         <v>0.7666290815390147</v>
@@ -47683,16 +47683,16 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161976</v>
+        <v>3.729452285161981</v>
       </c>
       <c r="C2006" t="n">
         <v>3.525832324725709</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.512329128995463</v>
+        <v>-2.501462205101315</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.520544248813777</v>
+        <v>2.524891018371436</v>
       </c>
       <c r="F2006" t="n">
         <v>0.8890561990824061</v>
@@ -47706,16 +47706,16 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321633</v>
+        <v>3.714941193321638</v>
       </c>
       <c r="C2007" t="n">
         <v>3.52872341927101</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.564602736331105</v>
+        <v>-2.553735812436956</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.502525900424821</v>
+        <v>2.506872669982481</v>
       </c>
       <c r="F2007" t="n">
         <v>0.8367825917467648</v>
@@ -47729,16 +47729,16 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347707</v>
       </c>
       <c r="C2008" t="n">
         <v>3.526835232164785</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.640932713932011</v>
+        <v>-2.630065790037862</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.470105722278234</v>
+        <v>2.474452491835893</v>
       </c>
       <c r="F2008" t="n">
         <v>0.8367825917467648</v>
@@ -47752,16 +47752,16 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887751</v>
       </c>
       <c r="C2009" t="n">
         <v>3.521655461767648</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.752689666547312</v>
+        <v>-2.741822742653163</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.420223170834976</v>
+        <v>2.424569940392635</v>
       </c>
       <c r="F2009" t="n">
         <v>0.7250256391314638</v>
@@ -47775,16 +47775,16 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343064</v>
+        <v>3.712897612343069</v>
       </c>
       <c r="C2010" t="n">
         <v>3.5200894719778</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.750848647489061</v>
+        <v>-2.739981723594912</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.419393588668429</v>
+        <v>2.423740358226088</v>
       </c>
       <c r="F2010" t="n">
         <v>0.7262938658029322</v>
@@ -47798,16 +47798,16 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647104</v>
+        <v>3.754911907647108</v>
       </c>
       <c r="C2011" t="n">
         <v>3.533162878843719</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.883149939586614</v>
+        <v>-2.872283015692465</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.379546478695326</v>
+        <v>2.383893248252985</v>
       </c>
       <c r="F2011" t="n">
         <v>0.7262938658029322</v>
@@ -47821,16 +47821,16 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763531</v>
+        <v>3.749896851763535</v>
       </c>
       <c r="C2012" t="n">
         <v>3.533162878843719</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.884711582401474</v>
+        <v>-2.873844658507325</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.378921821569381</v>
+        <v>2.383268591127041</v>
       </c>
       <c r="F2012" t="n">
         <v>0.7262938658029322</v>
@@ -47844,16 +47844,16 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392115</v>
+        <v>3.715834055392119</v>
       </c>
       <c r="C2013" t="n">
         <v>3.531686919970721</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.912612369510947</v>
+        <v>-2.901745445616798</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.366285547852595</v>
+        <v>2.370632317410254</v>
       </c>
       <c r="F2013" t="n">
         <v>0.6916969416599974</v>
@@ -47867,16 +47867,16 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172526</v>
+        <v>3.684909939172529</v>
       </c>
       <c r="C2014" t="n">
         <v>3.528451363947919</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.035138472213841</v>
+        <v>-3.024271548319692</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.314039550748636</v>
+        <v>2.318386320306296</v>
       </c>
       <c r="F2014" t="n">
         <v>0.5691708389571035</v>
@@ -47890,16 +47890,16 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971077</v>
+        <v>3.619362241971081</v>
       </c>
       <c r="C2015" t="n">
         <v>3.595157323538423</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.055199793490348</v>
+        <v>-3.044332869596199</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.372720981828537</v>
+        <v>2.377067751386196</v>
       </c>
       <c r="F2015" t="n">
         <v>0.5491095176805965</v>
@@ -47913,16 +47913,16 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199805</v>
+        <v>3.640764248199808</v>
       </c>
       <c r="C2016" t="n">
         <v>3.73546904254027</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.311920611485172</v>
+        <v>-3.301053687591023</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.410344373632454</v>
+        <v>2.414691143190113</v>
       </c>
       <c r="F2016" t="n">
         <v>0.4406949435367816</v>
@@ -47936,16 +47936,16 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622235</v>
+        <v>3.668303164622238</v>
       </c>
       <c r="C2017" t="n">
         <v>3.80444931168591</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.465907029261312</v>
+        <v>-3.455040105367163</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.417730075667638</v>
+        <v>2.422076845225297</v>
       </c>
       <c r="F2017" t="n">
         <v>0.4406949435367816</v>
@@ -47959,16 +47959,16 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808527</v>
+        <v>3.619937176808531</v>
       </c>
       <c r="C2018" t="n">
         <v>3.790500513806031</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.415385125433646</v>
+        <v>-3.404518201539497</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.423990039318825</v>
+        <v>2.428336808876485</v>
       </c>
       <c r="F2018" t="n">
         <v>0.4406949435367816</v>
@@ -47982,16 +47982,16 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994892</v>
+        <v>3.656346893994896</v>
       </c>
       <c r="C2019" t="n">
         <v>3.802371002861445</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.667860279441371</v>
+        <v>-3.656993355547222</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.334870466771149</v>
+        <v>2.339217236328809</v>
       </c>
       <c r="F2019" t="n">
         <v>0.4406949435367816</v>
@@ -48005,16 +48005,16 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358297</v>
+        <v>3.6740426963583</v>
       </c>
       <c r="C2020" t="n">
         <v>3.803581537380389</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.937333081363079</v>
+        <v>-3.92646615746893</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.22829188052141</v>
+        <v>2.232638650079069</v>
       </c>
       <c r="F2020" t="n">
         <v>0.4406949435367816</v>
@@ -48028,16 +48028,16 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637085</v>
+        <v>3.663523617637089</v>
       </c>
       <c r="C2021" t="n">
         <v>3.80770327960771</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.09487715309252</v>
+        <v>-4.084010229198372</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.169395994056955</v>
+        <v>2.173742763614614</v>
       </c>
       <c r="F2021" t="n">
         <v>0.3737931383965071</v>
@@ -48051,16 +48051,16 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301342</v>
+        <v>3.652163313301346</v>
       </c>
       <c r="C2022" t="n">
         <v>3.802781132343899</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.372841548675794</v>
+        <v>-4.361974624781645</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.053288088559834</v>
+        <v>2.057634858117494</v>
       </c>
       <c r="F2022" t="n">
         <v>0.2841734041110229</v>
@@ -48074,16 +48074,16 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215468</v>
+        <v>3.667976467215472</v>
       </c>
       <c r="C2023" t="n">
         <v>3.964985189042944</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.489809241314685</v>
+        <v>-4.478942317420536</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.168705068203322</v>
+        <v>2.173051837760982</v>
       </c>
       <c r="F2023" t="n">
         <v>0.2841734041110229</v>
@@ -48097,16 +48097,16 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456691</v>
+        <v>3.696553628456694</v>
       </c>
       <c r="C2024" t="n">
         <v>3.959831827006758</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.574527183535638</v>
+        <v>-4.563660259641489</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.129664529278755</v>
+        <v>2.134011298836414</v>
       </c>
       <c r="F2024" t="n">
         <v>0.1990573751829765</v>
@@ -48120,16 +48120,16 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253287</v>
+        <v>3.75005817625329</v>
       </c>
       <c r="C2025" t="n">
         <v>3.970061244575249</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.656462001804521</v>
+        <v>-4.645595077910373</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.107120019539694</v>
+        <v>2.111466789097353</v>
       </c>
       <c r="F2025" t="n">
         <v>0.1891226295958963</v>
@@ -48143,16 +48143,16 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717831</v>
+        <v>3.783647027717834</v>
       </c>
       <c r="C2026" t="n">
         <v>3.978986883031151</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.602723828404259</v>
+        <v>-4.59185690451011</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.1375409273557</v>
+        <v>2.14188769691336</v>
       </c>
       <c r="F2026" t="n">
         <v>0.2428608029961584</v>
@@ -48166,16 +48166,16 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616948</v>
+        <v>3.798310944616951</v>
       </c>
       <c r="C2027" t="n">
         <v>3.971139770275327</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.492717544927038</v>
+        <v>-4.481850621032889</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.173696327990765</v>
+        <v>2.178043097548424</v>
       </c>
       <c r="F2027" t="n">
         <v>0.2660653749134336</v>
@@ -48189,16 +48189,16 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203663</v>
+        <v>3.785578085203665</v>
       </c>
       <c r="C2028" t="n">
         <v>3.975389780997301</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.349657969186111</v>
+        <v>-4.338791045291963</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.235170169009109</v>
+        <v>2.239516938566769</v>
       </c>
       <c r="F2028" t="n">
         <v>0.2740788015034129</v>
@@ -48212,16 +48212,16 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436929</v>
+        <v>3.77725157243693</v>
       </c>
       <c r="C2029" t="n">
         <v>3.982650663879838</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.048211243714274</v>
+        <v>-4.037344319820125</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.363009742080381</v>
+        <v>2.36735651163804</v>
       </c>
       <c r="F2029" t="n">
         <v>0.5755255269752502</v>
@@ -48235,16 +48235,16 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064767</v>
+        <v>3.812650101064769</v>
       </c>
       <c r="C2030" t="n">
         <v>3.983621841632548</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.103166440157343</v>
+        <v>-4.092299516263195</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.341998841255863</v>
+        <v>2.346345610813523</v>
       </c>
       <c r="F2030" t="n">
         <v>0.5755255269752502</v>
@@ -48258,16 +48258,16 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859301</v>
+        <v>3.821198342859303</v>
       </c>
       <c r="C2031" t="n">
         <v>3.984464746012303</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.052128064150823</v>
+        <v>-4.041261140256674</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.363257096038227</v>
+        <v>2.367603865595886</v>
       </c>
       <c r="F2031" t="n">
         <v>0.5755255269752502</v>
@@ -48281,16 +48281,16 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354684</v>
+        <v>3.831748677354686</v>
       </c>
       <c r="C2032" t="n">
         <v>4.003502844886449</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.010988769284192</v>
+        <v>-4.000121845390043</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.398750912859025</v>
+        <v>2.403097682416684</v>
       </c>
       <c r="F2032" t="n">
         <v>0.616664821841881</v>
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.749722466692664</v>
+        <v>3.847598262527111</v>
       </c>
       <c r="C2033" t="n">
         <v>3.819686841010383</v>
       </c>
       <c r="D2033" t="n">
-        <v>-3.901740047478154</v>
+        <v>-3.901358151773488</v>
       </c>
       <c r="E2033" t="n">
-        <v>2.258634397705375</v>
+        <v>2.258787155987241</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.7259135436479194</v>
+        <v>0.7154285154584363</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.255234967199136</v>
+        <v>4.248943950285446</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240723.xlsx
+++ b/tame_output/ON/bt/strategyON_20240723.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.1%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>24.5%</t>
         </is>
       </c>
     </row>
@@ -844,17 +844,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -864,17 +864,17 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.9%</t>
+          <t>-75.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.9%</t>
+          <t>108.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.8%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.8%</t>
+          <t>-48.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.3%</t>
+          <t>-71.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>456.5%</t>
+          <t>452.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-551.7%</t>
+          <t>-577.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-47.8%</t>
+          <t>-45.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-150.3%</t>
+          <t>-160.7%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>70.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.9%</t>
+          <t>-26.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-121.8%</t>
+          <t>-123.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-152.4%</t>
+          <t>-151.3%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>84.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>76.0%</t>
+          <t>75.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-20.4%</t>
         </is>
       </c>
     </row>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923082</v>
+        <v>3.41997943392308</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297743</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737164</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539458</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.600038265158919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.6848438238121</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611567</v>
+        <v>3.768951674611565</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232411</v>
+        <v>3.747702660232409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436227</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311948</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017771</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.462344633660318</v>
+        <v>-7.721684445021402</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1658220724375385</v>
+        <v>0.06208614789310518</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.314228376767125</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388728</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.422160335294127</v>
+        <v>-7.681500146655211</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1822394156718561</v>
+        <v>0.07850349112742272</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.274044078400934</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626474</v>
+        <v>3.85616175162647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.258760464354765</v>
+        <v>-7.518100275715849</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.246966185268358</v>
+        <v>0.1432302607239246</v>
       </c>
       <c r="F1902" t="n">
         <v>-1.110644207461571</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291814</v>
+        <v>3.787330429291811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.025279242125166</v>
+        <v>-7.28461905348625</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.34828310299805</v>
+        <v>0.2445471784536162</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.8771629852319727</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.80163712278579</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.875612851117651</v>
+        <v>-7.134952662478735</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4052574490880967</v>
+        <v>0.3015215245436633</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.7842594939894367</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76318224839043</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.743337377486765</v>
+        <v>-7.002677188847849</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4535351252874782</v>
+        <v>0.3497992007430448</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.6519840203585501</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.587599044927023</v>
+        <v>-6.846938856288107</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.518645518999012</v>
+        <v>0.4149095944545782</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.4962456877988085</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960988</v>
+        <v>3.753882571960984</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.338599246243442</v>
+        <v>-6.597939057604526</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6311517796961028</v>
+        <v>0.5274158551516694</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.4962456877988085</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607646</v>
+        <v>3.692931855607642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.444189236016546</v>
+        <v>-6.70352904737763</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4609398541876426</v>
+        <v>0.3572039296432088</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.6018356775719129</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.7704225839879</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.462924138135143</v>
+        <v>-6.722263949496227</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5019902352172902</v>
+        <v>0.3982543106728564</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.6074316872320442</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710815</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.314984096727544</v>
+        <v>-6.574323908088628</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4412873290921624</v>
+        <v>0.3375514045477286</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.5871107713234867</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409207</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.262014574473556</v>
+        <v>-6.521354385834639</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4537611517402795</v>
+        <v>0.3500252271958457</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.5341412490694978</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098112</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.218466167702865</v>
+        <v>-6.477805979063949</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4642199023534626</v>
+        <v>0.3604839778090287</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.5341412490694978</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493423</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.185102961224096</v>
+        <v>-6.44444277258518</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4920275393261129</v>
+        <v>0.3882916147816795</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.5341412490694978</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.076843824101575</v>
+        <v>-6.336183635462659</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5298633146343166</v>
+        <v>0.4261273900898832</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.5341412490694978</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792048</v>
+        <v>3.828052928792045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.953552689284444</v>
+        <v>-6.212892500645528</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5766778625717461</v>
+        <v>0.4729419380273123</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.4108501142523673</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919908</v>
+        <v>3.812453678919905</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.932403490381001</v>
+        <v>-6.191743301742084</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5928385203704485</v>
+        <v>0.4891025958260151</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.3897009153489239</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318094</v>
+        <v>3.74832840831809</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.688638048397556</v>
+        <v>-5.94797785975864</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.686125405510877</v>
+        <v>0.5823894809664436</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.3897009153489239</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.586875228120261</v>
+        <v>-5.846215039481345</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7289548475418108</v>
+        <v>0.6252189229973775</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.3764818469564952</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279183</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.337024834171187</v>
+        <v>-5.596364645532271</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8216370801051429</v>
+        <v>0.7179011555607095</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.3764818469564952</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011499</v>
+        <v>3.835957987011495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.161132741703755</v>
+        <v>-5.420472553064839</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8955930406127646</v>
+        <v>0.7918571160683308</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.3764818469564952</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.989686278681291</v>
+        <v>-5.249026090042375</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9774991318763036</v>
+        <v>0.8737632073318702</v>
       </c>
       <c r="F1921" t="n">
         <v>-0.2050353839340321</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632778</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.915396712942952</v>
+        <v>-5.174736524304036</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.006235435787936</v>
+        <v>0.9024995112435028</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.1307458181956928</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883074</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.851760970709018</v>
+        <v>-5.111100782070102</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.036384533735827</v>
+        <v>0.9326486091913937</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.06711007596175828</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074783</v>
+        <v>3.798814771074779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.740334211383098</v>
+        <v>-4.999674022744181</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.062149496249991</v>
+        <v>0.9584135717055573</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.06711007596175828</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.79769488424229</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.499903714578237</v>
+        <v>-4.759243525939321</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.160064771596812</v>
+        <v>1.056328847052379</v>
       </c>
       <c r="F1925" t="n">
         <v>0.173320420843102</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367683</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.427661146407043</v>
+        <v>-4.687000957768126</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.192891112700111</v>
+        <v>1.089155188155677</v>
       </c>
       <c r="F1926" t="n">
         <v>0.173320420843102</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879965</v>
+        <v>3.822326997879961</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.409947459529177</v>
+        <v>-4.669287270890261</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.200655171368597</v>
+        <v>1.096919246824163</v>
       </c>
       <c r="F1927" t="n">
         <v>0.1765017497400188</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502337</v>
+        <v>3.848616626502333</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.30114257404945</v>
+        <v>-4.560482385410534</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.241175196780481</v>
+        <v>1.137439272236047</v>
       </c>
       <c r="F1928" t="n">
         <v>0.1765017497400188</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675938</v>
+        <v>3.818668951675933</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.08112177601244</v>
+        <v>-4.340461587373523</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.330762553005899</v>
+        <v>1.227026628461466</v>
       </c>
       <c r="F1929" t="n">
         <v>0.3177215948079991</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327452753995</v>
+        <v>3.843274527539945</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.948254086949162</v>
+        <v>-4.207593898310246</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.399803811433034</v>
+        <v>1.2960678868886</v>
       </c>
       <c r="F1930" t="n">
         <v>0.3177215948079991</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>3.845047386496258</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.828081003584662</v>
+        <v>-4.087420814945747</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.449018889219135</v>
+        <v>1.345282964674702</v>
       </c>
       <c r="F1931" t="n">
         <v>0.437894678172498</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576999</v>
+        <v>3.791273551576995</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.683408858484925</v>
+        <v>-3.94274866984601</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.51697584982047</v>
+        <v>1.413239925276036</v>
       </c>
       <c r="F1932" t="n">
         <v>0.5825668232722354</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.7358392229421</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.743283685842617</v>
+        <v>-4.002623497203702</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.479063410278819</v>
+        <v>1.375327485734385</v>
       </c>
       <c r="F1933" t="n">
         <v>0.5226919959145433</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.62346345493178</v>
+        <v>-3.882803266292865</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.542280671877363</v>
+        <v>1.438544747332929</v>
       </c>
       <c r="F1934" t="n">
         <v>0.5226919959145433</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430689</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.625933161393586</v>
+        <v>-3.885272972754671</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.448936988615082</v>
+        <v>1.345201064070648</v>
       </c>
       <c r="F1935" t="n">
         <v>0.5202222894527371</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003601</v>
+        <v>3.743220196003597</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.694303347717596</v>
+        <v>-3.95364315907868</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.340850775570779</v>
+        <v>1.237114851026345</v>
       </c>
       <c r="F1936" t="n">
         <v>0.529497988488952</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508365</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.708091400564642</v>
+        <v>-3.967431211925727</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.325772263063852</v>
+        <v>1.222036338519418</v>
       </c>
       <c r="F1937" t="n">
         <v>0.529497988488952</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417699</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.763611476457232</v>
+        <v>-4.022951287818317</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.440595069399018</v>
+        <v>1.336859144854585</v>
       </c>
       <c r="F1938" t="n">
         <v>0.529497988488952</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205894</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.588137216664763</v>
+        <v>-3.847477028025847</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.515352005307794</v>
+        <v>1.41161608076336</v>
       </c>
       <c r="F1939" t="n">
         <v>0.529497988488952</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225443</v>
+        <v>3.765024323225439</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.688206545411863</v>
+        <v>-3.958413280667096</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.451066302570161</v>
+        <v>1.342983608468068</v>
       </c>
       <c r="F1940" t="n">
         <v>0.529497988488952</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111296</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.654542999939581</v>
+        <v>-3.924749735194814</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.393070034160523</v>
+        <v>1.28498734005843</v>
       </c>
       <c r="F1941" t="n">
         <v>0.5631615339612339</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264166</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.594690380735858</v>
+        <v>-3.864897115991091</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.427183468274145</v>
+        <v>1.319100774172052</v>
       </c>
       <c r="F1942" t="n">
         <v>0.5631615339612339</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742302</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.50844691770948</v>
+        <v>-3.778653652964714</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.456627124058556</v>
+        <v>1.348544429956463</v>
       </c>
       <c r="F1943" t="n">
         <v>0.5631615339612339</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316049</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.55375373710846</v>
+        <v>-3.823960472363694</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.43028017174349</v>
+        <v>1.322197477641397</v>
       </c>
       <c r="F1944" t="n">
         <v>0.5223513709520031</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803194</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.582786841810762</v>
+        <v>-3.852993577065995</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.419218802895671</v>
+        <v>1.311136108793578</v>
       </c>
       <c r="F1945" t="n">
         <v>0.5223513709520031</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809502</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.489976360359902</v>
+        <v>-3.760183095615136</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.38561568736738</v>
+        <v>1.277532993265287</v>
       </c>
       <c r="F1946" t="n">
         <v>0.6151618524028625</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560428</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.53436582968933</v>
+        <v>-3.804572564944563</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.36973337556021</v>
+        <v>1.261650681458117</v>
       </c>
       <c r="F1947" t="n">
         <v>0.5707723830734348</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.42169461145308</v>
+        <v>-3.691901346708313</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.409877571366433</v>
+        <v>1.30179487726434</v>
       </c>
       <c r="F1948" t="n">
         <v>0.683443601309685</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.309317610270407</v>
+        <v>-3.579524345525641</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.46031966767017</v>
+        <v>1.352236973568076</v>
       </c>
       <c r="F1949" t="n">
         <v>0.683443601309685</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.33709800817176</v>
+        <v>-3.607304743426994</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.460704710278167</v>
+        <v>1.352622016176074</v>
       </c>
       <c r="F1950" t="n">
         <v>0.6556632034083318</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705327</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.455478680901899</v>
+        <v>-3.725685416157132</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.251708161186765</v>
+        <v>1.143625467084672</v>
       </c>
       <c r="F1951" t="n">
         <v>0.5884453512573556</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.56409275934523</v>
+        <v>-3.834299494600463</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.328412190528638</v>
+        <v>1.220329496426545</v>
       </c>
       <c r="F1952" t="n">
         <v>0.5884453512573556</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73301244119077</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.528683721097087</v>
+        <v>-3.79889045635232</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.357088831930219</v>
+        <v>1.249006137828125</v>
       </c>
       <c r="F1953" t="n">
         <v>0.5884453512573556</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913427</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.490300058538936</v>
+        <v>-3.760506793794169</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.369861738295848</v>
+        <v>1.261779044193754</v>
       </c>
       <c r="F1954" t="n">
         <v>0.6268290138155068</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532488</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.31318372850377</v>
+        <v>-3.583390463759003</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.437437299155216</v>
+        <v>1.329354605053123</v>
       </c>
       <c r="F1955" t="n">
         <v>0.6268290138155068</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.358275973337316</v>
+        <v>-3.628482708592549</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.420083792983711</v>
+        <v>1.312001098881617</v>
       </c>
       <c r="F1956" t="n">
         <v>0.564932970646117</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011236</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.178900552098548</v>
+        <v>-3.449107287353781</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.485620936785632</v>
+        <v>1.377538242683539</v>
       </c>
       <c r="F1957" t="n">
         <v>0.7217097288168357</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982231</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.223914765619154</v>
+        <v>-3.494121500874388</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.448422706708979</v>
+        <v>1.340340012606886</v>
       </c>
       <c r="F1958" t="n">
         <v>0.6913608335022311</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.73702660850954</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.490919275891589</v>
+        <v>-3.761126011146823</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.347312464938951</v>
+        <v>1.239229770836858</v>
       </c>
       <c r="F1959" t="n">
         <v>0.4969977954592826</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760815</v>
+        <v>3.702309454760811</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.592117057328762</v>
+        <v>-3.862323792583996</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.306037274260583</v>
+        <v>1.19795458015849</v>
       </c>
       <c r="F1960" t="n">
         <v>0.4285889819139634</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.70557166181546</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.58560609071445</v>
+        <v>-3.855812825969683</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.306241622460625</v>
+        <v>1.198158928358532</v>
       </c>
       <c r="F1961" t="n">
         <v>0.4285889819139634</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378105</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.566567963007152</v>
+        <v>-3.836774698262386</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.310381592751789</v>
+        <v>1.202298898649696</v>
       </c>
       <c r="F1962" t="n">
         <v>0.3704053705827688</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131254</v>
+        <v>3.731064473131249</v>
       </c>
       <c r="C1963" t="n">
         <v>2.914947071207078</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.59769459415777</v>
+        <v>-3.867901329413004</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.475512809230222</v>
+        <v>1.367430115128129</v>
       </c>
       <c r="F1963" t="n">
         <v>0.3704053705827688</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067869</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.915780400193211</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.611561355491688</v>
+        <v>-3.881768090746921</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.470799433682789</v>
+        <v>1.362716739580696</v>
       </c>
       <c r="F1964" t="n">
         <v>0.3325474538489459</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789126</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.921788930590137</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.566757183951758</v>
+        <v>-3.836963919206991</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.494729632695687</v>
+        <v>1.386646938593593</v>
       </c>
       <c r="F1965" t="n">
         <v>0.3325474538489459</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519913</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.819739151867337</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.419014213716756</v>
+        <v>-3.689220948971989</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.451777042066887</v>
+        <v>1.343694347964794</v>
       </c>
       <c r="F1966" t="n">
         <v>0.5003548110838291</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181175</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.822532773398818</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.521028896247977</v>
+        <v>-3.79123563150321</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.41376479058588</v>
+        <v>1.305682096483786</v>
       </c>
       <c r="F1967" t="n">
         <v>0.5003548110838291</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394734</v>
+        <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
         <v>2.823195121790476</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.514876190195192</v>
+        <v>-3.785082925450426</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.416888221398652</v>
+        <v>1.308805527296558</v>
       </c>
       <c r="F1968" t="n">
         <v>0.5065075171366133</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890616</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.822275598530586</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.531685488345694</v>
+        <v>-3.801892223600927</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.409244978878561</v>
+        <v>1.301162284776468</v>
       </c>
       <c r="F1969" t="n">
         <v>0.4896982189861117</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798431</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>2.888611152327407</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.469387489569572</v>
+        <v>-3.739594224824805</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.500499732185831</v>
+        <v>1.392417038083738</v>
       </c>
       <c r="F1970" t="n">
         <v>0.4896982189861117</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992195</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
         <v>2.690903154041534</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.267597291904414</v>
+        <v>-3.537804027159647</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.383507812966021</v>
+        <v>1.275425118863928</v>
       </c>
       <c r="F1971" t="n">
         <v>0.687716411155266</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852429</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
         <v>2.761193386363709</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.318484004590609</v>
+        <v>-3.588690739845842</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.433443360213719</v>
+        <v>1.325360666111625</v>
       </c>
       <c r="F1972" t="n">
         <v>0.6368296984690716</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.81906330031955</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
         <v>2.775821122479753</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.416224549215583</v>
+        <v>-3.686431284470816</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.408974878479773</v>
+        <v>1.300892184377679</v>
       </c>
       <c r="F1973" t="n">
         <v>0.6209404203360913</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489389</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.774357103304425</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.592562309338512</v>
+        <v>-3.862769044593746</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.336975755255273</v>
+        <v>1.228893061153179</v>
       </c>
       <c r="F1974" t="n">
         <v>0.4446026602131619</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397799</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.772848721344353</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.516140262906585</v>
+        <v>-3.786346998161819</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.366036191867972</v>
+        <v>1.257953497765878</v>
       </c>
       <c r="F1975" t="n">
         <v>0.4446026602131619</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316254</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
         <v>2.77271158877979</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.471767131268017</v>
+        <v>-3.74197386652325</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.383648311958836</v>
+        <v>1.275565617856742</v>
       </c>
       <c r="F1976" t="n">
         <v>0.4889757918517306</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105971</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
         <v>2.76710538291838</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.348932910380849</v>
+        <v>-3.619139645636083</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.427175794452293</v>
+        <v>1.3190931003502</v>
       </c>
       <c r="F1977" t="n">
         <v>0.4889757918517306</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190329</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
         <v>2.773487139946185</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.301277179819794</v>
+        <v>-3.571483915075027</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.45261984370452</v>
+        <v>1.344537149602427</v>
       </c>
       <c r="F1978" t="n">
         <v>0.5366315224127862</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569622</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
         <v>2.778379513320909</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.200759021321039</v>
+        <v>-3.470965756576272</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.497719480478747</v>
+        <v>1.389636786376653</v>
       </c>
       <c r="F1979" t="n">
         <v>0.6371496809115408</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557297</v>
+        <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
         <v>2.765134185796782</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.261425611723428</v>
+        <v>-3.531632346978661</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.460207516793663</v>
+        <v>1.35212482269157</v>
       </c>
       <c r="F1980" t="n">
         <v>0.5554513641930071</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932773</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
         <v>2.76923188840741</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.21658721011503</v>
+        <v>-3.486793945370263</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.482240580047651</v>
+        <v>1.374157885945558</v>
       </c>
       <c r="F1981" t="n">
         <v>0.5599947971378766</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917055</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.773392828038488</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.236085666357038</v>
+        <v>-3.506292401612272</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.478602137181926</v>
+        <v>1.370519443079832</v>
       </c>
       <c r="F1982" t="n">
         <v>0.5119101558579723</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405963</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.779272430566325</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.191882829271138</v>
+        <v>-3.462089564526371</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.502162874544123</v>
+        <v>1.39408018044203</v>
       </c>
       <c r="F1983" t="n">
         <v>0.5561129929438727</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265648</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
         <v>2.777682431035573</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.228861856934581</v>
+        <v>-3.499068592189814</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.485781263947993</v>
+        <v>1.3776985698459</v>
       </c>
       <c r="F1984" t="n">
         <v>0.5930868947352033</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284882</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.828930196218613</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.070570439395309</v>
+        <v>-3.340777174650542</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.600345596146742</v>
+        <v>1.492262902044649</v>
       </c>
       <c r="F1985" t="n">
         <v>0.5930868947352033</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321025</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.827370900812866</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.862928435760832</v>
+        <v>-3.133135171016066</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.681843102194785</v>
+        <v>1.573760408092692</v>
       </c>
       <c r="F1986" t="n">
         <v>0.8007288983696794</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475142</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.822319129051136</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.811896343038304</v>
+        <v>-3.082103078293538</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.697204167522067</v>
+        <v>1.589121473419973</v>
       </c>
       <c r="F1987" t="n">
         <v>0.8517609910922074</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404856</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.839506533143841</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.746672161911099</v>
+        <v>-3.016878897166333</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.740481244065654</v>
+        <v>1.63239854996356</v>
       </c>
       <c r="F1988" t="n">
         <v>0.916985172219413</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.84006118688256</v>
+        <v>3.840061186882555</v>
       </c>
       <c r="C1989" t="n">
         <v>2.835467505443121</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.709245141839965</v>
+        <v>-2.979451877095199</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.751413024393388</v>
+        <v>1.643330330291294</v>
       </c>
       <c r="F1989" t="n">
         <v>0.9222367102485947</v>
@@ -47315,16 +47315,16 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992663</v>
+        <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
         <v>2.836724297774361</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.729356797874674</v>
+        <v>-2.999563533129907</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.744625154310745</v>
+        <v>1.636542460208651</v>
       </c>
       <c r="F1990" t="n">
         <v>0.9332640552460139</v>
@@ -47338,16 +47338,16 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.82866144563629</v>
+        <v>3.828661445636285</v>
       </c>
       <c r="C1991" t="n">
         <v>2.997282068795572</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.675611983447469</v>
+        <v>-2.945818718702702</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.926680851102837</v>
+        <v>1.818598157000744</v>
       </c>
       <c r="F1991" t="n">
         <v>0.9433273646864758</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957629</v>
+        <v>3.813222820957623</v>
       </c>
       <c r="C1992" t="n">
         <v>3.117394978013389</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.600829722422456</v>
+        <v>-2.87103645767769</v>
       </c>
       <c r="E1992" t="n">
-        <v>2.07670666473066</v>
+        <v>1.968623970628566</v>
       </c>
       <c r="F1992" t="n">
         <v>1.018109625711488</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998758</v>
+        <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
         <v>3.109102954027248</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.574745638158648</v>
+        <v>-2.844952373413882</v>
       </c>
       <c r="E1993" t="n">
-        <v>2.078848274450042</v>
+        <v>1.970765580347948</v>
       </c>
       <c r="F1993" t="n">
         <v>1.018109625711488</v>
@@ -47407,16 +47407,16 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896932</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>3.107296149611028</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.496614457309701</v>
+        <v>-2.766821192564935</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.1082939423734</v>
+        <v>2.000211248271307</v>
       </c>
       <c r="F1994" t="n">
         <v>1.092286436595173</v>
@@ -47430,16 +47430,16 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.79626414395986</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>3.124850555337819</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.487721995916418</v>
+        <v>-2.757928731171652</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.129405332657504</v>
+        <v>2.021322638555411</v>
       </c>
       <c r="F1995" t="n">
         <v>1.092286436595173</v>
@@ -47453,16 +47453,16 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945368</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
         <v>3.116705602742403</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.656198112886296</v>
+        <v>-2.92640484814153</v>
       </c>
       <c r="E1996" t="n">
-        <v>2.053869933274138</v>
+        <v>1.945787239172044</v>
       </c>
       <c r="F1996" t="n">
         <v>1.064338600878592</v>
@@ -47476,16 +47476,16 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.79557406678271</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>3.097975299930265</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.958398584024713</v>
+        <v>-2.228605319279946</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.314259442006632</v>
+        <v>2.206176747904539</v>
       </c>
       <c r="F1997" t="n">
         <v>0.9939905415081816</v>
@@ -47499,16 +47499,16 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632638</v>
+        <v>3.784671345632634</v>
       </c>
       <c r="C1998" t="n">
         <v>3.08863932242717</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.93567748034156</v>
+        <v>-2.205884215596794</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.314011905976798</v>
+        <v>2.205929211874705</v>
       </c>
       <c r="F1998" t="n">
         <v>0.9939905415081816</v>
@@ -47522,16 +47522,16 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777676</v>
+        <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
         <v>3.247545448278339</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.064879293635603</v>
+        <v>-2.335086028890836</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.42123730651035</v>
+        <v>2.313154612408257</v>
       </c>
       <c r="F1999" t="n">
         <v>0.8647887282141393</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644415</v>
+        <v>3.77993372564441</v>
       </c>
       <c r="C2000" t="n">
         <v>3.284623270771985</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.219660300413858</v>
+        <v>-2.489867035669092</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.396402726292695</v>
+        <v>2.288320032190601</v>
       </c>
       <c r="F2000" t="n">
         <v>0.8314210541596632</v>
@@ -47568,16 +47568,16 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799967</v>
+        <v>3.769443619799962</v>
       </c>
       <c r="C2001" t="n">
         <v>3.28129862676153</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.212605610198685</v>
+        <v>-2.482812345453918</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.395899958368309</v>
+        <v>2.287817264266216</v>
       </c>
       <c r="F2001" t="n">
         <v>0.838475744374837</v>
@@ -47591,16 +47591,16 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331119</v>
+        <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
         <v>3.291304780406272</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.185654385872197</v>
+        <v>-2.45586112112743</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.416686601743646</v>
+        <v>2.308603907641552</v>
       </c>
       <c r="F2002" t="n">
         <v>0.8533560904025561</v>
@@ -47614,16 +47614,16 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.76805206778411</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
         <v>3.475407912551232</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.321607393928513</v>
+        <v>-2.591814129183747</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.546408530666079</v>
+        <v>2.438325836563986</v>
       </c>
       <c r="F2003" t="n">
         <v>0.8533560904025561</v>
@@ -47637,16 +47637,16 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714429</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
         <v>3.467524607454225</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.344015511733385</v>
+        <v>-2.614222246988619</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.529561978447123</v>
+        <v>2.42147928434503</v>
       </c>
       <c r="F2004" t="n">
         <v>0.8533560904025561</v>
@@ -47660,16 +47660,16 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155035</v>
+        <v>3.719118627155031</v>
       </c>
       <c r="C2005" t="n">
         <v>3.469578607003862</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.492021279212785</v>
+        <v>-2.762228014468018</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.472413671005001</v>
+        <v>2.364330976902908</v>
       </c>
       <c r="F2005" t="n">
         <v>0.7666290815390147</v>
@@ -47683,16 +47683,16 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161981</v>
+        <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
         <v>3.525832324725709</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.501462205101315</v>
+        <v>-2.771668940356548</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.524891018371436</v>
+        <v>2.416808324269343</v>
       </c>
       <c r="F2006" t="n">
         <v>0.8890561990824061</v>
@@ -47706,16 +47706,16 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321638</v>
+        <v>3.714941193321633</v>
       </c>
       <c r="C2007" t="n">
         <v>3.52872341927101</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.553735812436956</v>
+        <v>-2.82394254769219</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.506872669982481</v>
+        <v>2.398789975880387</v>
       </c>
       <c r="F2007" t="n">
         <v>0.8367825917467648</v>
@@ -47729,16 +47729,16 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347707</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.526835232164785</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.630065790037862</v>
+        <v>-2.900272525293095</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.474452491835893</v>
+        <v>2.3663697977338</v>
       </c>
       <c r="F2008" t="n">
         <v>0.8367825917467648</v>
@@ -47752,16 +47752,16 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887751</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
         <v>3.521655461767648</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.741822742653163</v>
+        <v>-3.012029477908396</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.424569940392635</v>
+        <v>2.316487246290542</v>
       </c>
       <c r="F2009" t="n">
         <v>0.7250256391314638</v>
@@ -47775,16 +47775,16 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343069</v>
+        <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
         <v>3.5200894719778</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.739981723594912</v>
+        <v>-3.010188458850145</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.423740358226088</v>
+        <v>2.315657664123995</v>
       </c>
       <c r="F2010" t="n">
         <v>0.7262938658029322</v>
@@ -47798,16 +47798,16 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647108</v>
+        <v>3.754911907647104</v>
       </c>
       <c r="C2011" t="n">
         <v>3.533162878843719</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.872283015692465</v>
+        <v>-3.142489750947699</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.383893248252985</v>
+        <v>2.275810554150892</v>
       </c>
       <c r="F2011" t="n">
         <v>0.7262938658029322</v>
@@ -47821,16 +47821,16 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763535</v>
+        <v>3.749896851763531</v>
       </c>
       <c r="C2012" t="n">
         <v>3.533162878843719</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.873844658507325</v>
+        <v>-3.144051393762559</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.383268591127041</v>
+        <v>2.275185897024948</v>
       </c>
       <c r="F2012" t="n">
         <v>0.7262938658029322</v>
@@ -47844,16 +47844,16 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392119</v>
+        <v>3.715834055392115</v>
       </c>
       <c r="C2013" t="n">
         <v>3.531686919970721</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.901745445616798</v>
+        <v>-3.171952180872032</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.370632317410254</v>
+        <v>2.262549623308161</v>
       </c>
       <c r="F2013" t="n">
         <v>0.6916969416599974</v>
@@ -47867,16 +47867,16 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172529</v>
+        <v>3.684909939172526</v>
       </c>
       <c r="C2014" t="n">
         <v>3.528451363947919</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.024271548319692</v>
+        <v>-3.294478283574926</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.318386320306296</v>
+        <v>2.210303626204202</v>
       </c>
       <c r="F2014" t="n">
         <v>0.5691708389571035</v>
@@ -47890,16 +47890,16 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971081</v>
+        <v>3.619362241971077</v>
       </c>
       <c r="C2015" t="n">
         <v>3.595157323538423</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.044332869596199</v>
+        <v>-3.314539604851432</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.377067751386196</v>
+        <v>2.268985057284103</v>
       </c>
       <c r="F2015" t="n">
         <v>0.5491095176805965</v>
@@ -47913,16 +47913,16 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199808</v>
+        <v>3.640764248199805</v>
       </c>
       <c r="C2016" t="n">
         <v>3.73546904254027</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.301053687591023</v>
+        <v>-3.571260422846256</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.414691143190113</v>
+        <v>2.30660844908802</v>
       </c>
       <c r="F2016" t="n">
         <v>0.4406949435367816</v>
@@ -47936,16 +47936,16 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622238</v>
+        <v>3.668303164622235</v>
       </c>
       <c r="C2017" t="n">
         <v>3.80444931168591</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.455040105367163</v>
+        <v>-3.725246840622397</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.422076845225297</v>
+        <v>2.313994151123204</v>
       </c>
       <c r="F2017" t="n">
         <v>0.4406949435367816</v>
@@ -47959,16 +47959,16 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808531</v>
+        <v>3.619937176808527</v>
       </c>
       <c r="C2018" t="n">
         <v>3.790500513806031</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.404518201539497</v>
+        <v>-3.674724936794731</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.428336808876485</v>
+        <v>2.320254114774391</v>
       </c>
       <c r="F2018" t="n">
         <v>0.4406949435367816</v>
@@ -47982,16 +47982,16 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994896</v>
+        <v>3.656346893994892</v>
       </c>
       <c r="C2019" t="n">
         <v>3.802371002861445</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.656993355547222</v>
+        <v>-3.927200090802455</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.339217236328809</v>
+        <v>2.231134542226715</v>
       </c>
       <c r="F2019" t="n">
         <v>0.4406949435367816</v>
@@ -48005,16 +48005,16 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.6740426963583</v>
+        <v>3.674042696358297</v>
       </c>
       <c r="C2020" t="n">
         <v>3.803581537380389</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.92646615746893</v>
+        <v>-4.196672892724163</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.232638650079069</v>
+        <v>2.124555955976976</v>
       </c>
       <c r="F2020" t="n">
         <v>0.4406949435367816</v>
@@ -48028,16 +48028,16 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637089</v>
+        <v>3.663523617637085</v>
       </c>
       <c r="C2021" t="n">
         <v>3.80770327960771</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.084010229198372</v>
+        <v>-4.354216964453605</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.173742763614614</v>
+        <v>2.06566006951252</v>
       </c>
       <c r="F2021" t="n">
         <v>0.3737931383965071</v>
@@ -48051,16 +48051,16 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301346</v>
+        <v>3.652163313301342</v>
       </c>
       <c r="C2022" t="n">
         <v>3.802781132343899</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.361974624781645</v>
+        <v>-4.632181360036879</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.057634858117494</v>
+        <v>1.949552164015401</v>
       </c>
       <c r="F2022" t="n">
         <v>0.2841734041110229</v>
@@ -48074,16 +48074,16 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215472</v>
+        <v>3.667976467215468</v>
       </c>
       <c r="C2023" t="n">
         <v>3.964985189042944</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.478942317420536</v>
+        <v>-4.74914905267577</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.173051837760982</v>
+        <v>2.064969143658888</v>
       </c>
       <c r="F2023" t="n">
         <v>0.2841734041110229</v>
@@ -48097,16 +48097,16 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456694</v>
+        <v>3.696553628456691</v>
       </c>
       <c r="C2024" t="n">
         <v>3.959831827006758</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.563660259641489</v>
+        <v>-4.833866994896723</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.134011298836414</v>
+        <v>2.025928604734321</v>
       </c>
       <c r="F2024" t="n">
         <v>0.1990573751829765</v>
@@ -48120,16 +48120,16 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.75005817625329</v>
+        <v>3.750058176253287</v>
       </c>
       <c r="C2025" t="n">
         <v>3.970061244575249</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.645595077910373</v>
+        <v>-4.915801813165606</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.111466789097353</v>
+        <v>2.003384094995259</v>
       </c>
       <c r="F2025" t="n">
         <v>0.1891226295958963</v>
@@ -48143,16 +48143,16 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717834</v>
+        <v>3.783647027717831</v>
       </c>
       <c r="C2026" t="n">
         <v>3.978986883031151</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.59185690451011</v>
+        <v>-4.862063639765344</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.14188769691336</v>
+        <v>2.033805002811266</v>
       </c>
       <c r="F2026" t="n">
         <v>0.2428608029961584</v>
@@ -48166,16 +48166,16 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616951</v>
+        <v>3.798310944616948</v>
       </c>
       <c r="C2027" t="n">
         <v>3.971139770275327</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.481850621032889</v>
+        <v>-4.752057356288122</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.178043097548424</v>
+        <v>2.069960403446331</v>
       </c>
       <c r="F2027" t="n">
         <v>0.2660653749134336</v>
@@ -48189,16 +48189,16 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203665</v>
+        <v>3.785578085203663</v>
       </c>
       <c r="C2028" t="n">
         <v>3.975389780997301</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.338791045291963</v>
+        <v>-4.608997780547197</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.239516938566769</v>
+        <v>2.131434244464675</v>
       </c>
       <c r="F2028" t="n">
         <v>0.2740788015034129</v>
@@ -48212,16 +48212,16 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.77725157243693</v>
+        <v>3.777251572436929</v>
       </c>
       <c r="C2029" t="n">
         <v>3.982650663879838</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.037344319820125</v>
+        <v>-4.30755105507536</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.36735651163804</v>
+        <v>2.259273817535947</v>
       </c>
       <c r="F2029" t="n">
         <v>0.5755255269752502</v>
@@ -48235,16 +48235,16 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064769</v>
+        <v>3.812650101064767</v>
       </c>
       <c r="C2030" t="n">
         <v>3.983621841632548</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.092299516263195</v>
+        <v>-4.362506251518429</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.346345610813523</v>
+        <v>2.238262916711429</v>
       </c>
       <c r="F2030" t="n">
         <v>0.5755255269752502</v>
@@ -48258,16 +48258,16 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859303</v>
+        <v>3.821198342859301</v>
       </c>
       <c r="C2031" t="n">
         <v>3.984464746012303</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.041261140256674</v>
+        <v>-4.311467875511909</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.367603865595886</v>
+        <v>2.259521171493793</v>
       </c>
       <c r="F2031" t="n">
         <v>0.5755255269752502</v>
@@ -48281,16 +48281,16 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354686</v>
+        <v>3.831748677354684</v>
       </c>
       <c r="C2032" t="n">
         <v>4.003502844886449</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.000121845390043</v>
+        <v>-4.270328580645278</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.403097682416684</v>
+        <v>2.29501498831459</v>
       </c>
       <c r="F2032" t="n">
         <v>0.616664821841881</v>
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.847598262527111</v>
+        <v>3.526103024090933</v>
       </c>
       <c r="C2033" t="n">
         <v>3.819686841010383</v>
       </c>
       <c r="D2033" t="n">
-        <v>-3.901358151773488</v>
+        <v>-4.159722440565676</v>
       </c>
       <c r="E2033" t="n">
-        <v>2.258787155987241</v>
+        <v>2.155441440470366</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.7154285154584363</v>
+        <v>0.727270961921483</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.248943950285446</v>
+        <v>4.256049418163274</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240723.xlsx
+++ b/tame_output/ON/bt/strategyON_20240723.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>57.3%</t>
         </is>
       </c>
     </row>
@@ -844,17 +844,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -864,17 +864,17 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.6%</t>
+          <t>-74.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.5%</t>
+          <t>110.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>96.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.3%</t>
+          <t>-70.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.5%</t>
+          <t>456.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-577.5%</t>
+          <t>-551.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,27 +1150,27 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.6%</t>
+          <t>-34.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-45.7%</t>
+          <t>-44.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-160.7%</t>
+          <t>-150.1%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-123.1%</t>
+          <t>-120.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-151.3%</t>
+          <t>-152.6%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>84.4%</t>
+          <t>84.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.2%</t>
+          <t>-22.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>76.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-17.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-20.4%</t>
+          <t>-21.2%</t>
         </is>
       </c>
     </row>
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.477989729264485</v>
+        <v>-7.471830951507869</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.1256098388030513</v>
+        <v>0.1280733499056983</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.171133866027758</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.422191348780327</v>
+        <v>2.414481835205938</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.664709437573788</v>
+        <v>-7.658550659817172</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.04689565094492743</v>
+        <v>0.04935916204757396</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.171133866027758</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.418165044245924</v>
+        <v>2.410455530671535</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.047710826316418</v>
+        <v>-8.041552048559803</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.106407005873709</v>
+        <v>-0.1039434947710625</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.171133866027758</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.41806294292434</v>
+        <v>2.410353429349951</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.44775050131761</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.052197271517807</v>
+        <v>-8.046038493761191</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.1056300679828341</v>
+        <v>-0.1031665568801881</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.162771121938499</v>
+        <v>-1.175620311229147</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.417942591774937</v>
+        <v>2.410233078200548</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.411727594021809</v>
+        <v>-8.405568816265193</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.2440918936863845</v>
+        <v>-0.2416283825837384</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.162771121938499</v>
+        <v>-1.175620311229147</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.423292895072987</v>
+        <v>2.415583381498598</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.462076657476031</v>
+        <v>-8.455917879719415</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.256315499110896</v>
+        <v>-0.2538519880082499</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.213120185392721</v>
+        <v>-1.225969374683369</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.400999476957631</v>
+        <v>2.393289963383242</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.559695934897427</v>
+        <v>-8.553537157140811</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.2923214594576855</v>
+        <v>-0.2898579483550394</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.310739462814118</v>
+        <v>-1.323588652104766</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.345469661126562</v>
+        <v>2.337760147552173</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.613767434405785</v>
+        <v>-8.60760865664917</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.311056502939457</v>
+        <v>-0.3085929918368104</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.364810962322477</v>
+        <v>-1.377660151613125</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.315920317743119</v>
+        <v>2.30821080416873</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.818025609735649</v>
+        <v>-8.811866831979033</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3872465759527599</v>
+        <v>-0.3847830648501138</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.492449906936466</v>
+        <v>-1.505299096227114</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.244850148093368</v>
+        <v>2.237140634518979</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.851678448244122</v>
+        <v>-8.845519670487507</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3962251568717132</v>
+        <v>-0.3937616457690671</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.592863274853503</v>
+        <v>-1.605712464144152</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.189084681827581</v>
+        <v>2.181375168253192</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.778208616576674</v>
+        <v>-8.772049838820058</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.3514655227113126</v>
+        <v>-0.3490020116086665</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.519393443186055</v>
+        <v>-1.532242632476703</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.248538282321471</v>
+        <v>2.240828768747082</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.953333033963217</v>
+        <v>-8.947174256206601</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.406960068918413</v>
+        <v>-0.4044965578157669</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.694517860572599</v>
+        <v>-1.707367049863247</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.158018852637062</v>
+        <v>2.150309339062673</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587859441027</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.187785127977707</v>
+        <v>-9.181626350221091</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.507960071425805</v>
+        <v>-0.5054965603231589</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.694517860572599</v>
+        <v>-1.707367049863247</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.150799687735466</v>
+        <v>2.143090174161077</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.292159859004153</v>
+        <v>-9.286001081247537</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5563821546103598</v>
+        <v>-0.5539186435077137</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.798892591599045</v>
+        <v>-1.811741780889693</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.081502658345622</v>
+        <v>2.073793144771233</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.34494601460448</v>
+        <v>-9.338787236847864</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5763808270119339</v>
+        <v>-0.5739173159092879</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.894568078181442</v>
+        <v>-1.90741726747209</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.025213156234741</v>
+        <v>2.017503642660351</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.470982807972769</v>
+        <v>-9.464824030216153</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.624101815730135</v>
+        <v>-0.6216383046274889</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.882165644662348</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.0430578585497</v>
+        <v>2.035348344975311</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.413911036076838</v>
+        <v>-9.407752258320222</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5972827712853621</v>
+        <v>-0.5948192601827156</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.882165644662348</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.047048194236101</v>
+        <v>2.039338680661713</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158919</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.555582877800958</v>
+        <v>-9.549424100044343</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6554267348737519</v>
+        <v>-0.6529632237711054</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.882165644662348</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.045572967337359</v>
+        <v>2.037863453762971</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940716</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.505992033376124</v>
+        <v>-9.499833255619508</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6205369869389457</v>
+        <v>-0.6180734758362996</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.819725610946866</v>
+        <v>-1.832574800237514</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.090380884157132</v>
+        <v>2.082671370582744</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.357073698904268</v>
+        <v>-9.350914921147652</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5740207867968863</v>
+        <v>-0.5715572756942398</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.788476020211692</v>
+        <v>-1.801325209502341</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.096079504951553</v>
+        <v>2.088369991377164</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615281</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.131228546184857</v>
+        <v>-9.12506976842824</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4741036526729134</v>
+        <v>-0.4716401415702665</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.746549344624529</v>
+        <v>-1.759398533915177</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.13081458334006</v>
+        <v>2.123105069765671</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848438238121</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.006649889847266</v>
+        <v>-9.000491112090648</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4231330455818179</v>
+        <v>-0.4206695344791709</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.746549344624529</v>
+        <v>-1.759398533915177</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.131953727896119</v>
+        <v>2.12424421432173</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646214</v>
+        <v>3.710935533646215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.059545177891552</v>
+        <v>-9.053386400134935</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4416573866374249</v>
+        <v>-0.439193875534778</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.754443187826731</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.137560709711294</v>
+        <v>2.129851196136905</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611565</v>
+        <v>3.768951674611566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.987412002603671</v>
+        <v>-8.981253224847054</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.4070704122836357</v>
+        <v>-0.4046069011809887</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.754443187826731</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.14329441394993</v>
+        <v>2.135584900375542</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955325</v>
+        <v>3.728577929955326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.916045609994024</v>
+        <v>-8.909886832237406</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3882611176336423</v>
+        <v>-0.3857976065309954</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.683076795217083</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.176376987121854</v>
+        <v>2.168667473547465</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232409</v>
+        <v>3.74770266023241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.822586576008799</v>
+        <v>-8.816427798252182</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.36076098535246</v>
+        <v>-0.3582974742498131</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.683076795217083</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.166493505808947</v>
+        <v>2.158783992234558</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.555344775140401</v>
+        <v>-8.549185997383784</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2556988255044748</v>
+        <v>-0.2532353144018278</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.683076795217083</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.164658945309573</v>
+        <v>2.156949431735184</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.457437736463911</v>
+        <v>-8.451278958707293</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2168363250073391</v>
+        <v>-0.2143728139046921</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.602241856065878</v>
+        <v>-1.615091045356527</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.205150080252446</v>
+        <v>2.197440566678057</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.433484195487953</v>
+        <v>-8.427325417731335</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2065864024714625</v>
+        <v>-0.2041228913688156</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.578288315089921</v>
+        <v>-1.591137504380569</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.220190710983514</v>
+        <v>2.212481197409125</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.78931111201777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.169424257165156</v>
+        <v>-8.163265479408539</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1142227433040959</v>
+        <v>-0.1117592322014489</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.327077566057773</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.365366357815439</v>
+        <v>2.357656844241051</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.721684445021402</v>
+        <v>-7.4561858559037</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.06208614789310518</v>
+        <v>0.1682855835401855</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.327077566057773</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.362579324155138</v>
+        <v>2.35486981058075</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.681500146655211</v>
+        <v>-7.41600155753751</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.07850349112742272</v>
+        <v>0.1847029267745031</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.274044078400934</v>
+        <v>-1.286893267691582</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.387033527062695</v>
+        <v>2.379324013488306</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85616175162647</v>
+        <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.518100275715849</v>
+        <v>-7.252601686598148</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.1432302607239246</v>
+        <v>0.249429696371005</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.110644207461571</v>
+        <v>-1.123493396752219</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.484440270847069</v>
+        <v>2.47673075727268</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291811</v>
+        <v>3.787330429291814</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.28461905348625</v>
+        <v>-7.019120464368549</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2445471784536162</v>
+        <v>0.350746614100697</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8771629852319727</v>
+        <v>-0.8900121745226208</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.632453433022681</v>
+        <v>2.624743919448292</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785789</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.134952662478735</v>
+        <v>-6.869454073361034</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3015215245436633</v>
+        <v>0.4077209601907437</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7842594939894367</v>
+        <v>-0.7971086832800849</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.685303317455243</v>
+        <v>2.677593803880854</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.002677188847849</v>
+        <v>-6.737178599730147</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3497992007430448</v>
+        <v>0.4559986363901252</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6519840203585501</v>
+        <v>-0.6648332096491982</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.760036088380802</v>
+        <v>2.752326574806413</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.784718794105953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.846938856288107</v>
+        <v>-6.581440267170406</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4149095944545782</v>
+        <v>0.521109030101659</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.5090948770894567</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.856294148604284</v>
+        <v>2.848584635029895</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960984</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.597939057604526</v>
+        <v>-6.332440468486825</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5274158551516694</v>
+        <v>0.6336152907987498</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.5090948770894567</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.869200489827942</v>
+        <v>2.861490976253553</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607642</v>
+        <v>3.692931855607645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.70352904737763</v>
+        <v>-6.438030458259929</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3572039296432088</v>
+        <v>0.4634033652902896</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.6018356775719129</v>
+        <v>-0.6146848668625611</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.677870566364861</v>
+        <v>2.670161052790472</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704225839879</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.722263949496227</v>
+        <v>-6.456765360378526</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3982543106728564</v>
+        <v>0.5044537463199372</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.6074316872320442</v>
+        <v>-0.6202808765226924</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.723057302445869</v>
+        <v>2.71534778887148</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710814</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.574323908088628</v>
+        <v>-6.308825318970927</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3375514045477286</v>
+        <v>0.4437508401948094</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.5871107713234867</v>
+        <v>-0.5999599606141348</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.615370929302836</v>
+        <v>2.607661415728447</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409206</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.521354385834639</v>
+        <v>-6.255855796716938</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3500252271958457</v>
+        <v>0.4562246628429265</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.5469904383601459</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.638438656401751</v>
+        <v>2.630729142827362</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.729969716098111</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.477805979063949</v>
+        <v>-6.212307389946248</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3604839778090287</v>
+        <v>0.4666834134561095</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.5469904383601459</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.631478044306657</v>
+        <v>2.623768530732268</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493422</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.44444277258518</v>
+        <v>-6.178944183467479</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3882916147816795</v>
+        <v>0.4944910504287598</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.5469904383601459</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.645940398687801</v>
+        <v>2.638230885113412</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.336183635462659</v>
+        <v>-6.070685046344957</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4261273900898832</v>
+        <v>0.5323268257369635</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.5469904383601459</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.640472519146996</v>
+        <v>2.632763005572607</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792045</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.212892500645528</v>
+        <v>-5.947393911527826</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4729419380273123</v>
+        <v>0.5791413736743931</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.4108501142523673</v>
+        <v>-0.4236993035430154</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.711945294047851</v>
+        <v>2.704235780473462</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919905</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.191743301742084</v>
+        <v>-5.926244712624383</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4891025958260151</v>
+        <v>0.5953020314730955</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.3897009153489239</v>
+        <v>-0.4025501046395721</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.732335791627242</v>
+        <v>2.724626278052853</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.74832840831809</v>
+        <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.94797785975864</v>
+        <v>-5.682479270640939</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5823894809664436</v>
+        <v>0.6885889166135239</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.3897009153489239</v>
+        <v>-0.4025501046395721</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.728116499974293</v>
+        <v>2.720406986399904</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057526</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.846215039481345</v>
+        <v>-5.580716450363644</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6252189229973775</v>
+        <v>0.7314183586444578</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.3893310362471434</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.738172254929766</v>
+        <v>2.730462741355377</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279183</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.596364645532271</v>
+        <v>-5.330866056414569</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7179011555607095</v>
+        <v>0.8241005912077899</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.3893310362471434</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.730914329913468</v>
+        <v>2.723204816339079</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011495</v>
+        <v>3.835957987011498</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.420472553064839</v>
+        <v>-5.154973963947137</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7918571160683308</v>
+        <v>0.8980565517154115</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.3893310362471434</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.734513453434117</v>
+        <v>2.726803939859728</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392983</v>
+        <v>3.780933911392986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.249026090042375</v>
+        <v>-4.983527500924674</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8737632073318702</v>
+        <v>0.9799626429789505</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.2050353839340321</v>
+        <v>-0.2178845732246802</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.850708837302149</v>
+        <v>2.84299932372776</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632778</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.174736524304036</v>
+        <v>-4.909237935186335</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9024995112435028</v>
+        <v>1.008698946890583</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.1307458181956928</v>
+        <v>-0.143595007486341</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.894303054361449</v>
+        <v>2.88659354078706</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.111100782070102</v>
+        <v>-4.8456021929524</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9326486091913937</v>
+        <v>1.038848044838474</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.06711007596175828</v>
+        <v>-0.07995926525240643</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.937179300756127</v>
+        <v>2.929469787181738</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074779</v>
+        <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.999674022744181</v>
+        <v>-4.73417543362648</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9584135717055573</v>
+        <v>1.064613007352638</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.06711007596175828</v>
+        <v>-0.07995926525240643</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.918373559539923</v>
+        <v>2.910664045965534</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.79769488424229</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.759243525939321</v>
+        <v>-4.49374493682162</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.056328847052379</v>
+        <v>1.162528282699459</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.173320420843102</v>
+        <v>0.1604712315524539</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.064374934247716</v>
+        <v>3.056665420673327</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.687000957768126</v>
+        <v>-4.421502368650425</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.089155188155677</v>
+        <v>1.195354623802757</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.173320420843102</v>
+        <v>0.1604712315524539</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.068304248082536</v>
+        <v>3.060594734508147</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879961</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.669287270890261</v>
+        <v>-4.40378868177256</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.096919246824163</v>
+        <v>1.203118682471244</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.1765017497400188</v>
+        <v>0.1636525604493707</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.070891629338026</v>
+        <v>3.063182115763638</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502333</v>
+        <v>3.848616626502336</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.560482385410534</v>
+        <v>-4.294983796292833</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.137439272236047</v>
+        <v>1.243638707883128</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.1765017497400188</v>
+        <v>0.1636525604493707</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.06788970055802</v>
+        <v>3.060180186983631</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675933</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.340461587373523</v>
+        <v>-4.074962998255822</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.227026628461466</v>
+        <v>1.333226064108546</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3177215948079991</v>
+        <v>0.3048724055173509</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.154200644609422</v>
+        <v>3.146491131035033</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539945</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.207593898310246</v>
+        <v>-3.942095309192544</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.2960678868886</v>
+        <v>1.402267322535681</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3177215948079991</v>
+        <v>0.3048724055173509</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.170094827411245</v>
+        <v>3.162385313836857</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496258</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.087420814945747</v>
+        <v>-3.821922225828045</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.345282964674702</v>
+        <v>1.451482400321782</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.437894678172498</v>
+        <v>0.4250454888818498</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.243344521870247</v>
+        <v>3.235635008295858</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576995</v>
+        <v>3.791273551576999</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.94274866984601</v>
+        <v>-3.677250080728308</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.413239925276036</v>
+        <v>1.519439360923117</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.5825668232722354</v>
+        <v>0.5697176339815873</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.340235911491529</v>
+        <v>3.33252639791714</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.7358392229421</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.002623497203702</v>
+        <v>-3.737124908086</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.375327485734385</v>
+        <v>1.481526921381466</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5226919959145433</v>
+        <v>0.5098428066238951</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.29034850647834</v>
+        <v>3.282638992903951</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674511</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.882803266292865</v>
+        <v>-3.617304677175162</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.438544747332929</v>
+        <v>1.544744182980009</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5226919959145433</v>
+        <v>0.5098428066238951</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.305637675712548</v>
+        <v>3.297928162138159</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430689</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.885272972754671</v>
+        <v>-3.619774383636968</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.345201064070648</v>
+        <v>1.451400499717729</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5202222894527371</v>
+        <v>0.5073731001620889</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.211800051157906</v>
+        <v>3.204090537583517</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003597</v>
+        <v>3.743220196003601</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.95364315907868</v>
+        <v>-3.688144569960978</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.237114851026345</v>
+        <v>1.343314286673426</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.529497988488952</v>
+        <v>0.5166487991983039</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.136627332064936</v>
+        <v>3.128917818490547</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508365</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.967431211925727</v>
+        <v>-3.701932622808025</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.222036338519418</v>
+        <v>1.328235774166499</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.529497988488952</v>
+        <v>0.5166487991983039</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.127064040696828</v>
+        <v>3.119354527122439</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417699</v>
+        <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.022951287818317</v>
+        <v>-3.757452698700614</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.336859144854585</v>
+        <v>1.443058580501665</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.529497988488952</v>
+        <v>0.5166487991983039</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.26409487738903</v>
+        <v>3.256385363814641</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205894</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.847477028025847</v>
+        <v>-3.581978438908145</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.41161608076336</v>
+        <v>1.517815516410441</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.529497988488952</v>
+        <v>0.5166487991983039</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.268662109380818</v>
+        <v>3.260952595806429</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225439</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.958413280667096</v>
+        <v>-3.692914691549394</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.342983608468068</v>
+        <v>1.449183044115149</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.529497988488952</v>
+        <v>0.5166487991983039</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.244404138142025</v>
+        <v>3.236694624567636</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111295</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.924749735194814</v>
+        <v>-3.659251146077112</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.28498734005843</v>
+        <v>1.391186775705511</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5631615339612339</v>
+        <v>0.5503123446705858</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.193140578826844</v>
+        <v>3.185431065252455</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.864897115991091</v>
+        <v>-3.599398526873389</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.319100774172052</v>
+        <v>1.425300209819133</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5631615339612339</v>
+        <v>0.5503123446705858</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.203312965258976</v>
+        <v>3.195603451684587</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.778653652964714</v>
+        <v>-3.513155063847011</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.348544429956463</v>
+        <v>1.454743865603544</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5631615339612339</v>
+        <v>0.5503123446705858</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.198259235832837</v>
+        <v>3.190549722258448</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.823960472363694</v>
+        <v>-3.558461883245991</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.322197477641397</v>
+        <v>1.428396913288478</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5223513709520031</v>
+        <v>0.509502181661355</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.165548913471823</v>
+        <v>3.157839399897434</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.852993577065995</v>
+        <v>-3.587494987948293</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.311136108793578</v>
+        <v>1.417335544440658</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5223513709520031</v>
+        <v>0.509502181661355</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.166100786504925</v>
+        <v>3.158391272930536</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.760183095615136</v>
+        <v>-3.494684506497434</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.277532993265287</v>
+        <v>1.383732428912368</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6151618524028625</v>
+        <v>0.6023126631122143</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.151059767266806</v>
+        <v>3.143350253692417</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.804572564944563</v>
+        <v>-3.539073975826861</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.261650681458117</v>
+        <v>1.367850117105198</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.5707723830734348</v>
+        <v>0.5579231937827867</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.126299561593751</v>
+        <v>3.118590048019362</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.691901346708313</v>
+        <v>-3.426402757590611</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.30179487726434</v>
+        <v>1.407994312911421</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.683443601309685</v>
+        <v>0.6705944120190368</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.188978001047224</v>
+        <v>3.181268487472835</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.579524345525641</v>
+        <v>-3.314025756407939</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.352236973568076</v>
+        <v>1.458436409215157</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.683443601309685</v>
+        <v>0.6705944120190368</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.194469296877891</v>
+        <v>3.186759783303502</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.607304743426994</v>
+        <v>-3.341806154309292</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.352622016176074</v>
+        <v>1.458821451823155</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6556632034083318</v>
+        <v>0.6428140141176837</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.189298259905618</v>
+        <v>3.181588746331229</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705323</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.725685416157132</v>
+        <v>-3.46018682703943</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.143625467084672</v>
+        <v>1.249824902731753</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5884453512573556</v>
+        <v>0.5755961619667075</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.987323268615686</v>
+        <v>2.979613755041297</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729267</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.834299494600463</v>
+        <v>-3.568800905482761</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.220329496426545</v>
+        <v>1.326528932073626</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5884453512573556</v>
+        <v>0.5755961619667075</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.107472929334891</v>
+        <v>3.099763415760502</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.79889045635232</v>
+        <v>-3.533391867234618</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.249006137828125</v>
+        <v>1.355205573475206</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5884453512573556</v>
+        <v>0.5755961619667075</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.121985955437214</v>
+        <v>3.114276441862825</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.760506793794169</v>
+        <v>-3.495008204676467</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.261779044193754</v>
+        <v>1.367978479840835</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6268290138155068</v>
+        <v>0.6139798245248587</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.142435594314474</v>
+        <v>3.134726080740085</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.583390463759003</v>
+        <v>-3.317891874641301</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.329354605053123</v>
+        <v>1.435554040700203</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6268290138155068</v>
+        <v>0.6139798245248587</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.139164623159775</v>
+        <v>3.131455109585386</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.628482708592549</v>
+        <v>-3.362984119474847</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.312001098881617</v>
+        <v>1.418200534528698</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.564932970646117</v>
+        <v>0.5520837813554689</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.102710389020055</v>
+        <v>3.095000875445666</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.449107287353781</v>
+        <v>-3.183608698236079</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.377538242683539</v>
+        <v>1.48373767833062</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7217097288168357</v>
+        <v>0.7088605395261875</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.190563419228901</v>
+        <v>3.182853905654512</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.494121500874388</v>
+        <v>-3.228622911756685</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.340340012606886</v>
+        <v>1.446539448253967</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6913608335022311</v>
+        <v>0.6785116442115829</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.153161537371727</v>
+        <v>3.145452023797338</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.761126011146823</v>
+        <v>-3.495627422029121</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.239229770836858</v>
+        <v>1.345429206483939</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4969977954592826</v>
+        <v>0.4841486061686344</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.042235276884904</v>
+        <v>3.034525763310515</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760811</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.862323792583996</v>
+        <v>-3.596825203466294</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.19795458015849</v>
+        <v>1.304154015805571</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4285889819139634</v>
+        <v>0.4157397926233152</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.000393910654214</v>
+        <v>2.992684397079825</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815458</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.855812825969683</v>
+        <v>-3.590314236851981</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.198158928358532</v>
+        <v>1.304358364005613</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4285889819139634</v>
+        <v>0.4157397926233152</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.99799387220853</v>
+        <v>2.990284358634141</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378103</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.836774698262386</v>
+        <v>-3.571276109144684</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.202298898649696</v>
+        <v>1.308498334296776</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3704053705827688</v>
+        <v>0.3575561812921206</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.959608424618059</v>
+        <v>2.95189891104367</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131249</v>
+        <v>3.731064473131252</v>
       </c>
       <c r="C1963" t="n">
         <v>2.914947071207078</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.867901329413004</v>
+        <v>-3.602402740295302</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.367430115128129</v>
+        <v>1.47362955077521</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3704053705827688</v>
+        <v>0.3575561812921206</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.137190293556739</v>
+        <v>3.12948077998235</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067867</v>
       </c>
       <c r="C1964" t="n">
         <v>2.915780400193211</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.881768090746921</v>
+        <v>-3.616269501629219</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.362716739580696</v>
+        <v>1.468916175227776</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3325474538489459</v>
+        <v>0.3196982645582977</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.115308872502579</v>
+        <v>3.10759935892819</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789124</v>
       </c>
       <c r="C1965" t="n">
         <v>2.921788930590137</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.836963919206991</v>
+        <v>-3.571465330089289</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.386646938593593</v>
+        <v>1.492846374240674</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3325474538489459</v>
+        <v>0.3196982645582977</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.121317402899505</v>
+        <v>3.113607889325116</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519911</v>
       </c>
       <c r="C1966" t="n">
         <v>2.819739151867337</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.689220948971989</v>
+        <v>-3.423722359854287</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.343694347964794</v>
+        <v>1.449893783611875</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5003548110838291</v>
+        <v>0.4875056217931809</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.119952038517634</v>
+        <v>3.112242524943245</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181172</v>
       </c>
       <c r="C1967" t="n">
         <v>2.822532773398818</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.79123563150321</v>
+        <v>-3.525737042385508</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.305682096483786</v>
+        <v>1.411881532130867</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5003548110838291</v>
+        <v>0.4875056217931809</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.122745660049115</v>
+        <v>3.115036146474726</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394729</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.823195121790476</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.785082925450426</v>
+        <v>-3.519584336332723</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.308805527296558</v>
+        <v>1.415004962943639</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5065075171366133</v>
+        <v>0.4936583278459652</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.127099632072444</v>
+        <v>3.119390118498055</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.822275598530586</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.801892223600927</v>
+        <v>-3.536393634483225</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.301162284776468</v>
+        <v>1.407361720423549</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4896982189861117</v>
+        <v>0.4768490296954636</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.116094529922254</v>
+        <v>3.108385016347865</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>2.888611152327407</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.739594224824805</v>
+        <v>-3.474095635707103</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.392417038083738</v>
+        <v>1.498616473730819</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4896982189861117</v>
+        <v>0.4768490296954636</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.182430083719074</v>
+        <v>3.174720570144685</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
         <v>2.690903154041534</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.537804027159647</v>
+        <v>-3.272305438041945</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.275425118863928</v>
+        <v>1.381624554511009</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.687716411155266</v>
+        <v>0.6748672218646179</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.103533000734694</v>
+        <v>3.095823487160305</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
         <v>2.761193386363709</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.588690739845842</v>
+        <v>-3.32319215072814</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.325360666111625</v>
+        <v>1.431560101758706</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.6368296984690716</v>
+        <v>0.6239805091784234</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.143291205445153</v>
+        <v>3.135581691870764</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
         <v>2.775821122479753</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.686431284470816</v>
+        <v>-3.420932695353114</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.300892184377679</v>
+        <v>1.40709162002476</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6209404203360913</v>
+        <v>0.6080912310454432</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.148385374681408</v>
+        <v>3.140675861107019</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
         <v>2.774357103304425</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.862769044593746</v>
+        <v>-3.597270455476044</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.228893061153179</v>
+        <v>1.33509249680026</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.4446026602131619</v>
+        <v>0.4317534709225138</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.041118699432322</v>
+        <v>3.033409185857933</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
         <v>2.772848721344353</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.786346998161819</v>
+        <v>-3.520848409044117</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.257953497765878</v>
+        <v>1.364152933412959</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.4446026602131619</v>
+        <v>0.4317534709225138</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.039610317472251</v>
+        <v>3.031900803897862</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
         <v>2.77271158877979</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.74197386652325</v>
+        <v>-3.476475277405548</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.275565617856742</v>
+        <v>1.381765053503823</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.4889757918517306</v>
+        <v>0.4761266025610824</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.066097063890828</v>
+        <v>3.058387550316439</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105968</v>
       </c>
       <c r="C1977" t="n">
         <v>2.76710538291838</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.619139645636083</v>
+        <v>-3.353641056518381</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.3190931003502</v>
+        <v>1.425292535997281</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.4889757918517306</v>
+        <v>0.4761266025610824</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.060490858029419</v>
+        <v>3.05278134445503</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190326</v>
       </c>
       <c r="C1978" t="n">
         <v>2.773487139946185</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.571483915075027</v>
+        <v>-3.305985325957325</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.344537149602427</v>
+        <v>1.450736585249508</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.5366315224127862</v>
+        <v>0.5237823331221381</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.095466053393856</v>
+        <v>3.087756539819468</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
         <v>2.778379513320909</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.470965756576272</v>
+        <v>-3.20546716745857</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.389636786376653</v>
+        <v>1.495836222023734</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.6371496809115408</v>
+        <v>0.6243004916208926</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.160669321867834</v>
+        <v>3.152959808293445</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557292</v>
+        <v>3.828808877557294</v>
       </c>
       <c r="C1980" t="n">
         <v>2.765134185796782</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.531632346978661</v>
+        <v>-3.266133757860959</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.35212482269157</v>
+        <v>1.458324258338651</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.5554513641930071</v>
+        <v>0.542602174902359</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.098405004312586</v>
+        <v>3.090695490738197</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
         <v>2.76923188840741</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.486793945370263</v>
+        <v>-3.221295356252561</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.374157885945558</v>
+        <v>1.480357321592638</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.5599947971378766</v>
+        <v>0.5471456078472284</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.105228766690137</v>
+        <v>3.097519253115748</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
         <v>2.773392828038488</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.506292401612272</v>
+        <v>-3.240793812494569</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.370519443079832</v>
+        <v>1.476718878726913</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5119101558579723</v>
+        <v>0.4990609665673241</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.080538921553272</v>
+        <v>3.072829407978883</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
         <v>2.779272430566325</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.462089564526371</v>
+        <v>-3.196590975408669</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.39408018044203</v>
+        <v>1.500279616089111</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.5561129929438727</v>
+        <v>0.5432638036532246</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.11294022633265</v>
+        <v>3.105230712758261</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.777682431035573</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.499068592189814</v>
+        <v>-3.233570003072112</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.3776985698459</v>
+        <v>1.483898005492981</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.5930868947352033</v>
+        <v>0.5802377054445551</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.133534567876695</v>
+        <v>3.125825054302307</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.828930196218613</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.340777174650542</v>
+        <v>-3.07527858553284</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.492262902044649</v>
+        <v>1.598462337691729</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.5930868947352033</v>
+        <v>0.5802377054445551</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.184782333059735</v>
+        <v>3.177072819485346</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
         <v>2.827370900812866</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.133135171016066</v>
+        <v>-2.867636581898364</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.573760408092692</v>
+        <v>1.679959843739773</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.8007288983696794</v>
+        <v>0.7878797090790313</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.307808239834674</v>
+        <v>3.300098726260285</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475138</v>
       </c>
       <c r="C1987" t="n">
         <v>2.822319129051136</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.082103078293538</v>
+        <v>-2.816604489175836</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.589121473419973</v>
+        <v>1.695320909067054</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.8517609910922074</v>
+        <v>0.8389118018015592</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.33337572370646</v>
+        <v>3.325666210132072</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
         <v>2.839506533143841</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.016878897166333</v>
+        <v>-2.75138030804863</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.63239854996356</v>
+        <v>1.738597985610641</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.916985172219413</v>
+        <v>0.9041359829287648</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.389697636475489</v>
+        <v>3.3819881229011</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882555</v>
+        <v>3.840061186882557</v>
       </c>
       <c r="C1989" t="n">
         <v>2.835467505443121</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.979451877095199</v>
+        <v>-2.713953287977497</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.643330330291294</v>
+        <v>1.749529765938375</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.9222367102485947</v>
+        <v>0.9093875209579465</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.388809531592278</v>
+        <v>3.381100018017889</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992658</v>
+        <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
         <v>2.836724297774361</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.999563533129907</v>
+        <v>-2.734064944012205</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.636542460208651</v>
+        <v>1.742741895855732</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.9332640552460139</v>
+        <v>0.9204148659553657</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.39668273092197</v>
+        <v>3.388973217347581</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636285</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.997282068795572</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.945818718702702</v>
+        <v>-2.680320129585</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.818598157000744</v>
+        <v>1.924797592647825</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9433273646864758</v>
+        <v>0.9304781753958277</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.563278487607458</v>
+        <v>3.555568974033069</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957623</v>
+        <v>3.813222820957625</v>
       </c>
       <c r="C1992" t="n">
         <v>3.117394978013389</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.87103645767769</v>
+        <v>-2.605537868559987</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.968623970628566</v>
+        <v>2.074823406275647</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.018109625711488</v>
+        <v>1.00526043642084</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.728260753440283</v>
+        <v>3.720551239865894</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998754</v>
+        <v>3.814230727998756</v>
       </c>
       <c r="C1993" t="n">
         <v>3.109102954027248</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.844952373413882</v>
+        <v>-2.57945378429618</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.970765580347948</v>
+        <v>2.076965015995029</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.018109625711488</v>
+        <v>1.00526043642084</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.719968729454142</v>
+        <v>3.712259215879753</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896929</v>
       </c>
       <c r="C1994" t="n">
         <v>3.107296149611028</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.766821192564935</v>
+        <v>-2.501322603447233</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.000211248271307</v>
+        <v>2.106410683918388</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.092286436595173</v>
+        <v>1.079437247304525</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.762668011568132</v>
+        <v>3.754958497993743</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
         <v>3.124850555337819</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.757928731171652</v>
+        <v>-2.49243014205395</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.021322638555411</v>
+        <v>2.127522074202492</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.092286436595173</v>
+        <v>1.079437247304525</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.780222417294923</v>
+        <v>3.772512903720534</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>3.116705602742403</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.92640484814153</v>
+        <v>-2.660906259023827</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.945787239172044</v>
+        <v>2.051986674819125</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.064338600878592</v>
+        <v>1.051489411587944</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.755308763269559</v>
+        <v>3.74759924969517</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>3.097975299930265</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.228605319279946</v>
+        <v>-1.963106730162244</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.206176747904539</v>
+        <v>2.31237618355162</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.9939905415081816</v>
+        <v>0.9811413522175334</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.694369624835174</v>
+        <v>3.686660111260785</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632634</v>
+        <v>3.784671345632636</v>
       </c>
       <c r="C1998" t="n">
         <v>3.08863932242717</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.205884215596794</v>
+        <v>-1.940385626479092</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.205929211874705</v>
+        <v>2.312128647521785</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.9939905415081816</v>
+        <v>0.9811413522175334</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.685033647332079</v>
+        <v>3.67732413375769</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777671</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>3.247545448278339</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.335086028890836</v>
+        <v>-2.069587439773134</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.313154612408257</v>
+        <v>2.419354048055338</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.8647887282141393</v>
+        <v>0.8519395389234912</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.766418685206823</v>
+        <v>3.758709171632434</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.77993372564441</v>
+        <v>3.779933725644412</v>
       </c>
       <c r="C2000" t="n">
         <v>3.284623270771985</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.489867035669092</v>
+        <v>-2.22436844655139</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.288320032190601</v>
+        <v>2.394519467837682</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.8314210541596632</v>
+        <v>0.818571864869015</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.783475903267783</v>
+        <v>3.775766389693394</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799962</v>
+        <v>3.769443619799964</v>
       </c>
       <c r="C2001" t="n">
         <v>3.28129862676153</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.482812345453918</v>
+        <v>-2.217313756336216</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.287817264266216</v>
+        <v>2.394016699913297</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.838475744374837</v>
+        <v>0.8256265550841888</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.784384073386433</v>
+        <v>3.776674559812044</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331115</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
         <v>3.291304780406272</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.45586112112743</v>
+        <v>-2.190362532009728</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.308603907641552</v>
+        <v>2.414803343288633</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.8533560904025561</v>
+        <v>0.840506901111908</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.803318434647806</v>
+        <v>3.795608921073417</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
         <v>3.475407912551232</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.591814129183747</v>
+        <v>-2.326315540066044</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.438325836563986</v>
+        <v>2.544525272211067</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.8533560904025561</v>
+        <v>0.840506901111908</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.987421566792765</v>
+        <v>3.979712053218377</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714427</v>
       </c>
       <c r="C2004" t="n">
         <v>3.467524607454225</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.614222246988619</v>
+        <v>-2.348723657870917</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.42147928434503</v>
+        <v>2.527678719992111</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.8533560904025561</v>
+        <v>0.840506901111908</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.979538261695758</v>
+        <v>3.97182874812137</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155031</v>
+        <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
         <v>3.469578607003862</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.762228014468018</v>
+        <v>-2.496729425350316</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.364330976902908</v>
+        <v>2.470530412549989</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.7666290815390147</v>
+        <v>0.7537798922483665</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.929556055927272</v>
+        <v>3.921846542352882</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161976</v>
+        <v>3.729452285161978</v>
       </c>
       <c r="C2006" t="n">
         <v>3.525832324725709</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.771668940356548</v>
+        <v>-2.506170351238846</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.416808324269343</v>
+        <v>2.523007759916424</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.8890561990824061</v>
+        <v>0.8762070097917579</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.059266044175153</v>
+        <v>4.051556530600764</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321633</v>
+        <v>3.714941193321635</v>
       </c>
       <c r="C2007" t="n">
         <v>3.52872341927101</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.82394254769219</v>
+        <v>-2.558443958574487</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.398789975880387</v>
+        <v>2.504989411527468</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.8367825917467648</v>
+        <v>0.8239334024561167</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.03079297431907</v>
+        <v>4.02308346074468</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
         <v>3.526835232164785</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.900272525293095</v>
+        <v>-2.634773936175393</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.3663697977338</v>
+        <v>2.472569233380881</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.8367825917467648</v>
+        <v>0.8239334024561167</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.028904787212845</v>
+        <v>4.021195273638456</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
         <v>3.521655461767648</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.012029477908396</v>
+        <v>-2.746530888790694</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.316487246290542</v>
+        <v>2.422686681937622</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.7250256391314638</v>
+        <v>0.7121764498408156</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.956670845246526</v>
+        <v>3.948961331672137</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343064</v>
+        <v>3.712897612343066</v>
       </c>
       <c r="C2010" t="n">
         <v>3.5200894719778</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.010188458850145</v>
+        <v>-2.744689869732443</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.315657664123995</v>
+        <v>2.421857099771076</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7262938658029322</v>
+        <v>0.713444676512284</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.955865791459559</v>
+        <v>3.948156277885171</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647104</v>
+        <v>3.754911907647106</v>
       </c>
       <c r="C2011" t="n">
         <v>3.533162878843719</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.142489750947699</v>
+        <v>-2.876991161829996</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.275810554150892</v>
+        <v>2.382009989797973</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7262938658029322</v>
+        <v>0.713444676512284</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.968939198325478</v>
+        <v>3.961229684751089</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763531</v>
+        <v>3.749896851763533</v>
       </c>
       <c r="C2012" t="n">
         <v>3.533162878843719</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.144051393762559</v>
+        <v>-2.878552804644857</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.275185897024948</v>
+        <v>2.381385332672028</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7262938658029322</v>
+        <v>0.713444676512284</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.968939198325478</v>
+        <v>3.961229684751089</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392115</v>
+        <v>3.715834055392117</v>
       </c>
       <c r="C2013" t="n">
         <v>3.531686919970721</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.171952180872032</v>
+        <v>-2.906453591754329</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.262549623308161</v>
+        <v>2.368749058955242</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6916969416599974</v>
+        <v>0.6788477523693492</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.94670508496672</v>
+        <v>3.93899557139233</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172526</v>
+        <v>3.684909939172528</v>
       </c>
       <c r="C2014" t="n">
         <v>3.528451363947919</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.294478283574926</v>
+        <v>-3.028979694457223</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.210303626204202</v>
+        <v>2.316503061851283</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5691708389571035</v>
+        <v>0.5563216496664554</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.869953867322182</v>
+        <v>3.862244353747793</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971077</v>
+        <v>3.619362241971079</v>
       </c>
       <c r="C2015" t="n">
         <v>3.595157323538423</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.314539604851432</v>
+        <v>-3.04904101573373</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.268985057284103</v>
+        <v>2.375184492931184</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5491095176805965</v>
+        <v>0.5362603283899483</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.924623034146781</v>
+        <v>3.916913520572392</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199805</v>
+        <v>3.640764248199806</v>
       </c>
       <c r="C2016" t="n">
         <v>3.73546904254027</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.571260422846256</v>
+        <v>-3.305761833728554</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.30660844908802</v>
+        <v>2.412807884735101</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4406949435367816</v>
+        <v>0.4278457542461335</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.999886008662339</v>
+        <v>3.992176495087951</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622235</v>
+        <v>3.668303164622237</v>
       </c>
       <c r="C2017" t="n">
         <v>3.80444931168591</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.725246840622397</v>
+        <v>-3.459748251504695</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.313994151123204</v>
+        <v>2.420193586770285</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4406949435367816</v>
+        <v>0.4278457542461335</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.068866277807979</v>
+        <v>4.061156764233591</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808527</v>
+        <v>3.619937176808529</v>
       </c>
       <c r="C2018" t="n">
         <v>3.790500513806031</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.674724936794731</v>
+        <v>-3.409226347677029</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.320254114774391</v>
+        <v>2.426453550421472</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.4406949435367816</v>
+        <v>0.4278457542461335</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.0549174799281</v>
+        <v>4.047207966353711</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994892</v>
+        <v>3.656346893994894</v>
       </c>
       <c r="C2019" t="n">
         <v>3.802371002861445</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.927200090802455</v>
+        <v>-3.661701501684753</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.231134542226715</v>
+        <v>2.337333977873796</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.4406949435367816</v>
+        <v>0.4278457542461335</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.066787968983514</v>
+        <v>4.059078455409125</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358297</v>
+        <v>3.674042696358299</v>
       </c>
       <c r="C2020" t="n">
         <v>3.803581537380389</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.196672892724163</v>
+        <v>-3.931174303606461</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.124555955976976</v>
+        <v>2.230755391624057</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.4406949435367816</v>
+        <v>0.4278457542461335</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.067998503502458</v>
+        <v>4.060288989928069</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637085</v>
+        <v>3.663523617637087</v>
       </c>
       <c r="C2021" t="n">
         <v>3.80770327960771</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.354216964453605</v>
+        <v>-4.088718375335903</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.06566006951252</v>
+        <v>2.171859505159602</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.3737931383965071</v>
+        <v>0.360943949105859</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.031979162645614</v>
+        <v>4.024269649071226</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301342</v>
+        <v>3.652163313301343</v>
       </c>
       <c r="C2022" t="n">
         <v>3.802781132343899</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.632181360036879</v>
+        <v>-4.366682770919176</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.949552164015401</v>
+        <v>2.055751599662481</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.2841734041110229</v>
+        <v>0.2713242148203747</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.973285174810513</v>
+        <v>3.965575661236125</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215468</v>
+        <v>3.667976467215469</v>
       </c>
       <c r="C2023" t="n">
         <v>3.964985189042944</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.74914905267577</v>
+        <v>-4.483650463558067</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.064969143658888</v>
+        <v>2.171168579305969</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.2841734041110229</v>
+        <v>0.2713242148203747</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.135489231509558</v>
+        <v>4.127779717935169</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456691</v>
+        <v>3.696553628456692</v>
       </c>
       <c r="C2024" t="n">
         <v>3.959831827006758</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.833866994896723</v>
+        <v>-4.568368405779021</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.025928604734321</v>
+        <v>2.132128040381402</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1990573751829765</v>
+        <v>0.1862081858923283</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.079266252116544</v>
+        <v>4.071556738542155</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253287</v>
+        <v>3.750058176253288</v>
       </c>
       <c r="C2025" t="n">
         <v>3.970061244575249</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.915801813165606</v>
+        <v>-4.650303224047904</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.003384094995259</v>
+        <v>2.10958353064234</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.1891226295958963</v>
+        <v>0.1762734403052482</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.083534822332787</v>
+        <v>4.075825308758398</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717831</v>
+        <v>3.783647027717832</v>
       </c>
       <c r="C2026" t="n">
         <v>3.978986883031151</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.862063639765344</v>
+        <v>-4.596565050647642</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.033805002811266</v>
+        <v>2.140004438458347</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.2428608029961584</v>
+        <v>0.2300116137055103</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.124703364828846</v>
+        <v>4.116993851254458</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616948</v>
+        <v>3.798310944616949</v>
       </c>
       <c r="C2027" t="n">
         <v>3.971139770275327</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.752057356288122</v>
+        <v>-4.48655876717042</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.069960403446331</v>
+        <v>2.176159839093412</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.2660653749134336</v>
+        <v>0.2532161856227855</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.130778995223388</v>
+        <v>4.123069481648999</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203663</v>
+        <v>3.785578085203664</v>
       </c>
       <c r="C2028" t="n">
         <v>3.975389780997301</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.608997780547197</v>
+        <v>-4.343499191429494</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.131434244464675</v>
+        <v>2.237633680111756</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.2740788015034129</v>
+        <v>0.2612296122127648</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.13983706189935</v>
+        <v>4.13212754832496</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436929</v>
+        <v>3.77725157243693</v>
       </c>
       <c r="C2029" t="n">
         <v>3.982650663879838</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.30755105507536</v>
+        <v>-4.042052465957656</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.259273817535947</v>
+        <v>2.365473253183028</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.5755255269752502</v>
+        <v>0.562676337684602</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.327965980064988</v>
+        <v>4.3202564664906</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.983621841632548</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.362506251518429</v>
+        <v>-4.097007662400726</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.238262916711429</v>
+        <v>2.34446235235851</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.5755255269752502</v>
+        <v>0.562676337684602</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.328937157817698</v>
+        <v>4.32122764424331</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.984464746012303</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.311467875511909</v>
+        <v>-4.045969286394206</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.259521171493793</v>
+        <v>2.365720607140874</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.5755255269752502</v>
+        <v>0.562676337684602</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.329780062197454</v>
+        <v>4.322070548623065</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>4.003502844886449</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.270328580645278</v>
+        <v>-4.004829991527575</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.29501498831459</v>
+        <v>2.401214423961672</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.616664821841881</v>
+        <v>0.6038156325512328</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.373501737991578</v>
+        <v>4.365792224417189</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.526103024090933</v>
+        <v>3.853557307023419</v>
       </c>
       <c r="C2033" t="n">
         <v>3.819686841010383</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.159722440565676</v>
+        <v>-3.894223851447973</v>
       </c>
       <c r="E2033" t="n">
-        <v>2.155441440470366</v>
+        <v>2.261640876117447</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.727270961921483</v>
+        <v>0.7144217726308348</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.256049418163274</v>
+        <v>4.248339904588884</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240723.xlsx
+++ b/tame_output/ON/bt/strategyON_20240723.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>24.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>84.3%</t>
+          <t>76.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,37 +844,37 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>47.9%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.9%</t>
+          <t>-75.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.9%</t>
+          <t>108.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.6%</t>
+          <t>124.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.8%</t>
+          <t>91.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.2%</t>
+          <t>-71.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.0%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>456.5%</t>
+          <t>452.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-551.0%</t>
+          <t>-573.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.5%</t>
+          <t>-34.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-44.3%</t>
+          <t>-45.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-150.1%</t>
+          <t>-159.1%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-120.2%</t>
+          <t>-123.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-152.6%</t>
+          <t>-151.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>75.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.3%</t>
+          <t>-23.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>76.0%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-21.2%</t>
+          <t>-87.1%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2033"/>
+  <dimension ref="A1:G2034"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.471830951507869</v>
+        <v>-7.477989729264485</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.1280733499056983</v>
+        <v>0.1256098388030513</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.171133866027758</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.414481835205938</v>
+        <v>2.422191348780327</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392308</v>
+        <v>3.419979433923081</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.658550659817172</v>
+        <v>-7.664709437573788</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.04935916204757396</v>
+        <v>0.04689565094492743</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.171133866027758</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.410455530671535</v>
+        <v>2.418165044245924</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297743</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.041552048559803</v>
+        <v>-8.047710826316418</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.1039434947710625</v>
+        <v>-0.106407005873709</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.171133866027758</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.410353429349951</v>
+        <v>2.41806294292434</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131761</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.046038493761191</v>
+        <v>-8.052197271517807</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.1031665568801881</v>
+        <v>-0.1056300679828341</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.175620311229147</v>
+        <v>-1.162771121938499</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.410233078200548</v>
+        <v>2.417942591774937</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737164</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.405568816265193</v>
+        <v>-8.411727594021809</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.2416283825837384</v>
+        <v>-0.2440918936863845</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.175620311229147</v>
+        <v>-1.162771121938499</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.415583381498598</v>
+        <v>2.423292895072987</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.455917879719415</v>
+        <v>-8.462076657476031</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.2538519880082499</v>
+        <v>-0.256315499110896</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.225969374683369</v>
+        <v>-1.213120185392721</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.393289963383242</v>
+        <v>2.400999476957631</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539458</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.553537157140811</v>
+        <v>-8.559695934897427</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.2898579483550394</v>
+        <v>-0.2923214594576855</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.323588652104766</v>
+        <v>-1.310739462814118</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.337760147552173</v>
+        <v>2.345469661126562</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.60760865664917</v>
+        <v>-8.613767434405785</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.3085929918368104</v>
+        <v>-0.311056502939457</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.377660151613125</v>
+        <v>-1.364810962322477</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.30821080416873</v>
+        <v>2.315920317743119</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.811866831979033</v>
+        <v>-8.818025609735649</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3847830648501138</v>
+        <v>-0.3872465759527599</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.505299096227114</v>
+        <v>-1.492449906936466</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.237140634518979</v>
+        <v>2.244850148093368</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.845519670487507</v>
+        <v>-8.851678448244122</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3937616457690671</v>
+        <v>-0.3962251568717132</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.605712464144152</v>
+        <v>-1.592863274853503</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.181375168253192</v>
+        <v>2.189084681827581</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.772049838820058</v>
+        <v>-8.778208616576674</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.3490020116086665</v>
+        <v>-0.3514655227113126</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.532242632476703</v>
+        <v>-1.519393443186055</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.240828768747082</v>
+        <v>2.248538282321471</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.947174256206601</v>
+        <v>-8.953333033963217</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.4044965578157669</v>
+        <v>-0.406960068918413</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.707367049863247</v>
+        <v>-1.694517860572599</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.150309339062673</v>
+        <v>2.158018852637062</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.181626350221091</v>
+        <v>-9.187785127977707</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.5054965603231589</v>
+        <v>-0.507960071425805</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.707367049863247</v>
+        <v>-1.694517860572599</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.143090174161077</v>
+        <v>2.150799687735466</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.286001081247537</v>
+        <v>-9.292159859004153</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5539186435077137</v>
+        <v>-0.5563821546103598</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.811741780889693</v>
+        <v>-1.798892591599045</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.073793144771233</v>
+        <v>2.081502658345622</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.338787236847864</v>
+        <v>-9.34494601460448</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5739173159092879</v>
+        <v>-0.5763808270119339</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.90741726747209</v>
+        <v>-1.894568078181442</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.017503642660351</v>
+        <v>2.025213156234741</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.464824030216153</v>
+        <v>-9.470982807972769</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6216383046274889</v>
+        <v>-0.624101815730135</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.882165644662348</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.035348344975311</v>
+        <v>2.0430578585497</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.407752258320222</v>
+        <v>-9.413911036076838</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5948192601827156</v>
+        <v>-0.5972827712853621</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.882165644662348</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.039338680661713</v>
+        <v>2.047048194236101</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.549424100044343</v>
+        <v>-9.555582877800958</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6529632237711054</v>
+        <v>-0.6554267348737519</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.882165644662348</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.037863453762971</v>
+        <v>2.045572967337359</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.499833255619508</v>
+        <v>-9.505992033376124</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6180734758362996</v>
+        <v>-0.6205369869389457</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.832574800237514</v>
+        <v>-1.819725610946866</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.082671370582744</v>
+        <v>2.090380884157132</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.350914921147652</v>
+        <v>-9.357073698904268</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5715572756942398</v>
+        <v>-0.5740207867968863</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.801325209502341</v>
+        <v>-1.788476020211692</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.088369991377164</v>
+        <v>2.096079504951553</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.12506976842824</v>
+        <v>-9.131228546184857</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4716401415702665</v>
+        <v>-0.4741036526729134</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.759398533915177</v>
+        <v>-1.746549344624529</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.123105069765671</v>
+        <v>2.13081458334006</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.000491112090648</v>
+        <v>-9.006649889847266</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4206695344791709</v>
+        <v>-0.4231330455818179</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.759398533915177</v>
+        <v>-1.746549344624529</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.12424421432173</v>
+        <v>2.131953727896119</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.053386400134935</v>
+        <v>-9.059545177891552</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.439193875534778</v>
+        <v>-0.4416573866374249</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.754443187826731</v>
+        <v>-1.741593998536083</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.129851196136905</v>
+        <v>2.137560709711294</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.981253224847054</v>
+        <v>-8.987412002603671</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.4046069011809887</v>
+        <v>-0.4070704122836357</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.754443187826731</v>
+        <v>-1.741593998536083</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.135584900375542</v>
+        <v>2.14329441394993</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.909886832237406</v>
+        <v>-8.916045609994024</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3857976065309954</v>
+        <v>-0.3882611176336423</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.683076795217083</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.168667473547465</v>
+        <v>2.176376987121854</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.816427798252182</v>
+        <v>-8.822586576008799</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3582974742498131</v>
+        <v>-0.36076098535246</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.683076795217083</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.158783992234558</v>
+        <v>2.166493505808947</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.549185997383784</v>
+        <v>-8.555344775140401</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2532353144018278</v>
+        <v>-0.2556988255044748</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.683076795217083</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.156949431735184</v>
+        <v>2.164658945309573</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.451278958707293</v>
+        <v>-8.457437736463911</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2143728139046921</v>
+        <v>-0.2168363250073391</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.615091045356527</v>
+        <v>-1.602241856065878</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.197440566678057</v>
+        <v>2.205150080252446</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.427325417731335</v>
+        <v>-8.433484195487953</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2041228913688156</v>
+        <v>-0.2065864024714625</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.591137504380569</v>
+        <v>-1.578288315089921</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.212481197409125</v>
+        <v>2.220190710983514</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.163265479408539</v>
+        <v>-8.169424257165156</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1117592322014489</v>
+        <v>-0.1142227433040959</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.327077566057773</v>
+        <v>-1.314228376767125</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.357656844241051</v>
+        <v>2.365366357815439</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.4561858559037</v>
+        <v>-7.693220105225982</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1682855835401855</v>
+        <v>0.07347188381127312</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.327077566057773</v>
+        <v>-1.314228376767125</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.35486981058075</v>
+        <v>2.362579324155138</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.41600155753751</v>
+        <v>-7.653035806859791</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1847029267745031</v>
+        <v>0.08988922704559066</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.286893267691582</v>
+        <v>-1.274044078400934</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.379324013488306</v>
+        <v>2.387033527062695</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626472</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.252601686598148</v>
+        <v>-7.489635935920429</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.249429696371005</v>
+        <v>0.1546159966420926</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.123493396752219</v>
+        <v>-1.110644207461571</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.47673075727268</v>
+        <v>2.484440270847069</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291814</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.019120464368549</v>
+        <v>-7.25615471369083</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.350746614100697</v>
+        <v>0.2559329143717841</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8900121745226208</v>
+        <v>-0.8771629852319727</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.624743919448292</v>
+        <v>2.632453433022681</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785789</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.869454073361034</v>
+        <v>-7.106488322683315</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4077209601907437</v>
+        <v>0.3129072604618313</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7971086832800849</v>
+        <v>-0.7842594939894367</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.677593803880854</v>
+        <v>2.685303317455243</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76318224839043</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.737178599730147</v>
+        <v>-6.974212849052429</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4559986363901252</v>
+        <v>0.3611849366612128</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6648332096491982</v>
+        <v>-0.6519840203585501</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.752326574806413</v>
+        <v>2.760036088380802</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105953</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.581440267170406</v>
+        <v>-6.818474516492687</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.521109030101659</v>
+        <v>0.4262953303727461</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.5090948770894567</v>
+        <v>-0.4962456877988085</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.848584635029895</v>
+        <v>2.856294148604284</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.332440468486825</v>
+        <v>-6.569474717809106</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6336152907987498</v>
+        <v>0.5388015910698374</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.5090948770894567</v>
+        <v>-0.4962456877988085</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.861490976253553</v>
+        <v>2.869200489827942</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607645</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.438030458259929</v>
+        <v>-6.67506470758221</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4634033652902896</v>
+        <v>0.3685896655613767</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.6146848668625611</v>
+        <v>-0.6018356775719129</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.670161052790472</v>
+        <v>2.677870566364861</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.456765360378526</v>
+        <v>-6.693799609700807</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5044537463199372</v>
+        <v>0.4096400465910244</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.6202808765226924</v>
+        <v>-0.6074316872320442</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.71534778887148</v>
+        <v>2.723057302445869</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710814</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.308825318970927</v>
+        <v>-6.545859568293208</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4437508401948094</v>
+        <v>0.3489371404658965</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.5999599606141348</v>
+        <v>-0.5871107713234867</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.607661415728447</v>
+        <v>2.615370929302836</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409206</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.255855796716938</v>
+        <v>-6.49289004603922</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4562246628429265</v>
+        <v>0.3614109631140137</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5469904383601459</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.630729142827362</v>
+        <v>2.638438656401751</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098111</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.212307389946248</v>
+        <v>-6.449341639268529</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4666834134561095</v>
+        <v>0.3718697137271967</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5469904383601459</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.623768530732268</v>
+        <v>2.631478044306657</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493422</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.178944183467479</v>
+        <v>-6.41597843278976</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4944910504287598</v>
+        <v>0.3996773506998474</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5469904383601459</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.638230885113412</v>
+        <v>2.645940398687801</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.070685046344957</v>
+        <v>-6.307719295667239</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5323268257369635</v>
+        <v>0.4375131260080511</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5469904383601459</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.632763005572607</v>
+        <v>2.640472519146996</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.947393911527826</v>
+        <v>-6.184428160850108</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5791413736743931</v>
+        <v>0.4843276739454803</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.4236993035430154</v>
+        <v>-0.4108501142523673</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.704235780473462</v>
+        <v>2.711945294047851</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.926244712624383</v>
+        <v>-6.163278961946665</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5953020314730955</v>
+        <v>0.5004883317441831</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.4025501046395721</v>
+        <v>-0.3897009153489239</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.724626278052853</v>
+        <v>2.732335791627242</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318093</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.682479270640939</v>
+        <v>-5.91951351996322</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6885889166135239</v>
+        <v>0.5937752168846115</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.4025501046395721</v>
+        <v>-0.3897009153489239</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.720406986399904</v>
+        <v>2.728116499974293</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057526</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.580716450363644</v>
+        <v>-5.817750699685925</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7314183586444578</v>
+        <v>0.6366046589155454</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.3893310362471434</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.730462741355377</v>
+        <v>2.738172254929766</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.330866056414569</v>
+        <v>-5.567900305736851</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8241005912077899</v>
+        <v>0.7292868914788775</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.3893310362471434</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.723204816339079</v>
+        <v>2.730914329913468</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011498</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.154973963947137</v>
+        <v>-5.392008213269419</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8980565517154115</v>
+        <v>0.8032428519864987</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.3893310362471434</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.726803939859728</v>
+        <v>2.734513453434117</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392986</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.983527500924674</v>
+        <v>-5.220561750246955</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9799626429789505</v>
+        <v>0.8851489432500381</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.2178845732246802</v>
+        <v>-0.2050353839340321</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.84299932372776</v>
+        <v>2.850708837302149</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.77376522263278</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.909237935186335</v>
+        <v>-5.146272184508616</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.008698946890583</v>
+        <v>0.9138852471616707</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.143595007486341</v>
+        <v>-0.1307458181956928</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.88659354078706</v>
+        <v>2.894303054361449</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.8456021929524</v>
+        <v>-5.082636442274682</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.038848044838474</v>
+        <v>0.9440343451095616</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.07995926525240643</v>
+        <v>-0.06711007596175828</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.929469787181738</v>
+        <v>2.937179300756127</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.73417543362648</v>
+        <v>-4.971209682948762</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.064613007352638</v>
+        <v>0.9697993076237252</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.07995926525240643</v>
+        <v>-0.06711007596175828</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.910664045965534</v>
+        <v>2.918373559539923</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.49374493682162</v>
+        <v>-4.730779186143901</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.162528282699459</v>
+        <v>1.067714582970547</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.1604712315524539</v>
+        <v>0.173320420843102</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.056665420673327</v>
+        <v>3.064374934247716</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.821593509367681</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.421502368650425</v>
+        <v>-4.658536617972707</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.195354623802757</v>
+        <v>1.100540924073845</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.1604712315524539</v>
+        <v>0.173320420843102</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.060594734508147</v>
+        <v>3.068304248082536</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879963</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.40378868177256</v>
+        <v>-4.640822931094841</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.203118682471244</v>
+        <v>1.108304982742331</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.1636525604493707</v>
+        <v>0.1765017497400188</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.063182115763638</v>
+        <v>3.070891629338026</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502336</v>
+        <v>3.848616626502335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.294983796292833</v>
+        <v>-4.532018045615114</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.243638707883128</v>
+        <v>1.148825008154215</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.1636525604493707</v>
+        <v>0.1765017497400188</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.060180186983631</v>
+        <v>3.06788970055802</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.074962998255822</v>
+        <v>-4.311997247578104</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.333226064108546</v>
+        <v>1.238412364379634</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3048724055173509</v>
+        <v>0.3177215948079991</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.146491131035033</v>
+        <v>3.154200644609422</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.942095309192544</v>
+        <v>-4.179129558514826</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.402267322535681</v>
+        <v>1.307453622806768</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3048724055173509</v>
+        <v>0.3177215948079991</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.162385313836857</v>
+        <v>3.170094827411245</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.821922225828045</v>
+        <v>-4.058956475150327</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.451482400321782</v>
+        <v>1.356668700592869</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4250454888818498</v>
+        <v>0.437894678172498</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.235635008295858</v>
+        <v>3.243344521870247</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576999</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.677250080728308</v>
+        <v>-3.91428433005059</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.519439360923117</v>
+        <v>1.424625661194204</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.5697176339815873</v>
+        <v>0.5825668232722354</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.33252639791714</v>
+        <v>3.340235911491529</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.737124908086</v>
+        <v>-3.974159157408282</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.481526921381466</v>
+        <v>1.386713221652553</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5098428066238951</v>
+        <v>0.5226919959145433</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.282638992903951</v>
+        <v>3.29034850647834</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.617304677175162</v>
+        <v>-3.854338926497445</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.544744182980009</v>
+        <v>1.449930483251097</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5098428066238951</v>
+        <v>0.5226919959145433</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.297928162138159</v>
+        <v>3.305637675712548</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.619774383636968</v>
+        <v>-3.856808632959251</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.451400499717729</v>
+        <v>1.356586799988816</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5073731001620889</v>
+        <v>0.5202222894527371</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.204090537583517</v>
+        <v>3.211800051157906</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003601</v>
+        <v>3.743220196003599</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.688144569960978</v>
+        <v>-3.925178819283261</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.343314286673426</v>
+        <v>1.248500586944513</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5166487991983039</v>
+        <v>0.529497988488952</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.128917818490547</v>
+        <v>3.136627332064936</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.701932622808025</v>
+        <v>-3.938966872130307</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.328235774166499</v>
+        <v>1.233422074437586</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5166487991983039</v>
+        <v>0.529497988488952</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.119354527122439</v>
+        <v>3.127064040696828</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.757452698700614</v>
+        <v>-3.994486948022897</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.443058580501665</v>
+        <v>1.348244880772753</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5166487991983039</v>
+        <v>0.529497988488952</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.256385363814641</v>
+        <v>3.26409487738903</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.581978438908145</v>
+        <v>-3.819012688230428</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.517815516410441</v>
+        <v>1.423001816681528</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5166487991983039</v>
+        <v>0.529497988488952</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.260952595806429</v>
+        <v>3.268662109380818</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.692914691549394</v>
+        <v>-3.919082016977528</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.449183044115149</v>
+        <v>1.358716113943895</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5166487991983039</v>
+        <v>0.529497988488952</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.236694624567636</v>
+        <v>3.244404138142025</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111295</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.659251146077112</v>
+        <v>-3.885418471505246</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.391186775705511</v>
+        <v>1.300719845534257</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5503123446705858</v>
+        <v>0.5631615339612339</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.185431065252455</v>
+        <v>3.193140578826844</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.599398526873389</v>
+        <v>-3.825565852301523</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.425300209819133</v>
+        <v>1.334833279647879</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5503123446705858</v>
+        <v>0.5631615339612339</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.195603451684587</v>
+        <v>3.203312965258976</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.513155063847011</v>
+        <v>-3.739322389275145</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.454743865603544</v>
+        <v>1.364276935432291</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5503123446705858</v>
+        <v>0.5631615339612339</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.190549722258448</v>
+        <v>3.198259235832837</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.558461883245991</v>
+        <v>-3.784629208674125</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.428396913288478</v>
+        <v>1.337929983117224</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.509502181661355</v>
+        <v>0.5223513709520031</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.157839399897434</v>
+        <v>3.165548913471823</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.587494987948293</v>
+        <v>-3.813662313376426</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.417335544440658</v>
+        <v>1.326868614269405</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.509502181661355</v>
+        <v>0.5223513709520031</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.158391272930536</v>
+        <v>3.166100786504925</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.494684506497434</v>
+        <v>-3.720851831925567</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.383732428912368</v>
+        <v>1.293265498741114</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6023126631122143</v>
+        <v>0.6151618524028625</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.143350253692417</v>
+        <v>3.151059767266806</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.539073975826861</v>
+        <v>-3.765241301254995</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.367850117105198</v>
+        <v>1.277383186933944</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.5579231937827867</v>
+        <v>0.5707723830734348</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.118590048019362</v>
+        <v>3.126299561593751</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.426402757590611</v>
+        <v>-3.652570083018745</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.407994312911421</v>
+        <v>1.317527382740167</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6705944120190368</v>
+        <v>0.683443601309685</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.181268487472835</v>
+        <v>3.188978001047224</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.314025756407939</v>
+        <v>-3.540193081836072</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.458436409215157</v>
+        <v>1.367969479043903</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6705944120190368</v>
+        <v>0.683443601309685</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.186759783303502</v>
+        <v>3.194469296877891</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.341806154309292</v>
+        <v>-3.567973479737425</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.458821451823155</v>
+        <v>1.368354521651901</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6428140141176837</v>
+        <v>0.6556632034083318</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.181588746331229</v>
+        <v>3.189298259905618</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.46018682703943</v>
+        <v>-3.686354152467564</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.249824902731753</v>
+        <v>1.159357972560499</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5755961619667075</v>
+        <v>0.5884453512573556</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.979613755041297</v>
+        <v>2.987323268615686</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.568800905482761</v>
+        <v>-3.794968230910895</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.326528932073626</v>
+        <v>1.236062001902372</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5755961619667075</v>
+        <v>0.5884453512573556</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.099763415760502</v>
+        <v>3.107472929334891</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.533391867234618</v>
+        <v>-3.759559192662752</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.355205573475206</v>
+        <v>1.264738643303952</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5755961619667075</v>
+        <v>0.5884453512573556</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.114276441862825</v>
+        <v>3.121985955437214</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.495008204676467</v>
+        <v>-3.721175530104601</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.367978479840835</v>
+        <v>1.277511549669582</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6139798245248587</v>
+        <v>0.6268290138155068</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.134726080740085</v>
+        <v>3.142435594314474</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.317891874641301</v>
+        <v>-3.544059200069435</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.435554040700203</v>
+        <v>1.34508711052895</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6139798245248587</v>
+        <v>0.6268290138155068</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.131455109585386</v>
+        <v>3.139164623159775</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.362984119474847</v>
+        <v>-3.58915144490298</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.418200534528698</v>
+        <v>1.327733604357445</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5520837813554689</v>
+        <v>0.564932970646117</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.095000875445666</v>
+        <v>3.102710389020055</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.183608698236079</v>
+        <v>-3.409776023664213</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.48373767833062</v>
+        <v>1.393270748159366</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7088605395261875</v>
+        <v>0.7217097288168357</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.182853905654512</v>
+        <v>3.190563419228901</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.228622911756685</v>
+        <v>-3.454790237184819</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.446539448253967</v>
+        <v>1.356072518082714</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6785116442115829</v>
+        <v>0.6913608335022311</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.145452023797338</v>
+        <v>3.153161537371727</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.495627422029121</v>
+        <v>-3.721794747457254</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.345429206483939</v>
+        <v>1.254962276312685</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4841486061686344</v>
+        <v>0.4969977954592826</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.034525763310515</v>
+        <v>3.042235276884904</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760813</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.596825203466294</v>
+        <v>-3.822992528894427</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.304154015805571</v>
+        <v>1.213687085634317</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4157397926233152</v>
+        <v>0.4285889819139634</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.992684397079825</v>
+        <v>3.000393910654214</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815458</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.590314236851981</v>
+        <v>-3.816481562280114</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.304358364005613</v>
+        <v>1.213891433834359</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4157397926233152</v>
+        <v>0.4285889819139634</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.990284358634141</v>
+        <v>2.99799387220853</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378103</v>
+        <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.571276109144684</v>
+        <v>-3.797443434572817</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.308498334296776</v>
+        <v>1.218031404125523</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3575561812921206</v>
+        <v>0.3704053705827688</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.95189891104367</v>
+        <v>2.959608424618059</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131252</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.914947071207078</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.602402740295302</v>
+        <v>-3.828570065723435</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.47362955077521</v>
+        <v>1.383162620603956</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3575561812921206</v>
+        <v>0.3704053705827688</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.12948077998235</v>
+        <v>3.137190293556739</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067867</v>
+        <v>3.722447362067865</v>
       </c>
       <c r="C1964" t="n">
         <v>2.915780400193211</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.616269501629219</v>
+        <v>-3.842436827057353</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.468916175227776</v>
+        <v>1.378449245056523</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3196982645582977</v>
+        <v>0.3325474538489459</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.10759935892819</v>
+        <v>3.115308872502579</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789124</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.921788930590137</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.571465330089289</v>
+        <v>-3.797632655517423</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.492846374240674</v>
+        <v>1.402379444069421</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3196982645582977</v>
+        <v>0.3325474538489459</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.113607889325116</v>
+        <v>3.121317402899505</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519911</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.819739151867337</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.423722359854287</v>
+        <v>-3.649889685282421</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.449893783611875</v>
+        <v>1.359426853440621</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4875056217931809</v>
+        <v>0.5003548110838291</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.112242524943245</v>
+        <v>3.119952038517634</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181172</v>
+        <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
         <v>2.822532773398818</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.525737042385508</v>
+        <v>-3.751904367813641</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.411881532130867</v>
+        <v>1.321414601959614</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4875056217931809</v>
+        <v>0.5003548110838291</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.115036146474726</v>
+        <v>3.122745660049115</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.823195121790476</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.519584336332723</v>
+        <v>-3.745751661760857</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.415004962943639</v>
+        <v>1.324538032772386</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4936583278459652</v>
+        <v>0.5065075171366133</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.119390118498055</v>
+        <v>3.127099632072444</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.822275598530586</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.536393634483225</v>
+        <v>-3.762560959911359</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.407361720423549</v>
+        <v>1.316894790252296</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4768490296954636</v>
+        <v>0.4896982189861117</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.108385016347865</v>
+        <v>3.116094529922254</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.888611152327407</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.474095635707103</v>
+        <v>-3.700262961135237</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.498616473730819</v>
+        <v>1.408149543559565</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4768490296954636</v>
+        <v>0.4896982189861117</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.174720570144685</v>
+        <v>3.182430083719074</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.690903154041534</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.272305438041945</v>
+        <v>-3.498472763470079</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.381624554511009</v>
+        <v>1.291157624339756</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6748672218646179</v>
+        <v>0.687716411155266</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.095823487160305</v>
+        <v>3.103533000734694</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.761193386363709</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.32319215072814</v>
+        <v>-3.549359476156273</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.431560101758706</v>
+        <v>1.341093171587453</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.6239805091784234</v>
+        <v>0.6368296984690716</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.135581691870764</v>
+        <v>3.143291205445153</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.775821122479753</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.420932695353114</v>
+        <v>-3.647100020781248</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.40709162002476</v>
+        <v>1.316624689853507</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6080912310454432</v>
+        <v>0.6209404203360913</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.140675861107019</v>
+        <v>3.148385374681408</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.774357103304425</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.597270455476044</v>
+        <v>-3.823437780904177</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.33509249680026</v>
+        <v>1.244625566629007</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.4317534709225138</v>
+        <v>0.4446026602131619</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.033409185857933</v>
+        <v>3.041118699432322</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.772848721344353</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.520848409044117</v>
+        <v>-3.74701573447225</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.364152933412959</v>
+        <v>1.273686003241706</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.4317534709225138</v>
+        <v>0.4446026602131619</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.031900803897862</v>
+        <v>3.039610317472251</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.77271158877979</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.476475277405548</v>
+        <v>-3.702642602833682</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.381765053503823</v>
+        <v>1.29129812333257</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.4761266025610824</v>
+        <v>0.4889757918517306</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.058387550316439</v>
+        <v>3.066097063890828</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.76710538291838</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.353641056518381</v>
+        <v>-3.579808381946514</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.425292535997281</v>
+        <v>1.334825605826027</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.4761266025610824</v>
+        <v>0.4889757918517306</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.05278134445503</v>
+        <v>3.060490858029419</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.773487139946185</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.305985325957325</v>
+        <v>-3.532152651385458</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.450736585249508</v>
+        <v>1.360269655078254</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.5237823331221381</v>
+        <v>0.5366315224127862</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.087756539819468</v>
+        <v>3.095466053393856</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.778379513320909</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.20546716745857</v>
+        <v>-3.431634492886704</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.495836222023734</v>
+        <v>1.405369291852481</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.6243004916208926</v>
+        <v>0.6371496809115408</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.152959808293445</v>
+        <v>3.160669321867834</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.765134185796782</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.266133757860959</v>
+        <v>-3.492301083289093</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.458324258338651</v>
+        <v>1.367857328167397</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.542602174902359</v>
+        <v>0.5554513641930071</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.090695490738197</v>
+        <v>3.098405004312586</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.76923188840741</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.221295356252561</v>
+        <v>-3.447462681680695</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.480357321592638</v>
+        <v>1.389890391421385</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.5471456078472284</v>
+        <v>0.5599947971378766</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.097519253115748</v>
+        <v>3.105228766690137</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.773392828038488</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.240793812494569</v>
+        <v>-3.466961137922703</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.476718878726913</v>
+        <v>1.38625194855566</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.4990609665673241</v>
+        <v>0.5119101558579723</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.072829407978883</v>
+        <v>3.080538921553272</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.779272430566325</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.196590975408669</v>
+        <v>-3.422758300836803</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.500279616089111</v>
+        <v>1.409812685917857</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.5432638036532246</v>
+        <v>0.5561129929438727</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.105230712758261</v>
+        <v>3.11294022633265</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.777682431035573</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.233570003072112</v>
+        <v>-3.459737328500246</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.483898005492981</v>
+        <v>1.393431075321727</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.5802377054445551</v>
+        <v>0.5930868947352033</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.125825054302307</v>
+        <v>3.133534567876695</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.828930196218613</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.07527858553284</v>
+        <v>-3.301445910960974</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.598462337691729</v>
+        <v>1.507995407520476</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.5802377054445551</v>
+        <v>0.5930868947352033</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.177072819485346</v>
+        <v>3.184782333059735</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.827370900812866</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.867636581898364</v>
+        <v>-3.093803907326497</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.679959843739773</v>
+        <v>1.58949291356852</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.7878797090790313</v>
+        <v>0.8007288983696794</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.300098726260285</v>
+        <v>3.307808239834674</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.822319129051136</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.816604489175836</v>
+        <v>-3.042771814603969</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.695320909067054</v>
+        <v>1.604853978895801</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.8389118018015592</v>
+        <v>0.8517609910922074</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.325666210132072</v>
+        <v>3.33337572370646</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.839506533143841</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.75138030804863</v>
+        <v>-2.977547633476764</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.738597985610641</v>
+        <v>1.648131055439388</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.9041359829287648</v>
+        <v>0.916985172219413</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.3819881229011</v>
+        <v>3.389697636475489</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.835467505443121</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.713953287977497</v>
+        <v>-2.94012061340563</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.749529765938375</v>
+        <v>1.659062835767122</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.9093875209579465</v>
+        <v>0.9222367102485947</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.381100018017889</v>
+        <v>3.388809531592278</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.836724297774361</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.734064944012205</v>
+        <v>-2.960232269440338</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.742741895855732</v>
+        <v>1.652274965684479</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.9204148659553657</v>
+        <v>0.9332640552460139</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.388973217347581</v>
+        <v>3.39668273092197</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.997282068795572</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.680320129585</v>
+        <v>-2.906487455013134</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.924797592647825</v>
+        <v>1.834330662476571</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9304781753958277</v>
+        <v>0.9433273646864758</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.555568974033069</v>
+        <v>3.563278487607458</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.117394978013389</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.605537868559987</v>
+        <v>-2.831705193988121</v>
       </c>
       <c r="E1992" t="n">
-        <v>2.074823406275647</v>
+        <v>1.984356476104394</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.00526043642084</v>
+        <v>1.018109625711488</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.720551239865894</v>
+        <v>3.728260753440283</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.109102954027248</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.57945378429618</v>
+        <v>-2.805621109724313</v>
       </c>
       <c r="E1993" t="n">
-        <v>2.076965015995029</v>
+        <v>1.986498085823776</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.00526043642084</v>
+        <v>1.018109625711488</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.712259215879753</v>
+        <v>3.719968729454142</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.107296149611028</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.501322603447233</v>
+        <v>-2.727489928875366</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.106410683918388</v>
+        <v>2.015943753747134</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.079437247304525</v>
+        <v>1.092286436595173</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.754958497993743</v>
+        <v>3.762668011568132</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.124850555337819</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.49243014205395</v>
+        <v>-2.718597467482083</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.127522074202492</v>
+        <v>2.037055144031239</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.079437247304525</v>
+        <v>1.092286436595173</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.772512903720534</v>
+        <v>3.780222417294923</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.116705602742403</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.660906259023827</v>
+        <v>-2.887073584451961</v>
       </c>
       <c r="E1996" t="n">
-        <v>2.051986674819125</v>
+        <v>1.961519744647871</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.051489411587944</v>
+        <v>1.064338600878592</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.74759924969517</v>
+        <v>3.755308763269559</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.097975299930265</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.963106730162244</v>
+        <v>-2.189274055590378</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.31237618355162</v>
+        <v>2.221909253380367</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.9811413522175334</v>
+        <v>0.9939905415081816</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.686660111260785</v>
+        <v>3.694369624835174</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.08863932242717</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.940385626479092</v>
+        <v>-2.166552951907225</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.312128647521785</v>
+        <v>2.221661717350532</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.9811413522175334</v>
+        <v>0.9939905415081816</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.67732413375769</v>
+        <v>3.685033647332079</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.247545448278339</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.069587439773134</v>
+        <v>-2.295754765201268</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.419354048055338</v>
+        <v>2.328887117884084</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.8519395389234912</v>
+        <v>0.8647887282141393</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.758709171632434</v>
+        <v>3.766418685206823</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.284623270771985</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.22436844655139</v>
+        <v>-2.450535771979523</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.394519467837682</v>
+        <v>2.304052537666429</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.818571864869015</v>
+        <v>0.8314210541596632</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.775766389693394</v>
+        <v>3.783475903267783</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.28129862676153</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.217313756336216</v>
+        <v>-2.44348108176435</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.394016699913297</v>
+        <v>2.303549769742043</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.8256265550841888</v>
+        <v>0.838475744374837</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.776674559812044</v>
+        <v>3.784384073386433</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.291304780406272</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.190362532009728</v>
+        <v>-2.416529857437862</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.414803343288633</v>
+        <v>2.32433641311738</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.840506901111908</v>
+        <v>0.8533560904025561</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.795608921073417</v>
+        <v>3.803318434647806</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.475407912551232</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.326315540066044</v>
+        <v>-2.552482865494178</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.544525272211067</v>
+        <v>2.454058342039813</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.840506901111908</v>
+        <v>0.8533560904025561</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.979712053218377</v>
+        <v>3.987421566792765</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.467524607454225</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.348723657870917</v>
+        <v>-2.57489098329905</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.527678719992111</v>
+        <v>2.437211789820857</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.840506901111908</v>
+        <v>0.8533560904025561</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.97182874812137</v>
+        <v>3.979538261695758</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.469578607003862</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.496729425350316</v>
+        <v>-2.72289675077845</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.470530412549989</v>
+        <v>2.380063482378735</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.7537798922483665</v>
+        <v>0.7666290815390147</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.921846542352882</v>
+        <v>3.929556055927272</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.525832324725709</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.506170351238846</v>
+        <v>-2.73233767666698</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.523007759916424</v>
+        <v>2.43254082974517</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.8762070097917579</v>
+        <v>0.8890561990824061</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.051556530600764</v>
+        <v>4.059266044175153</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.52872341927101</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.558443958574487</v>
+        <v>-2.784611284002621</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.504989411527468</v>
+        <v>2.414522481356214</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.8239334024561167</v>
+        <v>0.8367825917467648</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.02308346074468</v>
+        <v>4.03079297431907</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.526835232164785</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.634773936175393</v>
+        <v>-2.860941261603527</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.472569233380881</v>
+        <v>2.382102303209627</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.8239334024561167</v>
+        <v>0.8367825917467648</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.021195273638456</v>
+        <v>4.028904787212845</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.521655461767648</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.746530888790694</v>
+        <v>-2.972698214218828</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.422686681937622</v>
+        <v>2.332219751766369</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.7121764498408156</v>
+        <v>0.7250256391314638</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.948961331672137</v>
+        <v>3.956670845246526</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.5200894719778</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.744689869732443</v>
+        <v>-2.970857195160577</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.421857099771076</v>
+        <v>2.331390169599822</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.713444676512284</v>
+        <v>0.7262938658029322</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.948156277885171</v>
+        <v>3.955865791459559</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.533162878843719</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.876991161829996</v>
+        <v>-3.10315848725813</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.382009989797973</v>
+        <v>2.291543059626719</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.713444676512284</v>
+        <v>0.7262938658029322</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.961229684751089</v>
+        <v>3.968939198325478</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.533162878843719</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.878552804644857</v>
+        <v>-3.10472013007299</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.381385332672028</v>
+        <v>2.290918402500775</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.713444676512284</v>
+        <v>0.7262938658029322</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.961229684751089</v>
+        <v>3.968939198325478</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.531686919970721</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.906453591754329</v>
+        <v>-3.132620917182463</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.368749058955242</v>
+        <v>2.278282128783988</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6788477523693492</v>
+        <v>0.6916969416599974</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.93899557139233</v>
+        <v>3.94670508496672</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.528451363947919</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.028979694457223</v>
+        <v>-3.255147019885357</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.316503061851283</v>
+        <v>2.226036131680029</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5563216496664554</v>
+        <v>0.5691708389571035</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.862244353747793</v>
+        <v>3.869953867322182</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.595157323538423</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.04904101573373</v>
+        <v>-3.275208341161864</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.375184492931184</v>
+        <v>2.28471756275993</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5362603283899483</v>
+        <v>0.5491095176805965</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.916913520572392</v>
+        <v>3.924623034146781</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.73546904254027</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.305761833728554</v>
+        <v>-3.531929159156688</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.412807884735101</v>
+        <v>2.322340954563848</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4278457542461335</v>
+        <v>0.4406949435367816</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.992176495087951</v>
+        <v>3.999886008662339</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.80444931168591</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.459748251504695</v>
+        <v>-3.685915576932828</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.420193586770285</v>
+        <v>2.329726656599031</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4278457542461335</v>
+        <v>0.4406949435367816</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.061156764233591</v>
+        <v>4.068866277807979</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.790500513806031</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.409226347677029</v>
+        <v>-3.635393673105162</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.426453550421472</v>
+        <v>2.335986620250218</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.4278457542461335</v>
+        <v>0.4406949435367816</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.047207966353711</v>
+        <v>4.0549174799281</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.802371002861445</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.661701501684753</v>
+        <v>-3.887868827112887</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.337333977873796</v>
+        <v>2.246867047702543</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.4278457542461335</v>
+        <v>0.4406949435367816</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.059078455409125</v>
+        <v>4.066787968983514</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.803581537380389</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.931174303606461</v>
+        <v>-4.157341629034595</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.230755391624057</v>
+        <v>2.140288461452803</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.4278457542461335</v>
+        <v>0.4406949435367816</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.060288989928069</v>
+        <v>4.067998503502458</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.80770327960771</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.088718375335903</v>
+        <v>-4.314885700764036</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.171859505159602</v>
+        <v>2.081392574988348</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.360943949105859</v>
+        <v>0.3737931383965071</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.024269649071226</v>
+        <v>4.031979162645614</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301343</v>
+        <v>3.652163313301344</v>
       </c>
       <c r="C2022" t="n">
         <v>3.802781132343899</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.366682770919176</v>
+        <v>-4.59285009634731</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.055751599662481</v>
+        <v>1.965284669491228</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.2713242148203747</v>
+        <v>0.2841734041110229</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.965575661236125</v>
+        <v>3.973285174810513</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215469</v>
+        <v>3.66797646721547</v>
       </c>
       <c r="C2023" t="n">
         <v>3.964985189042944</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.483650463558067</v>
+        <v>-4.709817788986201</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.171168579305969</v>
+        <v>2.080701649134716</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.2713242148203747</v>
+        <v>0.2841734041110229</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.127779717935169</v>
+        <v>4.135489231509558</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456692</v>
+        <v>3.696553628456693</v>
       </c>
       <c r="C2024" t="n">
         <v>3.959831827006758</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.568368405779021</v>
+        <v>-4.794535731207154</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.132128040381402</v>
+        <v>2.041661110210149</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1862081858923283</v>
+        <v>0.1990573751829765</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.071556738542155</v>
+        <v>4.079266252116544</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253288</v>
+        <v>3.750058176253289</v>
       </c>
       <c r="C2025" t="n">
         <v>3.970061244575249</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.650303224047904</v>
+        <v>-4.876470549476037</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.10958353064234</v>
+        <v>2.019116600471087</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.1762734403052482</v>
+        <v>0.1891226295958963</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.075825308758398</v>
+        <v>4.083534822332787</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717832</v>
+        <v>3.783647027717833</v>
       </c>
       <c r="C2026" t="n">
         <v>3.978986883031151</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.596565050647642</v>
+        <v>-4.822732376075775</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.140004438458347</v>
+        <v>2.049537508287094</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.2300116137055103</v>
+        <v>0.2428608029961584</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.116993851254458</v>
+        <v>4.124703364828846</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616949</v>
+        <v>3.79831094461695</v>
       </c>
       <c r="C2027" t="n">
         <v>3.971139770275327</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.48655876717042</v>
+        <v>-4.712726092598554</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.176159839093412</v>
+        <v>2.085692908922158</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.2532161856227855</v>
+        <v>0.2660653749134336</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.123069481648999</v>
+        <v>4.130778995223388</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203664</v>
+        <v>3.785578085203665</v>
       </c>
       <c r="C2028" t="n">
         <v>3.975389780997301</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.343499191429494</v>
+        <v>-4.569666516857628</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.237633680111756</v>
+        <v>2.147166749940503</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.2612296122127648</v>
+        <v>0.2740788015034129</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.13212754832496</v>
+        <v>4.13983706189935</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.982650663879838</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.042052465957656</v>
+        <v>-4.268219791385791</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.365473253183028</v>
+        <v>2.275006323011774</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.562676337684602</v>
+        <v>0.5755255269752502</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.3202564664906</v>
+        <v>4.327965980064988</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064767</v>
+        <v>3.812650101064769</v>
       </c>
       <c r="C2030" t="n">
         <v>3.983621841632548</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.097007662400726</v>
+        <v>-4.32317498782886</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.34446235235851</v>
+        <v>2.253995422187256</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.562676337684602</v>
+        <v>0.5755255269752502</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.32122764424331</v>
+        <v>4.328937157817698</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859301</v>
+        <v>3.821198342859303</v>
       </c>
       <c r="C2031" t="n">
         <v>3.984464746012303</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.045969286394206</v>
+        <v>-4.27213661182234</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.365720607140874</v>
+        <v>2.27525367696962</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.562676337684602</v>
+        <v>0.5755255269752502</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.322070548623065</v>
+        <v>4.329780062197454</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354684</v>
+        <v>3.831748677354686</v>
       </c>
       <c r="C2032" t="n">
         <v>4.003502844886449</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.004829991527575</v>
+        <v>-4.230997316955709</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.401214423961672</v>
+        <v>2.310747493790418</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.6038156325512328</v>
+        <v>0.616664821841881</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.365792224417189</v>
+        <v>4.373501737991578</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,45 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.853557307023419</v>
+        <v>3.825767093085621</v>
       </c>
       <c r="C2033" t="n">
         <v>3.819686841010383</v>
       </c>
       <c r="D2033" t="n">
-        <v>-3.894223851447973</v>
+        <v>-4.120391176876107</v>
       </c>
       <c r="E2033" t="n">
-        <v>2.261640876117447</v>
+        <v>2.171173945946193</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.7144217726308348</v>
+        <v>0.727270961921483</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.248339904588884</v>
+        <v>4.256049418163274</v>
+      </c>
+    </row>
+    <row r="2034">
+      <c r="A2034" s="2" t="n">
+        <v>45496</v>
+      </c>
+      <c r="B2034" t="n">
+        <v>3.524299771904923</v>
+      </c>
+      <c r="C2034" t="n">
+        <v>3.595710968368273</v>
+      </c>
+      <c r="D2034" t="n">
+        <v>-4.120391176876107</v>
+      </c>
+      <c r="E2034" t="n">
+        <v>2.171173945946193</v>
+      </c>
+      <c r="F2034" t="n">
+        <v>0.727270961921483</v>
+      </c>
+      <c r="G2034" t="n">
+        <v>3.58877476535464</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240723.xlsx
+++ b/tame_output/ON/bt/strategyON_20240723.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>53.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>82.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,32 +844,32 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>66.2%</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>31.3%</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>31.9%</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>63.8%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.5%</t>
+          <t>-75.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>110.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>96.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.4%</t>
+          <t>-70.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>91.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.6%</t>
+          <t>456.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-573.6%</t>
+          <t>-555.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.1%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.6%</t>
+          <t>-34.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-45.9%</t>
+          <t>-43.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-159.1%</t>
+          <t>-151.9%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-123.1%</t>
+          <t>-121.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-151.3%</t>
+          <t>-152.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.4%</t>
+          <t>-22.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-87.1%</t>
+          <t>-71.3%</t>
         </is>
       </c>
     </row>
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.477989729264485</v>
+        <v>-7.471830951507869</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.1256098388030513</v>
+        <v>0.1280733499056983</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.171133866027758</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.422191348780327</v>
+        <v>2.414481835205938</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923081</v>
+        <v>3.41997943392308</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.664709437573788</v>
+        <v>-7.658550659817172</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.04689565094492743</v>
+        <v>0.04935916204757396</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.171133866027758</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.418165044245924</v>
+        <v>2.410455530671535</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297743</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.047710826316418</v>
+        <v>-8.041552048559803</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.106407005873709</v>
+        <v>-0.1039434947710625</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.171133866027758</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.41806294292434</v>
+        <v>2.410353429349951</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.052197271517807</v>
+        <v>-8.046038493761191</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.1056300679828341</v>
+        <v>-0.1031665568801881</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.162771121938499</v>
+        <v>-1.175620311229147</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.417942591774937</v>
+        <v>2.410233078200548</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737164</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.411727594021809</v>
+        <v>-8.405568816265193</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.2440918936863845</v>
+        <v>-0.2416283825837384</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.162771121938499</v>
+        <v>-1.175620311229147</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.423292895072987</v>
+        <v>2.415583381498598</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.462076657476031</v>
+        <v>-8.455917879719415</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.256315499110896</v>
+        <v>-0.2538519880082499</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.213120185392721</v>
+        <v>-1.225969374683369</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.400999476957631</v>
+        <v>2.393289963383242</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.501052558539458</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.559695934897427</v>
+        <v>-8.553537157140811</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.2923214594576855</v>
+        <v>-0.2898579483550394</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.310739462814118</v>
+        <v>-1.323588652104766</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.345469661126562</v>
+        <v>2.337760147552173</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.613767434405785</v>
+        <v>-8.60760865664917</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.311056502939457</v>
+        <v>-0.3085929918368104</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.364810962322477</v>
+        <v>-1.377660151613125</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.315920317743119</v>
+        <v>2.30821080416873</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.818025609735649</v>
+        <v>-8.811866831979033</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3872465759527599</v>
+        <v>-0.3847830648501138</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.492449906936466</v>
+        <v>-1.505299096227114</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.244850148093368</v>
+        <v>2.237140634518979</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.851678448244122</v>
+        <v>-8.845519670487507</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3962251568717132</v>
+        <v>-0.3937616457690671</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.592863274853503</v>
+        <v>-1.605712464144152</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.189084681827581</v>
+        <v>2.181375168253192</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.778208616576674</v>
+        <v>-8.772049838820058</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.3514655227113126</v>
+        <v>-0.3490020116086665</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.519393443186055</v>
+        <v>-1.532242632476703</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.248538282321471</v>
+        <v>2.240828768747082</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.953333033963217</v>
+        <v>-8.947174256206601</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.406960068918413</v>
+        <v>-0.4044965578157669</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.694517860572599</v>
+        <v>-1.707367049863247</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.158018852637062</v>
+        <v>2.150309339062673</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.187785127977707</v>
+        <v>-9.181626350221091</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.507960071425805</v>
+        <v>-0.5054965603231589</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.694517860572599</v>
+        <v>-1.707367049863247</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.150799687735466</v>
+        <v>2.143090174161077</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.292159859004153</v>
+        <v>-9.286001081247537</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5563821546103598</v>
+        <v>-0.5539186435077137</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.798892591599045</v>
+        <v>-1.811741780889693</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.081502658345622</v>
+        <v>2.073793144771233</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.34494601460448</v>
+        <v>-9.338787236847864</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5763808270119339</v>
+        <v>-0.5739173159092879</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.894568078181442</v>
+        <v>-1.90741726747209</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.025213156234741</v>
+        <v>2.017503642660351</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.470982807972769</v>
+        <v>-9.464824030216153</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.624101815730135</v>
+        <v>-0.6216383046274889</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.882165644662348</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.0430578585497</v>
+        <v>2.035348344975311</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.413911036076838</v>
+        <v>-9.407752258320222</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5972827712853621</v>
+        <v>-0.5948192601827156</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.882165644662348</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.047048194236101</v>
+        <v>2.039338680661713</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.555582877800958</v>
+        <v>-9.549424100044343</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6554267348737519</v>
+        <v>-0.6529632237711054</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.882165644662348</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.045572967337359</v>
+        <v>2.037863453762971</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.505992033376124</v>
+        <v>-9.499833255619508</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6205369869389457</v>
+        <v>-0.6180734758362996</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.819725610946866</v>
+        <v>-1.832574800237514</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.090380884157132</v>
+        <v>2.082671370582744</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.357073698904268</v>
+        <v>-9.350914921147652</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5740207867968863</v>
+        <v>-0.5715572756942398</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.788476020211692</v>
+        <v>-1.801325209502341</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.096079504951553</v>
+        <v>2.088369991377164</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.131228546184857</v>
+        <v>-9.12506976842824</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4741036526729134</v>
+        <v>-0.4716401415702665</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.746549344624529</v>
+        <v>-1.759398533915177</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.13081458334006</v>
+        <v>2.123105069765671</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.006649889847266</v>
+        <v>-9.000491112090648</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4231330455818179</v>
+        <v>-0.4206695344791709</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.746549344624529</v>
+        <v>-1.759398533915177</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.131953727896119</v>
+        <v>2.12424421432173</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.059545177891552</v>
+        <v>-9.053386400134935</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4416573866374249</v>
+        <v>-0.439193875534778</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.754443187826731</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.137560709711294</v>
+        <v>2.129851196136905</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.987412002603671</v>
+        <v>-8.981253224847054</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.4070704122836357</v>
+        <v>-0.4046069011809887</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.754443187826731</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.14329441394993</v>
+        <v>2.135584900375542</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.916045609994024</v>
+        <v>-8.909886832237406</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3882611176336423</v>
+        <v>-0.3857976065309954</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.683076795217083</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.176376987121854</v>
+        <v>2.168667473547465</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.822586576008799</v>
+        <v>-8.816427798252182</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.36076098535246</v>
+        <v>-0.3582974742498131</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.683076795217083</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.166493505808947</v>
+        <v>2.158783992234558</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.555344775140401</v>
+        <v>-8.549185997383784</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2556988255044748</v>
+        <v>-0.2532353144018278</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.683076795217083</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.164658945309573</v>
+        <v>2.156949431735184</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.457437736463911</v>
+        <v>-8.451278958707293</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2168363250073391</v>
+        <v>-0.2143728139046921</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.602241856065878</v>
+        <v>-1.615091045356527</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.205150080252446</v>
+        <v>2.197440566678057</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.433484195487953</v>
+        <v>-8.427325417731335</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2065864024714625</v>
+        <v>-0.2041228913688156</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.578288315089921</v>
+        <v>-1.591137504380569</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.220190710983514</v>
+        <v>2.212481197409125</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.169424257165156</v>
+        <v>-8.163265479408539</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1142227433040959</v>
+        <v>-0.1117592322014489</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.327077566057773</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.365366357815439</v>
+        <v>2.357656844241051</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.693220105225982</v>
+        <v>-7.4561858559037</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.07347188381127312</v>
+        <v>0.1682855835401855</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.327077566057773</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.362579324155138</v>
+        <v>2.35486981058075</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.653035806859791</v>
+        <v>-7.41600155753751</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.08988922704559066</v>
+        <v>0.1847029267745031</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.274044078400934</v>
+        <v>-1.286893267691582</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.387033527062695</v>
+        <v>2.379324013488306</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.489635935920429</v>
+        <v>-7.252601686598148</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.1546159966420926</v>
+        <v>0.249429696371005</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.110644207461571</v>
+        <v>-1.123493396752219</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.484440270847069</v>
+        <v>2.47673075727268</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.25615471369083</v>
+        <v>-7.019120464368549</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2559329143717841</v>
+        <v>0.350746614100697</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8771629852319727</v>
+        <v>-0.8900121745226208</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.632453433022681</v>
+        <v>2.624743919448292</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.106488322683315</v>
+        <v>-6.869454073361034</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3129072604618313</v>
+        <v>0.4077209601907437</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7842594939894367</v>
+        <v>-0.7971086832800849</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.685303317455243</v>
+        <v>2.677593803880854</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.974212849052429</v>
+        <v>-6.737178599730147</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3611849366612128</v>
+        <v>0.4559986363901252</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6519840203585501</v>
+        <v>-0.6648332096491982</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.760036088380802</v>
+        <v>2.752326574806413</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.818474516492687</v>
+        <v>-6.581440267170406</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4262953303727461</v>
+        <v>0.521109030101659</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.5090948770894567</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.856294148604284</v>
+        <v>2.848584635029895</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.569474717809106</v>
+        <v>-6.332440468486825</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5388015910698374</v>
+        <v>0.6336152907987498</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.5090948770894567</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.869200489827942</v>
+        <v>2.861490976253553</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.67506470758221</v>
+        <v>-6.438030458259929</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3685896655613767</v>
+        <v>0.4634033652902896</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.6018356775719129</v>
+        <v>-0.6146848668625611</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.677870566364861</v>
+        <v>2.670161052790472</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.693799609700807</v>
+        <v>-6.456765360378526</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4096400465910244</v>
+        <v>0.5044537463199372</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.6074316872320442</v>
+        <v>-0.6202808765226924</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.723057302445869</v>
+        <v>2.71534778887148</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.545859568293208</v>
+        <v>-6.308825318970927</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3489371404658965</v>
+        <v>0.4437508401948094</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.5871107713234867</v>
+        <v>-0.5999599606141348</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.615370929302836</v>
+        <v>2.607661415728447</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.49289004603922</v>
+        <v>-6.255855796716938</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3614109631140137</v>
+        <v>0.4562246628429265</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.5469904383601459</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.638438656401751</v>
+        <v>2.630729142827362</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.449341639268529</v>
+        <v>-6.212307389946248</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3718697137271967</v>
+        <v>0.4666834134561095</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.5469904383601459</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.631478044306657</v>
+        <v>2.623768530732268</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.41597843278976</v>
+        <v>-6.178944183467479</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3996773506998474</v>
+        <v>0.4944910504287598</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.5469904383601459</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.645940398687801</v>
+        <v>2.638230885113412</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.307719295667239</v>
+        <v>-6.070685046344957</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4375131260080511</v>
+        <v>0.5323268257369635</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.5469904383601459</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.640472519146996</v>
+        <v>2.632763005572607</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.184428160850108</v>
+        <v>-5.947393911527826</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4843276739454803</v>
+        <v>0.5791413736743931</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.4108501142523673</v>
+        <v>-0.4236993035430154</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.711945294047851</v>
+        <v>2.704235780473462</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.163278961946665</v>
+        <v>-5.926244712624383</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5004883317441831</v>
+        <v>0.5953020314730955</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.3897009153489239</v>
+        <v>-0.4025501046395721</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.732335791627242</v>
+        <v>2.724626278052853</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.91951351996322</v>
+        <v>-5.682479270640939</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5937752168846115</v>
+        <v>0.6885889166135239</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.3897009153489239</v>
+        <v>-0.4025501046395721</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.728116499974293</v>
+        <v>2.720406986399904</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.817750699685925</v>
+        <v>-5.580716450363644</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6366046589155454</v>
+        <v>0.7314183586444578</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.3893310362471434</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.738172254929766</v>
+        <v>2.730462741355377</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.567900305736851</v>
+        <v>-5.330866056414569</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7292868914788775</v>
+        <v>0.8241005912077899</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.3893310362471434</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.730914329913468</v>
+        <v>2.723204816339079</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.392008213269419</v>
+        <v>-5.154973963947137</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8032428519864987</v>
+        <v>0.8980565517154115</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.3893310362471434</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.734513453434117</v>
+        <v>2.726803939859728</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.220561750246955</v>
+        <v>-4.983527500924674</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8851489432500381</v>
+        <v>0.9799626429789505</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.2050353839340321</v>
+        <v>-0.2178845732246802</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.850708837302149</v>
+        <v>2.84299932372776</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.146272184508616</v>
+        <v>-4.909237935186335</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9138852471616707</v>
+        <v>1.008698946890583</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.1307458181956928</v>
+        <v>-0.143595007486341</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.894303054361449</v>
+        <v>2.88659354078706</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.082636442274682</v>
+        <v>-4.8456021929524</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9440343451095616</v>
+        <v>1.038848044838474</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.06711007596175828</v>
+        <v>-0.07995926525240643</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.937179300756127</v>
+        <v>2.929469787181738</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.971209682948762</v>
+        <v>-4.73417543362648</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9697993076237252</v>
+        <v>1.064613007352638</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.06711007596175828</v>
+        <v>-0.07995926525240643</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.918373559539923</v>
+        <v>2.910664045965534</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.730779186143901</v>
+        <v>-4.49374493682162</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.067714582970547</v>
+        <v>1.162528282699459</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.173320420843102</v>
+        <v>0.1604712315524539</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.064374934247716</v>
+        <v>3.056665420673327</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.658536617972707</v>
+        <v>-4.421502368650425</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.100540924073845</v>
+        <v>1.195354623802757</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.173320420843102</v>
+        <v>0.1604712315524539</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.068304248082536</v>
+        <v>3.060594734508147</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879963</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.640822931094841</v>
+        <v>-4.40378868177256</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.108304982742331</v>
+        <v>1.203118682471244</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.1765017497400188</v>
+        <v>0.1636525604493707</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.070891629338026</v>
+        <v>3.063182115763638</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502335</v>
+        <v>3.848616626502333</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.532018045615114</v>
+        <v>-4.340423249819815</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.148825008154215</v>
+        <v>1.225462926472335</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.1765017497400188</v>
+        <v>0.1636525604493707</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.06788970055802</v>
+        <v>3.060180186983631</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675934</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.311997247578104</v>
+        <v>-4.120402451782804</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.238412364379634</v>
+        <v>1.315050282697753</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3177215948079991</v>
+        <v>0.3048724055173509</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.154200644609422</v>
+        <v>3.146491131035033</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539946</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.179129558514826</v>
+        <v>-3.987534762719526</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.307453622806768</v>
+        <v>1.384091541124888</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3177215948079991</v>
+        <v>0.3048724055173509</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.170094827411245</v>
+        <v>3.162385313836857</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.058956475150327</v>
+        <v>-3.867361679355027</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.356668700592869</v>
+        <v>1.43330661891099</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.437894678172498</v>
+        <v>0.4250454888818498</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.243344521870247</v>
+        <v>3.235635008295858</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.91428433005059</v>
+        <v>-3.72268953425529</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.424625661194204</v>
+        <v>1.501263579512324</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.5825668232722354</v>
+        <v>0.5697176339815873</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.340235911491529</v>
+        <v>3.33252639791714</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942101</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.974159157408282</v>
+        <v>-3.782564361612982</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.386713221652553</v>
+        <v>1.463351139970673</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5226919959145433</v>
+        <v>0.5098428066238951</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.29034850647834</v>
+        <v>3.282638992903951</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.854338926497445</v>
+        <v>-3.662744130702145</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.449930483251097</v>
+        <v>1.526568401569217</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5226919959145433</v>
+        <v>0.5098428066238951</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.305637675712548</v>
+        <v>3.297928162138159</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430689</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.856808632959251</v>
+        <v>-3.665213837163951</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.356586799988816</v>
+        <v>1.433224718306936</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5202222894527371</v>
+        <v>0.5073731001620889</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.211800051157906</v>
+        <v>3.204090537583517</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003599</v>
+        <v>3.743220196003597</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.925178819283261</v>
+        <v>-3.73358402348796</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.248500586944513</v>
+        <v>1.325138505262633</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.529497988488952</v>
+        <v>0.5166487991983039</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.136627332064936</v>
+        <v>3.128917818490547</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508366</v>
+        <v>3.714179139508365</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.938966872130307</v>
+        <v>-3.747372076335007</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.233422074437586</v>
+        <v>1.310059992755706</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.529497988488952</v>
+        <v>0.5166487991983039</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.127064040696828</v>
+        <v>3.119354527122439</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417701</v>
+        <v>3.710906731417699</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.994486948022897</v>
+        <v>-3.802892152227597</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.348244880772753</v>
+        <v>1.424882799090873</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.529497988488952</v>
+        <v>0.5166487991983039</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.26409487738903</v>
+        <v>3.256385363814641</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205894</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.819012688230428</v>
+        <v>-3.627417892435127</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.423001816681528</v>
+        <v>1.499639734999648</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.529497988488952</v>
+        <v>0.5166487991983039</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.268662109380818</v>
+        <v>3.260952595806429</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225438</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.919082016977528</v>
+        <v>-3.738354145076376</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.358716113943895</v>
+        <v>1.431007262704356</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.529497988488952</v>
+        <v>0.5166487991983039</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.244404138142025</v>
+        <v>3.236694624567636</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111292</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.885418471505246</v>
+        <v>-3.704690599604094</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.300719845534257</v>
+        <v>1.373010994294718</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5631615339612339</v>
+        <v>0.5503123446705858</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.193140578826844</v>
+        <v>3.185431065252455</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.825565852301523</v>
+        <v>-3.644837980400371</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.334833279647879</v>
+        <v>1.40712442840834</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5631615339612339</v>
+        <v>0.5503123446705858</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.203312965258976</v>
+        <v>3.195603451684587</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742297</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.739322389275145</v>
+        <v>-3.558594517373994</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.364276935432291</v>
+        <v>1.436568084192751</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5631615339612339</v>
+        <v>0.5503123446705858</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.198259235832837</v>
+        <v>3.190549722258448</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316047</v>
+        <v>3.752027499316044</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.784629208674125</v>
+        <v>-3.603901336772974</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.337929983117224</v>
+        <v>1.410221131877685</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5223513709520031</v>
+        <v>0.509502181661355</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.165548913471823</v>
+        <v>3.157839399897434</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.813662313376426</v>
+        <v>-3.632934441475275</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.326868614269405</v>
+        <v>1.399159763029866</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5223513709520031</v>
+        <v>0.509502181661355</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.166100786504925</v>
+        <v>3.158391272930536</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809496</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.720851831925567</v>
+        <v>-3.540123960024416</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.293265498741114</v>
+        <v>1.365556647501575</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6151618524028625</v>
+        <v>0.6023126631122143</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.151059767266806</v>
+        <v>3.143350253692417</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560423</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.765241301254995</v>
+        <v>-3.584513429353843</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.277383186933944</v>
+        <v>1.349674335694405</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.5707723830734348</v>
+        <v>0.5579231937827867</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.126299561593751</v>
+        <v>3.118590048019362</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.652570083018745</v>
+        <v>-3.471842211117593</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.317527382740167</v>
+        <v>1.389818531500628</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.683443601309685</v>
+        <v>0.6705944120190368</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.188978001047224</v>
+        <v>3.181268487472835</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798534</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.540193081836072</v>
+        <v>-3.359465209934921</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.367969479043903</v>
+        <v>1.440260627804364</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.683443601309685</v>
+        <v>0.6705944120190368</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.194469296877891</v>
+        <v>3.186759783303502</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498861</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.567973479737425</v>
+        <v>-3.387245607836274</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.368354521651901</v>
+        <v>1.440645670412362</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6556632034083318</v>
+        <v>0.6428140141176837</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.189298259905618</v>
+        <v>3.181588746331229</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.686354152467564</v>
+        <v>-3.505626280566412</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.159357972560499</v>
+        <v>1.23164912132096</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5884453512573556</v>
+        <v>0.5755961619667075</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.987323268615686</v>
+        <v>2.979613755041297</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729265</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.794968230910895</v>
+        <v>-3.614240359009743</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.236062001902372</v>
+        <v>1.308353150662833</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5884453512573556</v>
+        <v>0.5755961619667075</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.107472929334891</v>
+        <v>3.099763415760502</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190764</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.759559192662752</v>
+        <v>-3.5788313207616</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.264738643303952</v>
+        <v>1.337029792064413</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5884453512573556</v>
+        <v>0.5755961619667075</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.121985955437214</v>
+        <v>3.114276441862825</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913422</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.721175530104601</v>
+        <v>-3.540447658203449</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.277511549669582</v>
+        <v>1.349802698430042</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6268290138155068</v>
+        <v>0.6139798245248587</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.142435594314474</v>
+        <v>3.134726080740085</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532482</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.544059200069435</v>
+        <v>-3.363331328168283</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.34508711052895</v>
+        <v>1.417378259289411</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6268290138155068</v>
+        <v>0.6139798245248587</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.139164623159775</v>
+        <v>3.131455109585386</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793899</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.58915144490298</v>
+        <v>-3.408423573001829</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.327733604357445</v>
+        <v>1.400024753117905</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.564932970646117</v>
+        <v>0.5520837813554689</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.102710389020055</v>
+        <v>3.095000875445666</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.409776023664213</v>
+        <v>-3.229048151763061</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.393270748159366</v>
+        <v>1.465561896919827</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7217097288168357</v>
+        <v>0.7088605395261875</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.190563419228901</v>
+        <v>3.182853905654512</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982225</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.454790237184819</v>
+        <v>-3.274062365283668</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.356072518082714</v>
+        <v>1.428363666843174</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6913608335022311</v>
+        <v>0.6785116442115829</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.153161537371727</v>
+        <v>3.145452023797338</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509533</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.721794747457254</v>
+        <v>-3.541066875556103</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.254962276312685</v>
+        <v>1.327253425073146</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4969977954592826</v>
+        <v>0.4841486061686344</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.042235276884904</v>
+        <v>3.034525763310515</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760813</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.822992528894427</v>
+        <v>-3.642264656993276</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.213687085634317</v>
+        <v>1.285978234394778</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4285889819139634</v>
+        <v>0.4157397926233152</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.000393910654214</v>
+        <v>2.992684397079825</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.816481562280114</v>
+        <v>-3.635753690378963</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.213891433834359</v>
+        <v>1.28618258259482</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4285889819139634</v>
+        <v>0.4157397926233152</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.99799387220853</v>
+        <v>2.990284358634141</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.797443434572817</v>
+        <v>-3.616715562671666</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.218031404125523</v>
+        <v>1.290322552885984</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3704053705827688</v>
+        <v>0.3575561812921206</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.959608424618059</v>
+        <v>2.95189891104367</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131249</v>
       </c>
       <c r="C1963" t="n">
         <v>2.914947071207078</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.828570065723435</v>
+        <v>-3.647842193822284</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.383162620603956</v>
+        <v>1.455453769364417</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3704053705827688</v>
+        <v>0.3575561812921206</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.137190293556739</v>
+        <v>3.12948077998235</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067865</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.915780400193211</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.842436827057353</v>
+        <v>-3.661708955156201</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.378449245056523</v>
+        <v>1.450740393816984</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3325474538489459</v>
+        <v>0.3196982645582977</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.115308872502579</v>
+        <v>3.10759935892819</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.921788930590137</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.797632655517423</v>
+        <v>-3.616904783616271</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.402379444069421</v>
+        <v>1.474670592829881</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3325474538489459</v>
+        <v>0.3196982645582977</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.121317402899505</v>
+        <v>3.113607889325116</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.819739151867337</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.649889685282421</v>
+        <v>-3.469161813381269</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.359426853440621</v>
+        <v>1.431718002201082</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5003548110838291</v>
+        <v>0.4875056217931809</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.119952038517634</v>
+        <v>3.112242524943245</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181171</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.822532773398818</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.751904367813641</v>
+        <v>-3.57117649591249</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.321414601959614</v>
+        <v>1.393705750720074</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5003548110838291</v>
+        <v>0.4875056217931809</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.122745660049115</v>
+        <v>3.115036146474726</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.823195121790476</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.745751661760857</v>
+        <v>-3.565023789859706</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.324538032772386</v>
+        <v>1.396829181532846</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5065075171366133</v>
+        <v>0.4936583278459652</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.127099632072444</v>
+        <v>3.119390118498055</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.822275598530586</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.762560959911359</v>
+        <v>-3.581833088010207</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.316894790252296</v>
+        <v>1.389185939012756</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4896982189861117</v>
+        <v>0.4768490296954636</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.116094529922254</v>
+        <v>3.108385016347865</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>2.888611152327407</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.700262961135237</v>
+        <v>-3.519535089234085</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.408149543559565</v>
+        <v>1.480440692320026</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4896982189861117</v>
+        <v>0.4768490296954636</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.182430083719074</v>
+        <v>3.174720570144685</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992192</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
         <v>2.690903154041534</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.498472763470079</v>
+        <v>-3.317744891568927</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.291157624339756</v>
+        <v>1.363448773100216</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.687716411155266</v>
+        <v>0.6748672218646179</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.103533000734694</v>
+        <v>3.095823487160305</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
         <v>2.761193386363709</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.549359476156273</v>
+        <v>-3.368631604255122</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.341093171587453</v>
+        <v>1.413384320347913</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.6368296984690716</v>
+        <v>0.6239805091784234</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.143291205445153</v>
+        <v>3.135581691870764</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
         <v>2.775821122479753</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.647100020781248</v>
+        <v>-3.466372148880096</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.316624689853507</v>
+        <v>1.388915838613967</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6209404203360913</v>
+        <v>0.6080912310454432</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.148385374681408</v>
+        <v>3.140675861107019</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.774357103304425</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.823437780904177</v>
+        <v>-3.642709909003026</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.244625566629007</v>
+        <v>1.316916715389467</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.4446026602131619</v>
+        <v>0.4317534709225138</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.041118699432322</v>
+        <v>3.033409185857933</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.772848721344353</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.74701573447225</v>
+        <v>-3.566287862571099</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.273686003241706</v>
+        <v>1.345977152002166</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.4446026602131619</v>
+        <v>0.4317534709225138</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.039610317472251</v>
+        <v>3.031900803897862</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316249</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
         <v>2.77271158877979</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.702642602833682</v>
+        <v>-3.52191473093253</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.29129812333257</v>
+        <v>1.36358927209303</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.4889757918517306</v>
+        <v>0.4761266025610824</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.066097063890828</v>
+        <v>3.058387550316439</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105968</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
         <v>2.76710538291838</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.579808381946514</v>
+        <v>-3.399080510045363</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.334825605826027</v>
+        <v>1.407116754586488</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.4889757918517306</v>
+        <v>0.4761266025610824</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.060490858029419</v>
+        <v>3.05278134445503</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190326</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
         <v>2.773487139946185</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.532152651385458</v>
+        <v>-3.351424779484307</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.360269655078254</v>
+        <v>1.432560803838715</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.5366315224127862</v>
+        <v>0.5237823331221381</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.095466053393856</v>
+        <v>3.087756539819468</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
         <v>2.778379513320909</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.431634492886704</v>
+        <v>-3.250906620985552</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.405369291852481</v>
+        <v>1.477660440612941</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.6371496809115408</v>
+        <v>0.6243004916208926</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.160669321867834</v>
+        <v>3.152959808293445</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557294</v>
+        <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
         <v>2.765134185796782</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.492301083289093</v>
+        <v>-3.311573211387941</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.367857328167397</v>
+        <v>1.440148476927858</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.5554513641930071</v>
+        <v>0.542602174902359</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.098405004312586</v>
+        <v>3.090695490738197</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932769</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
         <v>2.76923188840741</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.447462681680695</v>
+        <v>-3.266734809779543</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.389890391421385</v>
+        <v>1.462181540181846</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.5599947971378766</v>
+        <v>0.5471456078472284</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.105228766690137</v>
+        <v>3.097519253115748</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917051</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.773392828038488</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.466961137922703</v>
+        <v>-3.286233266021552</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.38625194855566</v>
+        <v>1.45854309731612</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5119101558579723</v>
+        <v>0.4990609665673241</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.080538921553272</v>
+        <v>3.072829407978883</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.779272430566325</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.422758300836803</v>
+        <v>-3.242030428935651</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.409812685917857</v>
+        <v>1.482103834678318</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.5561129929438727</v>
+        <v>0.5432638036532246</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.11294022633265</v>
+        <v>3.105230712758261</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
         <v>2.777682431035573</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.459737328500246</v>
+        <v>-3.279009456599094</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.393431075321727</v>
+        <v>1.465722224082188</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.5930868947352033</v>
+        <v>0.5802377054445551</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.133534567876695</v>
+        <v>3.125825054302307</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.828930196218613</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.301445910960974</v>
+        <v>-3.120718039059822</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.507995407520476</v>
+        <v>1.580286556280937</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.5930868947352033</v>
+        <v>0.5802377054445551</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.184782333059735</v>
+        <v>3.177072819485346</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321021</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.827370900812866</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.093803907326497</v>
+        <v>-2.913076035425346</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.58949291356852</v>
+        <v>1.66178406232898</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.8007288983696794</v>
+        <v>0.7878797090790313</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.307808239834674</v>
+        <v>3.300098726260285</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475138</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.822319129051136</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.042771814603969</v>
+        <v>-2.862043942702818</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.604853978895801</v>
+        <v>1.677145127656261</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.8517609910922074</v>
+        <v>0.8389118018015592</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.33337572370646</v>
+        <v>3.325666210132072</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.839506533143841</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.977547633476764</v>
+        <v>-2.796819761575613</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.648131055439388</v>
+        <v>1.720422204199848</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.916985172219413</v>
+        <v>0.9041359829287648</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.389697636475489</v>
+        <v>3.3819881229011</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882557</v>
+        <v>3.840061186882554</v>
       </c>
       <c r="C1989" t="n">
         <v>2.835467505443121</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.94012061340563</v>
+        <v>-2.759392741504479</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.659062835767122</v>
+        <v>1.731353984527582</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.9222367102485947</v>
+        <v>0.9093875209579465</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.388809531592278</v>
+        <v>3.381100018017889</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899266</v>
+        <v>3.845169808992657</v>
       </c>
       <c r="C1990" t="n">
         <v>2.836724297774361</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.960232269440338</v>
+        <v>-2.779504397539187</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.652274965684479</v>
+        <v>1.724566114444939</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.9332640552460139</v>
+        <v>0.9204148659553657</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.39668273092197</v>
+        <v>3.388973217347581</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636284</v>
       </c>
       <c r="C1991" t="n">
         <v>2.997282068795572</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.906487455013134</v>
+        <v>-2.725759583111982</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.834330662476571</v>
+        <v>1.906621811237032</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9433273646864758</v>
+        <v>0.9304781753958277</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.563278487607458</v>
+        <v>3.555568974033069</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957625</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>3.117394978013389</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.831705193988121</v>
+        <v>-2.65097732208697</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.984356476104394</v>
+        <v>2.056647624864854</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.018109625711488</v>
+        <v>1.00526043642084</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.728260753440283</v>
+        <v>3.720551239865894</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998756</v>
+        <v>3.814230727998752</v>
       </c>
       <c r="C1993" t="n">
         <v>3.109102954027248</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.805621109724313</v>
+        <v>-2.624893237823162</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.986498085823776</v>
+        <v>2.058789234584236</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.018109625711488</v>
+        <v>1.00526043642084</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.719968729454142</v>
+        <v>3.712259215879753</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896929</v>
+        <v>3.803397818896926</v>
       </c>
       <c r="C1994" t="n">
         <v>3.107296149611028</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.727489928875366</v>
+        <v>-2.546762056974215</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.015943753747134</v>
+        <v>2.088234902507595</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.092286436595173</v>
+        <v>1.079437247304525</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.762668011568132</v>
+        <v>3.754958497993743</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959857</v>
+        <v>3.796264143959854</v>
       </c>
       <c r="C1995" t="n">
         <v>3.124850555337819</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.718597467482083</v>
+        <v>-2.537869595580932</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.037055144031239</v>
+        <v>2.109346292791699</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.092286436595173</v>
+        <v>1.079437247304525</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.780222417294923</v>
+        <v>3.772512903720534</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945362</v>
       </c>
       <c r="C1996" t="n">
         <v>3.116705602742403</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.887073584451961</v>
+        <v>-2.70634571255081</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.961519744647871</v>
+        <v>2.033810893408332</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.064338600878592</v>
+        <v>1.051489411587944</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.755308763269559</v>
+        <v>3.74759924969517</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782704</v>
       </c>
       <c r="C1997" t="n">
         <v>3.097975299930265</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.189274055590378</v>
+        <v>-2.008546183689226</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.221909253380367</v>
+        <v>2.294200402140827</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.9939905415081816</v>
+        <v>0.9811413522175334</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.694369624835174</v>
+        <v>3.686660111260785</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632636</v>
+        <v>3.784671345632632</v>
       </c>
       <c r="C1998" t="n">
         <v>3.08863932242717</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.166552951907225</v>
+        <v>-1.985825080006074</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.221661717350532</v>
+        <v>2.293952866110993</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.9939905415081816</v>
+        <v>0.9811413522175334</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.685033647332079</v>
+        <v>3.67732413375769</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777669</v>
       </c>
       <c r="C1999" t="n">
         <v>3.247545448278339</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.295754765201268</v>
+        <v>-2.115026893300116</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.328887117884084</v>
+        <v>2.401178266644545</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.8647887282141393</v>
+        <v>0.8519395389234912</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.766418685206823</v>
+        <v>3.758709171632434</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644412</v>
+        <v>3.779933725644408</v>
       </c>
       <c r="C2000" t="n">
         <v>3.284623270771985</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.450535771979523</v>
+        <v>-2.269807900078372</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.304052537666429</v>
+        <v>2.376343686426889</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.8314210541596632</v>
+        <v>0.818571864869015</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.783475903267783</v>
+        <v>3.775766389693394</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799964</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>3.28129862676153</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.44348108176435</v>
+        <v>-2.262753209863198</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.303549769742043</v>
+        <v>2.375840918502504</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.838475744374837</v>
+        <v>0.8256265550841888</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.784384073386433</v>
+        <v>3.776674559812044</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.766673496331113</v>
       </c>
       <c r="C2002" t="n">
         <v>3.291304780406272</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.416529857437862</v>
+        <v>-2.23580198553671</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.32433641311738</v>
+        <v>2.39662756187784</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.8533560904025561</v>
+        <v>0.840506901111908</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.803318434647806</v>
+        <v>3.795608921073417</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784108</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.475407912551232</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.552482865494178</v>
+        <v>-2.371754993593027</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.454058342039813</v>
+        <v>2.526349490800274</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.8533560904025561</v>
+        <v>0.840506901111908</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.987421566792765</v>
+        <v>3.979712053218377</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714427</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
         <v>3.467524607454225</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.57489098329905</v>
+        <v>-2.394163111397899</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.437211789820857</v>
+        <v>2.509502938581318</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.8533560904025561</v>
+        <v>0.840506901111908</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.979538261695758</v>
+        <v>3.97182874812137</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155033</v>
+        <v>3.719118627155029</v>
       </c>
       <c r="C2005" t="n">
         <v>3.469578607003862</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.72289675077845</v>
+        <v>-2.542168878877298</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.380063482378735</v>
+        <v>2.452354631139196</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.7666290815390147</v>
+        <v>0.7537798922483665</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.929556055927272</v>
+        <v>3.921846542352882</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161978</v>
+        <v>3.729452285161974</v>
       </c>
       <c r="C2006" t="n">
         <v>3.525832324725709</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.73233767666698</v>
+        <v>-2.551609804765828</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.43254082974517</v>
+        <v>2.504831978505631</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.8890561990824061</v>
+        <v>0.8762070097917579</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.059266044175153</v>
+        <v>4.051556530600764</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321635</v>
+        <v>3.714941193321631</v>
       </c>
       <c r="C2007" t="n">
         <v>3.52872341927101</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.784611284002621</v>
+        <v>-2.60388341210147</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.414522481356214</v>
+        <v>2.486813630116675</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.8367825917467648</v>
+        <v>0.8239334024561167</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.03079297431907</v>
+        <v>4.02308346074468</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347703</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
         <v>3.526835232164785</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.860941261603527</v>
+        <v>-2.680213389702375</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.382102303209627</v>
+        <v>2.454393451970088</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.8367825917467648</v>
+        <v>0.8239334024561167</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.028904787212845</v>
+        <v>4.021195273638456</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887748</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.521655461767648</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.972698214218828</v>
+        <v>-2.791970342317676</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.332219751766369</v>
+        <v>2.40451090052683</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.7250256391314638</v>
+        <v>0.7121764498408156</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.956670845246526</v>
+        <v>3.948961331672137</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343066</v>
+        <v>3.712897612343062</v>
       </c>
       <c r="C2010" t="n">
         <v>3.5200894719778</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.970857195160577</v>
+        <v>-2.790129323259425</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.331390169599822</v>
+        <v>2.403681318360283</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7262938658029322</v>
+        <v>0.713444676512284</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.955865791459559</v>
+        <v>3.948156277885171</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647106</v>
+        <v>3.754911907647102</v>
       </c>
       <c r="C2011" t="n">
         <v>3.533162878843719</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.10315848725813</v>
+        <v>-2.922430615356979</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.291543059626719</v>
+        <v>2.36383420838718</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7262938658029322</v>
+        <v>0.713444676512284</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.968939198325478</v>
+        <v>3.961229684751089</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763533</v>
+        <v>3.74989685176353</v>
       </c>
       <c r="C2012" t="n">
         <v>3.533162878843719</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.10472013007299</v>
+        <v>-2.923992258171839</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.290918402500775</v>
+        <v>2.363209551261236</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7262938658029322</v>
+        <v>0.713444676512284</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.968939198325478</v>
+        <v>3.961229684751089</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392117</v>
+        <v>3.715834055392113</v>
       </c>
       <c r="C2013" t="n">
         <v>3.531686919970721</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.132620917182463</v>
+        <v>-2.951893045281312</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.278282128783988</v>
+        <v>2.350573277544449</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6916969416599974</v>
+        <v>0.6788477523693492</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.94670508496672</v>
+        <v>3.93899557139233</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172528</v>
+        <v>3.684909939172524</v>
       </c>
       <c r="C2014" t="n">
         <v>3.528451363947919</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.255147019885357</v>
+        <v>-3.074419147984206</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.226036131680029</v>
+        <v>2.29832728044049</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5691708389571035</v>
+        <v>0.5563216496664554</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.869953867322182</v>
+        <v>3.862244353747793</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971079</v>
+        <v>3.619362241971075</v>
       </c>
       <c r="C2015" t="n">
         <v>3.595157323538423</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.275208341161864</v>
+        <v>-3.094480469260712</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.28471756275993</v>
+        <v>2.357008711520391</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5491095176805965</v>
+        <v>0.5362603283899483</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.924623034146781</v>
+        <v>3.916913520572392</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199806</v>
+        <v>3.640764248199803</v>
       </c>
       <c r="C2016" t="n">
         <v>3.73546904254027</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.531929159156688</v>
+        <v>-3.351201287255536</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.322340954563848</v>
+        <v>2.394632103324308</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4406949435367816</v>
+        <v>0.4278457542461335</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.999886008662339</v>
+        <v>3.992176495087951</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622237</v>
+        <v>3.668303164622233</v>
       </c>
       <c r="C2017" t="n">
         <v>3.80444931168591</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.685915576932828</v>
+        <v>-3.505187705031677</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.329726656599031</v>
+        <v>2.402017805359492</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4406949435367816</v>
+        <v>0.4278457542461335</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.068866277807979</v>
+        <v>4.061156764233591</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808529</v>
+        <v>3.619937176808525</v>
       </c>
       <c r="C2018" t="n">
         <v>3.790500513806031</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.635393673105162</v>
+        <v>-3.454665801204011</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.335986620250218</v>
+        <v>2.408277769010679</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.4406949435367816</v>
+        <v>0.4278457542461335</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.0549174799281</v>
+        <v>4.047207966353711</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994894</v>
+        <v>3.656346893994891</v>
       </c>
       <c r="C2019" t="n">
         <v>3.802371002861445</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.887868827112887</v>
+        <v>-3.707140955211735</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.246867047702543</v>
+        <v>2.319158196463003</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.4406949435367816</v>
+        <v>0.4278457542461335</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.066787968983514</v>
+        <v>4.059078455409125</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358299</v>
+        <v>3.674042696358295</v>
       </c>
       <c r="C2020" t="n">
         <v>3.803581537380389</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.157341629034595</v>
+        <v>-3.976613757133443</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.140288461452803</v>
+        <v>2.212579610213264</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.4406949435367816</v>
+        <v>0.4278457542461335</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.067998503502458</v>
+        <v>4.060288989928069</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637087</v>
+        <v>3.663523617637083</v>
       </c>
       <c r="C2021" t="n">
         <v>3.80770327960771</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.314885700764036</v>
+        <v>-4.134157828862885</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.081392574988348</v>
+        <v>2.153683723748808</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.3737931383965071</v>
+        <v>0.360943949105859</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.031979162645614</v>
+        <v>4.024269649071226</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301344</v>
+        <v>3.652163313301339</v>
       </c>
       <c r="C2022" t="n">
         <v>3.802781132343899</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.59285009634731</v>
+        <v>-4.412122224446159</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.965284669491228</v>
+        <v>2.037575818251689</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.2841734041110229</v>
+        <v>0.2713242148203747</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.973285174810513</v>
+        <v>3.965575661236125</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.66797646721547</v>
+        <v>3.667976467215466</v>
       </c>
       <c r="C2023" t="n">
         <v>3.964985189042944</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.709817788986201</v>
+        <v>-4.52908991708505</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.080701649134716</v>
+        <v>2.152992797895176</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.2841734041110229</v>
+        <v>0.2713242148203747</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.135489231509558</v>
+        <v>4.127779717935169</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456693</v>
+        <v>3.696553628456689</v>
       </c>
       <c r="C2024" t="n">
         <v>3.959831827006758</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.794535731207154</v>
+        <v>-4.613807859306003</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.041661110210149</v>
+        <v>2.113952258970609</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1990573751829765</v>
+        <v>0.1862081858923283</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.079266252116544</v>
+        <v>4.071556738542155</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253289</v>
+        <v>3.750058176253284</v>
       </c>
       <c r="C2025" t="n">
         <v>3.970061244575249</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.876470549476037</v>
+        <v>-4.695742677574886</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.019116600471087</v>
+        <v>2.091407749231547</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.1891226295958963</v>
+        <v>0.1762734403052482</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.083534822332787</v>
+        <v>4.075825308758398</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717833</v>
+        <v>3.783647027717828</v>
       </c>
       <c r="C2026" t="n">
         <v>3.978986883031151</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.822732376075775</v>
+        <v>-4.642004504174624</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.049537508287094</v>
+        <v>2.121828657047554</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.2428608029961584</v>
+        <v>0.2300116137055103</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.124703364828846</v>
+        <v>4.116993851254458</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.79831094461695</v>
+        <v>3.798310944616945</v>
       </c>
       <c r="C2027" t="n">
         <v>3.971139770275327</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.712726092598554</v>
+        <v>-4.531998220697402</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.085692908922158</v>
+        <v>2.157984057682619</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.2660653749134336</v>
+        <v>0.2532161856227855</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.130778995223388</v>
+        <v>4.123069481648999</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203665</v>
+        <v>3.78557808520366</v>
       </c>
       <c r="C2028" t="n">
         <v>3.975389780997301</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.569666516857628</v>
+        <v>-4.388938644956477</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.147166749940503</v>
+        <v>2.219457898700963</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.2740788015034129</v>
+        <v>0.2612296122127648</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.13983706189935</v>
+        <v>4.13212754832496</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.77725157243693</v>
+        <v>3.777251572436926</v>
       </c>
       <c r="C2029" t="n">
         <v>3.982650663879838</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.268219791385791</v>
+        <v>-4.08749191948464</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.275006323011774</v>
+        <v>2.347297471772235</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.5755255269752502</v>
+        <v>0.562676337684602</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.327965980064988</v>
+        <v>4.3202564664906</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064769</v>
+        <v>3.812650101064763</v>
       </c>
       <c r="C2030" t="n">
         <v>3.983621841632548</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.32317498782886</v>
+        <v>-4.142447115927709</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.253995422187256</v>
+        <v>2.326286570947717</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.5755255269752502</v>
+        <v>0.562676337684602</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.328937157817698</v>
+        <v>4.32122764424331</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859303</v>
+        <v>3.821198342859297</v>
       </c>
       <c r="C2031" t="n">
         <v>3.984464746012303</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.27213661182234</v>
+        <v>-4.091408739921189</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.27525367696962</v>
+        <v>2.347544825730081</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.5755255269752502</v>
+        <v>0.562676337684602</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.329780062197454</v>
+        <v>4.322070548623065</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354686</v>
+        <v>3.831748677354681</v>
       </c>
       <c r="C2032" t="n">
         <v>4.003502844886449</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.230997316955709</v>
+        <v>-4.050269445054558</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.310747493790418</v>
+        <v>2.383038642550878</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.616664821841881</v>
+        <v>0.6038156325512328</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.373501737991578</v>
+        <v>4.365792224417189</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825767093085621</v>
+        <v>3.825767093085616</v>
       </c>
       <c r="C2033" t="n">
         <v>3.819686841010383</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.120391176876107</v>
+        <v>-3.939663304974956</v>
       </c>
       <c r="E2033" t="n">
-        <v>2.171173945946193</v>
+        <v>2.243465094706654</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.727270961921483</v>
+        <v>0.7144217726308348</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.256049418163274</v>
+        <v>4.248339904588884</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.524299771904923</v>
+        <v>3.81909815196194</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.595710968368273</v>
+        <v>3.753859693851584</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.120391176876107</v>
+        <v>-3.939663304974956</v>
       </c>
       <c r="E2034" t="n">
-        <v>2.171173945946193</v>
+        <v>2.243465094706654</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.727270961921483</v>
+        <v>0.7144217726308348</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.58877476535464</v>
+        <v>3.746923490837952</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240723.xlsx
+++ b/tame_output/ON/bt/strategyON_20240723.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>55.2%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>82.0%</t>
+          <t>87.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -829,17 +829,17 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>71.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>79.9%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-75.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.8%</t>
+          <t>111.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.5%</t>
+          <t>124.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.7%</t>
+          <t>97.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.7%</t>
+          <t>-48.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.4%</t>
+          <t>-70.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>92.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-555.5%</t>
+          <t>-557.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.5%</t>
+          <t>-34.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-43.9%</t>
+          <t>-47.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-151.9%</t>
+          <t>-143.2%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>71.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.3%</t>
+          <t>-26.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-121.6%</t>
+          <t>-109.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-152.6%</t>
+          <t>-150.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.2%</t>
+          <t>-21.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-17.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-71.3%</t>
+          <t>-55.2%</t>
         </is>
       </c>
     </row>
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.471830951507869</v>
+        <v>-7.477989729264485</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.1280733499056983</v>
+        <v>0.1256098388030513</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.171133866027758</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.414481835205938</v>
+        <v>2.422191348780327</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.658550659817172</v>
+        <v>-7.664709437573788</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.04935916204757396</v>
+        <v>0.04689565094492743</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.171133866027758</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.410455530671535</v>
+        <v>2.418165044245924</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.041552048559803</v>
+        <v>-8.047710826316418</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.1039434947710625</v>
+        <v>-0.106407005873709</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.171133866027758</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.410353429349951</v>
+        <v>2.41806294292434</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.44775050131761</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.046038493761191</v>
+        <v>-8.052197271517807</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.1031665568801881</v>
+        <v>-0.1056300679828341</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.175620311229147</v>
+        <v>-1.162771121938499</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.410233078200548</v>
+        <v>2.417942591774937</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.405568816265193</v>
+        <v>-8.411727594021809</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.2416283825837384</v>
+        <v>-0.2440918936863845</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.175620311229147</v>
+        <v>-1.162771121938499</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.415583381498598</v>
+        <v>2.423292895072987</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.455917879719415</v>
+        <v>-8.462076657476031</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.2538519880082499</v>
+        <v>-0.256315499110896</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.225969374683369</v>
+        <v>-1.213120185392721</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.393289963383242</v>
+        <v>2.400999476957631</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.553537157140811</v>
+        <v>-8.559695934897427</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.2898579483550394</v>
+        <v>-0.2923214594576855</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.323588652104766</v>
+        <v>-1.310739462814118</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.337760147552173</v>
+        <v>2.345469661126562</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.60760865664917</v>
+        <v>-8.613767434405785</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.3085929918368104</v>
+        <v>-0.311056502939457</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.377660151613125</v>
+        <v>-1.364810962322477</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.30821080416873</v>
+        <v>2.315920317743119</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.811866831979033</v>
+        <v>-8.818025609735649</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3847830648501138</v>
+        <v>-0.3872465759527599</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.505299096227114</v>
+        <v>-1.492449906936466</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.237140634518979</v>
+        <v>2.244850148093368</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.845519670487507</v>
+        <v>-8.851678448244122</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3937616457690671</v>
+        <v>-0.3962251568717132</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.605712464144152</v>
+        <v>-1.592863274853503</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.181375168253192</v>
+        <v>2.189084681827581</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.772049838820058</v>
+        <v>-8.778208616576674</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.3490020116086665</v>
+        <v>-0.3514655227113126</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.532242632476703</v>
+        <v>-1.519393443186055</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.240828768747082</v>
+        <v>2.248538282321471</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.947174256206601</v>
+        <v>-8.953333033963217</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.4044965578157669</v>
+        <v>-0.406960068918413</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.707367049863247</v>
+        <v>-1.694517860572599</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.150309339062673</v>
+        <v>2.158018852637062</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.181626350221091</v>
+        <v>-9.187785127977707</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.5054965603231589</v>
+        <v>-0.507960071425805</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.707367049863247</v>
+        <v>-1.694517860572599</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.143090174161077</v>
+        <v>2.150799687735466</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.286001081247537</v>
+        <v>-9.292159859004153</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5539186435077137</v>
+        <v>-0.5563821546103598</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.811741780889693</v>
+        <v>-1.798892591599045</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.073793144771233</v>
+        <v>2.081502658345622</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.338787236847864</v>
+        <v>-9.34494601460448</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5739173159092879</v>
+        <v>-0.5763808270119339</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.90741726747209</v>
+        <v>-1.894568078181442</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.017503642660351</v>
+        <v>2.025213156234741</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.464824030216153</v>
+        <v>-9.470982807972769</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6216383046274889</v>
+        <v>-0.624101815730135</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.882165644662348</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.035348344975311</v>
+        <v>2.0430578585497</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.407752258320222</v>
+        <v>-9.413911036076838</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5948192601827156</v>
+        <v>-0.5972827712853621</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.882165644662348</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.039338680661713</v>
+        <v>2.047048194236101</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.549424100044343</v>
+        <v>-9.555582877800958</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6529632237711054</v>
+        <v>-0.6554267348737519</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.882165644662348</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.037863453762971</v>
+        <v>2.045572967337359</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.499833255619508</v>
+        <v>-9.505992033376124</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6180734758362996</v>
+        <v>-0.6205369869389457</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.832574800237514</v>
+        <v>-1.819725610946866</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.082671370582744</v>
+        <v>2.090380884157132</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.350914921147652</v>
+        <v>-9.357073698904268</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5715572756942398</v>
+        <v>-0.5740207867968863</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.801325209502341</v>
+        <v>-1.788476020211692</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.088369991377164</v>
+        <v>2.096079504951553</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.12506976842824</v>
+        <v>-9.131228546184857</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4716401415702665</v>
+        <v>-0.4741036526729134</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.759398533915177</v>
+        <v>-1.746549344624529</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.123105069765671</v>
+        <v>2.13081458334006</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.000491112090648</v>
+        <v>-9.006649889847266</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4206695344791709</v>
+        <v>-0.4231330455818179</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.759398533915177</v>
+        <v>-1.746549344624529</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.12424421432173</v>
+        <v>2.131953727896119</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.053386400134935</v>
+        <v>-9.059545177891552</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.439193875534778</v>
+        <v>-0.4416573866374249</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.754443187826731</v>
+        <v>-1.741593998536083</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.129851196136905</v>
+        <v>2.137560709711294</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.981253224847054</v>
+        <v>-8.987412002603671</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.4046069011809887</v>
+        <v>-0.4070704122836357</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.754443187826731</v>
+        <v>-1.741593998536083</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.135584900375542</v>
+        <v>2.14329441394993</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.909886832237406</v>
+        <v>-8.916045609994024</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3857976065309954</v>
+        <v>-0.3882611176336423</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.683076795217083</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.168667473547465</v>
+        <v>2.176376987121854</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.816427798252182</v>
+        <v>-8.822586576008799</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3582974742498131</v>
+        <v>-0.36076098535246</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.683076795217083</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.158783992234558</v>
+        <v>2.166493505808947</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.549185997383784</v>
+        <v>-8.555344775140401</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2532353144018278</v>
+        <v>-0.2556988255044748</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.683076795217083</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.156949431735184</v>
+        <v>2.164658945309573</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.451278958707293</v>
+        <v>-8.457437736463911</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2143728139046921</v>
+        <v>-0.2168363250073391</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.615091045356527</v>
+        <v>-1.602241856065878</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.197440566678057</v>
+        <v>2.205150080252446</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.427325417731335</v>
+        <v>-8.433484195487953</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2041228913688156</v>
+        <v>-0.2065864024714625</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.591137504380569</v>
+        <v>-1.578288315089921</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.212481197409125</v>
+        <v>2.220190710983514</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.163265479408539</v>
+        <v>-8.169424257165156</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1117592322014489</v>
+        <v>-0.1142227433040959</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.327077566057773</v>
+        <v>-1.314228376767125</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.357656844241051</v>
+        <v>2.365366357815439</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.4561858559037</v>
+        <v>-7.462344633660318</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1682855835401855</v>
+        <v>0.1658220724375385</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.327077566057773</v>
+        <v>-1.314228376767125</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.35486981058075</v>
+        <v>2.362579324155138</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.41600155753751</v>
+        <v>-7.422160335294127</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1847029267745031</v>
+        <v>0.1822394156718561</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.286893267691582</v>
+        <v>-1.274044078400934</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.379324013488306</v>
+        <v>2.387033527062695</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.252601686598148</v>
+        <v>-7.258760464354765</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.249429696371005</v>
+        <v>0.246966185268358</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.123493396752219</v>
+        <v>-1.110644207461571</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.47673075727268</v>
+        <v>2.484440270847069</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291813</v>
+        <v>3.787330429291814</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.019120464368549</v>
+        <v>-7.025279242125166</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.350746614100697</v>
+        <v>0.34828310299805</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8900121745226208</v>
+        <v>-0.8771629852319727</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.624743919448292</v>
+        <v>2.632453433022681</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.801637122785789</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.869454073361034</v>
+        <v>-6.875612851117651</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4077209601907437</v>
+        <v>0.4052574490880967</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7971086832800849</v>
+        <v>-0.7842594939894367</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.677593803880854</v>
+        <v>2.685303317455243</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.737178599730147</v>
+        <v>-6.743337377486765</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4559986363901252</v>
+        <v>0.4535351252874782</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6648332096491982</v>
+        <v>-0.6519840203585501</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.752326574806413</v>
+        <v>2.760036088380802</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.581440267170406</v>
+        <v>-6.587599044927023</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.521109030101659</v>
+        <v>0.518645518999012</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.5090948770894567</v>
+        <v>-0.4962456877988085</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.848584635029895</v>
+        <v>2.856294148604284</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.332440468486825</v>
+        <v>-6.338599246243442</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6336152907987498</v>
+        <v>0.6311517796961028</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.5090948770894567</v>
+        <v>-0.4962456877988085</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.861490976253553</v>
+        <v>2.869200489827942</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.438030458259929</v>
+        <v>-6.444189236016546</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4634033652902896</v>
+        <v>0.4609398541876426</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.6146848668625611</v>
+        <v>-0.6018356775719129</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.670161052790472</v>
+        <v>2.677870566364861</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.456765360378526</v>
+        <v>-6.462924138135143</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5044537463199372</v>
+        <v>0.5019902352172902</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.6202808765226924</v>
+        <v>-0.6074316872320442</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.71534778887148</v>
+        <v>2.723057302445869</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710814</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.308825318970927</v>
+        <v>-6.314984096727544</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4437508401948094</v>
+        <v>0.4412873290921624</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.5999599606141348</v>
+        <v>-0.5871107713234867</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.607661415728447</v>
+        <v>2.615370929302836</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409206</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.255855796716938</v>
+        <v>-6.262014574473556</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4562246628429265</v>
+        <v>0.4537611517402795</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5469904383601459</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.630729142827362</v>
+        <v>2.638438656401751</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098111</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.212307389946248</v>
+        <v>-6.218466167702865</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4666834134561095</v>
+        <v>0.4642199023534626</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5469904383601459</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.623768530732268</v>
+        <v>2.631478044306657</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493422</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.178944183467479</v>
+        <v>-6.185102961224096</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4944910504287598</v>
+        <v>0.4920275393261129</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5469904383601459</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.638230885113412</v>
+        <v>2.645940398687801</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.070685046344957</v>
+        <v>-6.076843824101575</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5323268257369635</v>
+        <v>0.5298633146343166</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5469904383601459</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.632763005572607</v>
+        <v>2.640472519146996</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.947393911527826</v>
+        <v>-5.953552689284444</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5791413736743931</v>
+        <v>0.5766778625717461</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.4236993035430154</v>
+        <v>-0.4108501142523673</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.704235780473462</v>
+        <v>2.711945294047851</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.926244712624383</v>
+        <v>-5.932403490381001</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5953020314730955</v>
+        <v>0.5928385203704485</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.4025501046395721</v>
+        <v>-0.3897009153489239</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.724626278052853</v>
+        <v>2.732335791627242</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.682479270640939</v>
+        <v>-5.688638048397556</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6885889166135239</v>
+        <v>0.686125405510877</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.4025501046395721</v>
+        <v>-0.3897009153489239</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.720406986399904</v>
+        <v>2.728116499974293</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057526</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.580716450363644</v>
+        <v>-5.586875228120261</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7314183586444578</v>
+        <v>0.7289548475418108</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.3893310362471434</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.730462741355377</v>
+        <v>2.738172254929766</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.330866056414569</v>
+        <v>-5.337024834171187</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8241005912077899</v>
+        <v>0.8216370801051429</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.3893310362471434</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.723204816339079</v>
+        <v>2.730914329913468</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011498</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.154973963947137</v>
+        <v>-5.161132741703755</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8980565517154115</v>
+        <v>0.8955930406127646</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.3893310362471434</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.726803939859728</v>
+        <v>2.734513453434117</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.983527500924674</v>
+        <v>-4.989686278681291</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9799626429789505</v>
+        <v>0.9774991318763036</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.2178845732246802</v>
+        <v>-0.2050353839340321</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.84299932372776</v>
+        <v>2.850708837302149</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376522263278</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.909237935186335</v>
+        <v>-4.915396712942952</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.008698946890583</v>
+        <v>1.006235435787936</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.143595007486341</v>
+        <v>-0.1307458181956928</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.88659354078706</v>
+        <v>2.894303054361449</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.8456021929524</v>
+        <v>-4.851760970709018</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.038848044838474</v>
+        <v>1.036384533735827</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.07995926525240643</v>
+        <v>-0.06711007596175828</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.929469787181738</v>
+        <v>2.937179300756127</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.73417543362648</v>
+        <v>-4.740334211383098</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.064613007352638</v>
+        <v>1.062149496249991</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.07995926525240643</v>
+        <v>-0.06711007596175828</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.910664045965534</v>
+        <v>2.918373559539923</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242292</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.49374493682162</v>
+        <v>-4.499903714578237</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.162528282699459</v>
+        <v>1.160064771596812</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.1604712315524539</v>
+        <v>0.173320420843102</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.056665420673327</v>
+        <v>3.064374934247716</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367681</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.421502368650425</v>
+        <v>-4.427661146407043</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.195354623802757</v>
+        <v>1.192891112700111</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.1604712315524539</v>
+        <v>0.173320420843102</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.060594734508147</v>
+        <v>3.068304248082536</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.40378868177256</v>
+        <v>-4.409947459529177</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.203118682471244</v>
+        <v>1.200655171368597</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.1636525604493707</v>
+        <v>0.1765017497400188</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.063182115763638</v>
+        <v>3.070891629338026</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502333</v>
+        <v>3.848616626502335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.340423249819815</v>
+        <v>-4.30114257404945</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.225462926472335</v>
+        <v>1.241175196780481</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.1636525604493707</v>
+        <v>0.1765017497400188</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.060180186983631</v>
+        <v>3.06788970055802</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675934</v>
+        <v>3.818668951675936</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.120402451782804</v>
+        <v>-4.08112177601244</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.315050282697753</v>
+        <v>1.330762553005899</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3048724055173509</v>
+        <v>0.3177215948079991</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.146491131035033</v>
+        <v>3.154200644609422</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539946</v>
+        <v>3.843274527539948</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.987534762719526</v>
+        <v>-3.948254086949162</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.384091541124888</v>
+        <v>1.399803811433034</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3048724055173509</v>
+        <v>0.3177215948079991</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.162385313836857</v>
+        <v>3.170094827411245</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496259</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.867361679355027</v>
+        <v>-3.828081003584662</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.43330661891099</v>
+        <v>1.449018889219135</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4250454888818498</v>
+        <v>0.437894678172498</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.235635008295858</v>
+        <v>3.243344521870247</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.72268953425529</v>
+        <v>-3.683408858484925</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.501263579512324</v>
+        <v>1.51697584982047</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.5697176339815873</v>
+        <v>0.5825668232722354</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.33252639791714</v>
+        <v>3.340235911491529</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942101</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.782564361612982</v>
+        <v>-3.743283685842617</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.463351139970673</v>
+        <v>1.479063410278819</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5098428066238951</v>
+        <v>0.5226919959145433</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.282638992903951</v>
+        <v>3.29034850647834</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674511</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.662744130702145</v>
+        <v>-3.62346345493178</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.526568401569217</v>
+        <v>1.542280671877363</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5098428066238951</v>
+        <v>0.5226919959145433</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.297928162138159</v>
+        <v>3.305637675712548</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430689</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.665213837163951</v>
+        <v>-3.625933161393586</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.433224718306936</v>
+        <v>1.448936988615082</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5073731001620889</v>
+        <v>0.5202222894527371</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.204090537583517</v>
+        <v>3.211800051157906</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003597</v>
+        <v>3.743220196003599</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.73358402348796</v>
+        <v>-3.694303347717596</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.325138505262633</v>
+        <v>1.340850775570779</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5166487991983039</v>
+        <v>0.529497988488952</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.128917818490547</v>
+        <v>3.136627332064936</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508365</v>
+        <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.747372076335007</v>
+        <v>-3.708091400564642</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.310059992755706</v>
+        <v>1.325772263063852</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5166487991983039</v>
+        <v>0.529497988488952</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.119354527122439</v>
+        <v>3.127064040696828</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417699</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.802892152227597</v>
+        <v>-3.763611476457232</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.424882799090873</v>
+        <v>1.440595069399018</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5166487991983039</v>
+        <v>0.529497988488952</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.256385363814641</v>
+        <v>3.26409487738903</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205894</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.627417892435127</v>
+        <v>-3.588137216664763</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.499639734999648</v>
+        <v>1.515352005307794</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5166487991983039</v>
+        <v>0.529497988488952</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.260952595806429</v>
+        <v>3.268662109380818</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225438</v>
+        <v>3.76502432322544</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.738354145076376</v>
+        <v>-3.699073469306011</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.431007262704356</v>
+        <v>1.446719533012502</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5166487991983039</v>
+        <v>0.529497988488952</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.236694624567636</v>
+        <v>3.244404138142025</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111292</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.704690599604094</v>
+        <v>-3.665409923833729</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.373010994294718</v>
+        <v>1.388723264602864</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5503123446705858</v>
+        <v>0.5631615339612339</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.185431065252455</v>
+        <v>3.193140578826844</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264161</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.644837980400371</v>
+        <v>-3.605557304630006</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.40712442840834</v>
+        <v>1.422836698716486</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5503123446705858</v>
+        <v>0.5631615339612339</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.195603451684587</v>
+        <v>3.203312965258976</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742297</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.558594517373994</v>
+        <v>-3.519313841603629</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.436568084192751</v>
+        <v>1.452280354500897</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5503123446705858</v>
+        <v>0.5631615339612339</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.190549722258448</v>
+        <v>3.198259235832837</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316044</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.603901336772974</v>
+        <v>-3.564620661002609</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.410221131877685</v>
+        <v>1.425933402185831</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.509502181661355</v>
+        <v>0.5223513709520031</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.157839399897434</v>
+        <v>3.165548913471823</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.632934441475275</v>
+        <v>-3.59365376570491</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.399159763029866</v>
+        <v>1.414872033338011</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.509502181661355</v>
+        <v>0.5223513709520031</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.158391272930536</v>
+        <v>3.166100786504925</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809496</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.540123960024416</v>
+        <v>-3.500843284254051</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.365556647501575</v>
+        <v>1.381268917809721</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6023126631122143</v>
+        <v>0.6151618524028625</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.143350253692417</v>
+        <v>3.151059767266806</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560423</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.584513429353843</v>
+        <v>-3.545232753583479</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.349674335694405</v>
+        <v>1.365386606002551</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.5579231937827867</v>
+        <v>0.5707723830734348</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.118590048019362</v>
+        <v>3.126299561593751</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472734</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.471842211117593</v>
+        <v>-3.432561535347229</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.389818531500628</v>
+        <v>1.405530801808774</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6705944120190368</v>
+        <v>0.683443601309685</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.181268487472835</v>
+        <v>3.188978001047224</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798534</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.359465209934921</v>
+        <v>-3.320184534164556</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.440260627804364</v>
+        <v>1.45597289811251</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6705944120190368</v>
+        <v>0.683443601309685</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.186759783303502</v>
+        <v>3.194469296877891</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498861</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.387245607836274</v>
+        <v>-3.347964932065909</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.440645670412362</v>
+        <v>1.456357940720508</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6428140141176837</v>
+        <v>0.6556632034083318</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.181588746331229</v>
+        <v>3.189298259905618</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.505626280566412</v>
+        <v>-3.466345604796047</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.23164912132096</v>
+        <v>1.247361391629106</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5755961619667075</v>
+        <v>0.5884453512573556</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.979613755041297</v>
+        <v>2.987323268615686</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729265</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.614240359009743</v>
+        <v>-3.574959683239379</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.308353150662833</v>
+        <v>1.324065420970979</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5755961619667075</v>
+        <v>0.5884453512573556</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.099763415760502</v>
+        <v>3.107472929334891</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190764</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.5788313207616</v>
+        <v>-3.539550644991236</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.337029792064413</v>
+        <v>1.352742062372559</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5755961619667075</v>
+        <v>0.5884453512573556</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.114276441862825</v>
+        <v>3.121985955437214</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913422</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.540447658203449</v>
+        <v>-3.501166982433085</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.349802698430042</v>
+        <v>1.365514968738188</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6139798245248587</v>
+        <v>0.6268290138155068</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.134726080740085</v>
+        <v>3.142435594314474</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532482</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.363331328168283</v>
+        <v>-3.324050652397919</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.417378259289411</v>
+        <v>1.433090529597556</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6139798245248587</v>
+        <v>0.6268290138155068</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.131455109585386</v>
+        <v>3.139164623159775</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793899</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.408423573001829</v>
+        <v>-3.369142897231464</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.400024753117905</v>
+        <v>1.415737023426051</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5520837813554689</v>
+        <v>0.564932970646117</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.095000875445666</v>
+        <v>3.102710389020055</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011231</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.229048151763061</v>
+        <v>-3.189767475992697</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.465561896919827</v>
+        <v>1.481274167227973</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7088605395261875</v>
+        <v>0.7217097288168357</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.182853905654512</v>
+        <v>3.190563419228901</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982225</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.274062365283668</v>
+        <v>-3.234781689513303</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.428363666843174</v>
+        <v>1.44407593715132</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6785116442115829</v>
+        <v>0.6913608335022311</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.145452023797338</v>
+        <v>3.153161537371727</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509533</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.541066875556103</v>
+        <v>-3.501786199785738</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.327253425073146</v>
+        <v>1.342965695381292</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4841486061686344</v>
+        <v>0.4969977954592826</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.034525763310515</v>
+        <v>3.042235276884904</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.642264656993276</v>
+        <v>-3.602983981222911</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.285978234394778</v>
+        <v>1.301690504702924</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4157397926233152</v>
+        <v>0.4285889819139634</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.992684397079825</v>
+        <v>3.000393910654214</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.635753690378963</v>
+        <v>-3.596473014608598</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.28618258259482</v>
+        <v>1.301894852902966</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4157397926233152</v>
+        <v>0.4285889819139634</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.990284358634141</v>
+        <v>2.99799387220853</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.616715562671666</v>
+        <v>-3.577434886901301</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.290322552885984</v>
+        <v>1.306034823194129</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3575561812921206</v>
+        <v>0.3704053705827688</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.95189891104367</v>
+        <v>2.959608424618059</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131249</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.914947071207078</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.647842193822284</v>
+        <v>-3.608561518051919</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.455453769364417</v>
+        <v>1.471166039672563</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3575561812921206</v>
+        <v>0.3704053705827688</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.12948077998235</v>
+        <v>3.137190293556739</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067865</v>
       </c>
       <c r="C1964" t="n">
         <v>2.915780400193211</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.661708955156201</v>
+        <v>-3.622428279385836</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.450740393816984</v>
+        <v>1.466452664125129</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3196982645582977</v>
+        <v>0.3325474538489459</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.10759935892819</v>
+        <v>3.115308872502579</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.921788930590137</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.616904783616271</v>
+        <v>-3.577624107845907</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.474670592829881</v>
+        <v>1.490382863138027</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3196982645582977</v>
+        <v>0.3325474538489459</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.113607889325116</v>
+        <v>3.121317402899505</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.819739151867337</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.469161813381269</v>
+        <v>-3.429881137610904</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.431718002201082</v>
+        <v>1.447430272509228</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4875056217931809</v>
+        <v>0.5003548110838291</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.112242524943245</v>
+        <v>3.119952038517634</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
         <v>2.822532773398818</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.57117649591249</v>
+        <v>-3.531895820142125</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.393705750720074</v>
+        <v>1.40941802102822</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4875056217931809</v>
+        <v>0.5003548110838291</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.115036146474726</v>
+        <v>3.122745660049115</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.823195121790476</v>
+        <v>2.916989965414152</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.565023789859706</v>
+        <v>-3.623039882840909</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.396829181532846</v>
+        <v>1.467417587964041</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4936583278459652</v>
+        <v>0.4092107483850456</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.119390118498055</v>
+        <v>3.16251641444518</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.822275598530586</v>
+        <v>2.916070442154262</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.581833088010207</v>
+        <v>-3.63984918099141</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.389185939012756</v>
+        <v>1.459774345443951</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4768490296954636</v>
+        <v>0.3924014502345439</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.108385016347865</v>
+        <v>3.151511312294989</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.888611152327407</v>
+        <v>2.982405995951083</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.519535089234085</v>
+        <v>-3.577551182215288</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.480440692320026</v>
+        <v>1.551029098751221</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4768490296954636</v>
+        <v>0.3924014502345439</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.174720570144685</v>
+        <v>3.21784686609181</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.690903154041534</v>
+        <v>2.78469799766521</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.317744891568927</v>
+        <v>-3.37576098455013</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.363448773100216</v>
+        <v>1.434037179531411</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6748672218646179</v>
+        <v>0.5904196424036983</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.095823487160305</v>
+        <v>3.13894978310743</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.761193386363709</v>
+        <v>2.854988229987386</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.368631604255122</v>
+        <v>-3.426647697236325</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.413384320347913</v>
+        <v>1.483972726779108</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.6239805091784234</v>
+        <v>0.5395329297175038</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.135581691870764</v>
+        <v>3.178707987817888</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.775821122479753</v>
+        <v>2.869615966103429</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.466372148880096</v>
+        <v>-3.5243882418613</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.388915838613967</v>
+        <v>1.459504245045162</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6080912310454432</v>
+        <v>0.5236436515845235</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.140675861107019</v>
+        <v>3.183802157054143</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.774357103304425</v>
+        <v>2.868151946928101</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.642709909003026</v>
+        <v>-3.700726001984229</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.316916715389467</v>
+        <v>1.387505121820662</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.4317534709225138</v>
+        <v>0.3473058914615941</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.033409185857933</v>
+        <v>3.076535481805058</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.772848721344353</v>
+        <v>2.86664356496803</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.566287862571099</v>
+        <v>-3.624303955552302</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.345977152002166</v>
+        <v>1.416565558433361</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.4317534709225138</v>
+        <v>0.3473058914615941</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.031900803897862</v>
+        <v>3.075027099844986</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.77271158877979</v>
+        <v>2.866506432403466</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.52191473093253</v>
+        <v>-3.579930823913733</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.36358927209303</v>
+        <v>1.434177678524225</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.4761266025610824</v>
+        <v>0.3916790231001627</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.058387550316439</v>
+        <v>3.101513846263563</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105968</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.76710538291838</v>
+        <v>2.860900226542056</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.399080510045363</v>
+        <v>-3.457096603026566</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.407116754586488</v>
+        <v>1.477705161017683</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.4761266025610824</v>
+        <v>0.3916790231001627</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.05278134445503</v>
+        <v>3.095907640402154</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190326</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.773487139946185</v>
+        <v>2.86728198356986</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.351424779484307</v>
+        <v>-3.409440872465511</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.432560803838715</v>
+        <v>1.503149210269909</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.5237823331221381</v>
+        <v>0.4393347536612184</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.087756539819468</v>
+        <v>3.130882835766592</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.778379513320909</v>
+        <v>2.872174356944585</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.250906620985552</v>
+        <v>-3.308922713966756</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.477660440612941</v>
+        <v>1.548248847044136</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.6243004916208926</v>
+        <v>0.5398529121599729</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.152959808293445</v>
+        <v>3.196086104240569</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557292</v>
+        <v>3.828808877557294</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.765134185796782</v>
+        <v>2.858929029420457</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.311573211387941</v>
+        <v>-3.369589304369145</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.440148476927858</v>
+        <v>1.510736883359052</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.542602174902359</v>
+        <v>0.4581545954414392</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.090695490738197</v>
+        <v>3.133821786685321</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.76923188840741</v>
+        <v>2.863026732031086</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.266734809779543</v>
+        <v>-3.324750902760747</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.462181540181846</v>
+        <v>1.53276994661304</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.5471456078472284</v>
+        <v>0.4626980283863087</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.097519253115748</v>
+        <v>3.140645549062872</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.773392828038488</v>
+        <v>2.867187671662164</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.286233266021552</v>
+        <v>-3.344249359002755</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.45854309731612</v>
+        <v>1.529131503747315</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.4990609665673241</v>
+        <v>0.4146133871064044</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.072829407978883</v>
+        <v>3.115955703926007</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.779272430566325</v>
+        <v>2.873067274190001</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.242030428935651</v>
+        <v>-3.300046521916855</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.482103834678318</v>
+        <v>1.552692241109512</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.5432638036532246</v>
+        <v>0.4588162241923048</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.105230712758261</v>
+        <v>3.148357008705384</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.777682431035573</v>
+        <v>2.871477274659249</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.279009456599094</v>
+        <v>-3.337025549580298</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.465722224082188</v>
+        <v>1.536310630513382</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.5802377054445551</v>
+        <v>0.4957901259836354</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.125825054302307</v>
+        <v>3.16895135024943</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.828930196218613</v>
+        <v>2.922725039842288</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.120718039059822</v>
+        <v>-3.178734132041026</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.580286556280937</v>
+        <v>1.650874962712131</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.5802377054445551</v>
+        <v>0.4957901259836354</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.177072819485346</v>
+        <v>3.22019911543247</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.827370900812866</v>
+        <v>2.921165744436542</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.913076035425346</v>
+        <v>-2.971092128406549</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.66178406232898</v>
+        <v>1.732372468760174</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.7878797090790313</v>
+        <v>0.7034321296181115</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.300098726260285</v>
+        <v>3.343225022207409</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475138</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.822319129051136</v>
+        <v>2.916113972674812</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.862043942702818</v>
+        <v>-2.920060035684021</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.677145127656261</v>
+        <v>1.747733534087456</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.8389118018015592</v>
+        <v>0.7544642223406395</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.325666210132072</v>
+        <v>3.368792506079195</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.839506533143841</v>
+        <v>2.933301376767516</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.796819761575613</v>
+        <v>-2.854835854556816</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.720422204199848</v>
+        <v>1.791010610631043</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.9041359829287648</v>
+        <v>0.8196884034678451</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.3819881229011</v>
+        <v>3.425114418848224</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882554</v>
+        <v>3.840061186882557</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.835467505443121</v>
+        <v>2.929262349066797</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.759392741504479</v>
+        <v>-2.817408834485682</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.731353984527582</v>
+        <v>1.801942390958777</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.9093875209579465</v>
+        <v>0.8249399414970268</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.381100018017889</v>
+        <v>3.424226313965013</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992657</v>
+        <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.836724297774361</v>
+        <v>2.930519141398037</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.779504397539187</v>
+        <v>-2.886151317582024</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.724566114444939</v>
+        <v>1.77570219005148</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.9204148659553657</v>
+        <v>0.8534014165888318</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.388973217347581</v>
+        <v>3.442559991351336</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636284</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.997282068795572</v>
+        <v>3.091076912419248</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.725759583111982</v>
+        <v>-2.832406503154819</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.906621811237032</v>
+        <v>1.957757886843573</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9304781753958277</v>
+        <v>0.8634647260292938</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.555568974033069</v>
+        <v>3.609155748036824</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957625</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.117394978013389</v>
+        <v>3.211189821637065</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.65097732208697</v>
+        <v>-2.757624242129807</v>
       </c>
       <c r="E1992" t="n">
-        <v>2.056647624864854</v>
+        <v>2.107783700471395</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.00526043642084</v>
+        <v>0.9382469870543064</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.720551239865894</v>
+        <v>3.774138013869649</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998752</v>
+        <v>3.814230727998756</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.109102954027248</v>
+        <v>3.202897797650924</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.624893237823162</v>
+        <v>-2.731540157865999</v>
       </c>
       <c r="E1993" t="n">
-        <v>2.058789234584236</v>
+        <v>2.109925310190778</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.00526043642084</v>
+        <v>0.9382469870543064</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.712259215879753</v>
+        <v>3.765845989883508</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896926</v>
+        <v>3.803397818896929</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.107296149611028</v>
+        <v>3.201090993234704</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.546762056974215</v>
+        <v>-2.653408977017052</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.088234902507595</v>
+        <v>2.139370978114136</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.079437247304525</v>
+        <v>1.012423797937991</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.754958497993743</v>
+        <v>3.808545271997498</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959854</v>
+        <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.124850555337819</v>
+        <v>3.218645398961495</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.537869595580932</v>
+        <v>-2.644516515623769</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.109346292791699</v>
+        <v>2.16048236839824</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.079437247304525</v>
+        <v>1.012423797937991</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.772512903720534</v>
+        <v>3.82609967772429</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945362</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.116705602742403</v>
+        <v>3.210500446366079</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.70634571255081</v>
+        <v>-2.812992632593647</v>
       </c>
       <c r="E1996" t="n">
-        <v>2.033810893408332</v>
+        <v>2.084946969014873</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.051489411587944</v>
+        <v>0.9844759622214101</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.74759924969517</v>
+        <v>3.801186023698925</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782704</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.097975299930265</v>
+        <v>3.191770143553941</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.008546183689226</v>
+        <v>-2.115193103732063</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.294200402140827</v>
+        <v>2.345336477747368</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.9811413522175334</v>
+        <v>0.9141279028509994</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.686660111260785</v>
+        <v>3.740246885264541</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632632</v>
+        <v>3.784671345632636</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.08863932242717</v>
+        <v>3.182434166050845</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.985825080006074</v>
+        <v>-2.092472000048911</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.293952866110993</v>
+        <v>2.345088941717534</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.9811413522175334</v>
+        <v>0.9141279028509994</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.67732413375769</v>
+        <v>3.730910907761445</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777669</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.247545448278339</v>
+        <v>3.341340291902014</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.115026893300116</v>
+        <v>-2.221673813342953</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.401178266644545</v>
+        <v>2.452314342251086</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.8519395389234912</v>
+        <v>0.7849260895569572</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.758709171632434</v>
+        <v>3.812295945636189</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644408</v>
+        <v>3.779933725644412</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.284623270771985</v>
+        <v>3.378418114395661</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.269807900078372</v>
+        <v>-2.376454820121209</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.376343686426889</v>
+        <v>2.42747976203343</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.818571864869015</v>
+        <v>0.751558415502481</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.775766389693394</v>
+        <v>3.82935316369715</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799964</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.28129862676153</v>
+        <v>3.375093470385206</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.262753209863198</v>
+        <v>-2.369400129906035</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.375840918502504</v>
+        <v>2.426976994109045</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.8256265550841888</v>
+        <v>0.7586131057176548</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.776674559812044</v>
+        <v>3.830261333815799</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331113</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.291304780406272</v>
+        <v>3.385099624029948</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.23580198553671</v>
+        <v>-2.342448905579547</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.39662756187784</v>
+        <v>2.447763637484381</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.840506901111908</v>
+        <v>0.773493451745374</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.795608921073417</v>
+        <v>3.849195695077172</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.475407912551232</v>
+        <v>3.569202756174907</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.371754993593027</v>
+        <v>-2.478401913635864</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.526349490800274</v>
+        <v>2.577485566406815</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.840506901111908</v>
+        <v>0.773493451745374</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.979712053218377</v>
+        <v>4.033298827222132</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714427</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.467524607454225</v>
+        <v>3.5613194510779</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.394163111397899</v>
+        <v>-2.500810031440736</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.509502938581318</v>
+        <v>2.560639014187859</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.840506901111908</v>
+        <v>0.773493451745374</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.97182874812137</v>
+        <v>4.025415522125125</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155029</v>
+        <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.469578607003862</v>
+        <v>3.563373450627538</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.542168878877298</v>
+        <v>-2.648815798920135</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.452354631139196</v>
+        <v>2.503490706745737</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.7537798922483665</v>
+        <v>0.6867664428818325</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.921846542352882</v>
+        <v>3.975433316356638</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161974</v>
+        <v>3.729452285161978</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.525832324725709</v>
+        <v>3.619627168349385</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.551609804765828</v>
+        <v>-2.658256724808665</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.504831978505631</v>
+        <v>2.555968054112172</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.8762070097917579</v>
+        <v>0.8091935604252239</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.051556530600764</v>
+        <v>4.105143304604519</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321631</v>
+        <v>3.714941193321635</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.52872341927101</v>
+        <v>3.622518262894686</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.60388341210147</v>
+        <v>-2.710530332144307</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.486813630116675</v>
+        <v>2.537949705723216</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.8239334024561167</v>
+        <v>0.7569199530895827</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.02308346074468</v>
+        <v>4.076670234748436</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.526835232164785</v>
+        <v>3.620630075788461</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.680213389702375</v>
+        <v>-2.786860309745212</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.454393451970088</v>
+        <v>2.505529527576629</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.8239334024561167</v>
+        <v>0.7569199530895827</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.021195273638456</v>
+        <v>4.074782047642211</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.521655461767648</v>
+        <v>3.615450305391323</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.791970342317676</v>
+        <v>-2.898617262360514</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.40451090052683</v>
+        <v>2.455646976133371</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.7121764498408156</v>
+        <v>0.6451630004742817</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.948961331672137</v>
+        <v>4.002548105675893</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343062</v>
+        <v>3.712897612343066</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.5200894719778</v>
+        <v>3.613884315601476</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.790129323259425</v>
+        <v>-2.896776243302262</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.403681318360283</v>
+        <v>2.454817393966824</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.713444676512284</v>
+        <v>0.6464312271457501</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.948156277885171</v>
+        <v>4.001743051888926</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647102</v>
+        <v>3.754911907647106</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.533162878843719</v>
+        <v>3.626957722467394</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.922430615356979</v>
+        <v>-3.029077535399816</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.36383420838718</v>
+        <v>2.414970283993721</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.713444676512284</v>
+        <v>0.6464312271457501</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.961229684751089</v>
+        <v>4.014816458754844</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74989685176353</v>
+        <v>3.749896851763533</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.533162878843719</v>
+        <v>3.626957722467394</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.923992258171839</v>
+        <v>-3.030639178214676</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.363209551261236</v>
+        <v>2.414345626867777</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.713444676512284</v>
+        <v>0.6464312271457501</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.961229684751089</v>
+        <v>4.014816458754844</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392113</v>
+        <v>3.715834055392117</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.531686919970721</v>
+        <v>3.625481763594396</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.951893045281312</v>
+        <v>-3.058539965324149</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.350573277544449</v>
+        <v>2.40170935315099</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6788477523693492</v>
+        <v>0.6118343030028153</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.93899557139233</v>
+        <v>3.992582345396086</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172524</v>
+        <v>3.684909939172528</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.528451363947919</v>
+        <v>3.622246207571595</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.074419147984206</v>
+        <v>-3.181066068027043</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.29832728044049</v>
+        <v>2.349463356047031</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5563216496664554</v>
+        <v>0.4893082002999214</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.862244353747793</v>
+        <v>3.915831127751548</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971075</v>
+        <v>3.619362241971079</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.595157323538423</v>
+        <v>3.688952167162099</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.094480469260712</v>
+        <v>-3.201127389303549</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.357008711520391</v>
+        <v>2.408144787126932</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5362603283899483</v>
+        <v>0.4692468790234144</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.916913520572392</v>
+        <v>3.970500294576148</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199803</v>
+        <v>3.640764248199806</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.73546904254027</v>
+        <v>3.829263886163946</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.351201287255536</v>
+        <v>-3.457848207298373</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.394632103324308</v>
+        <v>2.445768178930849</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4278457542461335</v>
+        <v>0.3608323048795996</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.992176495087951</v>
+        <v>4.045763269091706</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622233</v>
+        <v>3.668303164622237</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.80444931168591</v>
+        <v>3.898244155309586</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.505187705031677</v>
+        <v>-3.611834625074514</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.402017805359492</v>
+        <v>2.453153880966033</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4278457542461335</v>
+        <v>0.3608323048795996</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.061156764233591</v>
+        <v>4.114743538237346</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808525</v>
+        <v>3.619937176808529</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.790500513806031</v>
+        <v>3.884295357429707</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.454665801204011</v>
+        <v>-3.561312721246848</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.408277769010679</v>
+        <v>2.45941384461722</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.4278457542461335</v>
+        <v>0.3608323048795996</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.047207966353711</v>
+        <v>4.100794740357466</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994891</v>
+        <v>3.656346893994894</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.802371002861445</v>
+        <v>3.896165846485121</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.707140955211735</v>
+        <v>-3.813787875254572</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.319158196463003</v>
+        <v>2.370294272069544</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.4278457542461335</v>
+        <v>0.3608323048795996</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.059078455409125</v>
+        <v>4.11266522941288</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358295</v>
+        <v>3.674042696358299</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.803581537380389</v>
+        <v>3.897376381004064</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.976613757133443</v>
+        <v>-4.08326067717628</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.212579610213264</v>
+        <v>2.263715685819805</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.4278457542461335</v>
+        <v>0.3608323048795996</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.060288989928069</v>
+        <v>4.113875763931825</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637083</v>
+        <v>3.663523617637087</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.80770327960771</v>
+        <v>3.901498123231386</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.134157828862885</v>
+        <v>-4.240804748905722</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.153683723748808</v>
+        <v>2.20481979935535</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.360943949105859</v>
+        <v>0.2939304997393251</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.024269649071226</v>
+        <v>4.077856423074981</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301339</v>
+        <v>3.652163313301343</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.802781132343899</v>
+        <v>3.896575975967575</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.412122224446159</v>
+        <v>-4.518769144488996</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.037575818251689</v>
+        <v>2.08871189385823</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.2713242148203747</v>
+        <v>0.2043107654538408</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.965575661236125</v>
+        <v>4.01916243523988</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215466</v>
+        <v>3.667976467215469</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.964985189042944</v>
+        <v>4.058780032666619</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.52908991708505</v>
+        <v>-4.635736837127887</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.152992797895176</v>
+        <v>2.204128873501717</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.2713242148203747</v>
+        <v>0.2043107654538408</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.127779717935169</v>
+        <v>4.181366491938924</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456689</v>
+        <v>3.696553628456692</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.959831827006758</v>
+        <v>4.053626670630433</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.613807859306003</v>
+        <v>-4.72045477934884</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.113952258970609</v>
+        <v>2.16508833457715</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1862081858923283</v>
+        <v>0.1191947365257944</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.071556738542155</v>
+        <v>4.12514351254591</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253284</v>
+        <v>3.750058176253288</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.970061244575249</v>
+        <v>4.063856088198925</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.695742677574886</v>
+        <v>-4.802389597617723</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.091407749231547</v>
+        <v>2.142543824838088</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.1762734403052482</v>
+        <v>0.1092599909387142</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.075825308758398</v>
+        <v>4.129412082762154</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717828</v>
+        <v>3.783647027717832</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.978986883031151</v>
+        <v>4.072781726654827</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.642004504174624</v>
+        <v>-4.748651424217461</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.121828657047554</v>
+        <v>2.172964732654095</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.2300116137055103</v>
+        <v>0.1629981643389763</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.116993851254458</v>
+        <v>4.170580625258213</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616945</v>
+        <v>3.798310944616949</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.971139770275327</v>
+        <v>4.064934613899003</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.531998220697402</v>
+        <v>-4.638645140740239</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.157984057682619</v>
+        <v>2.20912013328916</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.2532161856227855</v>
+        <v>0.1862027362562516</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.123069481648999</v>
+        <v>4.176656255652754</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.78557808520366</v>
+        <v>3.785578085203664</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.975389780997301</v>
+        <v>4.069184624620977</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.388938644956477</v>
+        <v>-4.495585564999313</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.219457898700963</v>
+        <v>2.270593974307505</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.2612296122127648</v>
+        <v>0.1942161628462308</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.13212754832496</v>
+        <v>4.185714322328716</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436926</v>
+        <v>3.77725157243693</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.982650663879838</v>
+        <v>4.076445507503514</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.08749191948464</v>
+        <v>-4.194138839527476</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.347297471772235</v>
+        <v>2.398433547378776</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.562676337684602</v>
+        <v>0.495662888318068</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.3202564664906</v>
+        <v>4.373843240494355</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064763</v>
+        <v>3.812650101064767</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.983621841632548</v>
+        <v>4.077416685256224</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.142447115927709</v>
+        <v>-4.249094035970545</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.326286570947717</v>
+        <v>2.377422646554258</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.562676337684602</v>
+        <v>0.495662888318068</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.32122764424331</v>
+        <v>4.374814418247065</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859297</v>
+        <v>3.821198342859301</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.984464746012303</v>
+        <v>4.078259589635979</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.091408739921189</v>
+        <v>-4.198055659964025</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.347544825730081</v>
+        <v>2.398680901336622</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.562676337684602</v>
+        <v>0.495662888318068</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.322070548623065</v>
+        <v>4.375657322626821</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354681</v>
+        <v>3.831748677354684</v>
       </c>
       <c r="C2032" t="n">
-        <v>4.003502844886449</v>
+        <v>4.097297688510125</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.050269445054558</v>
+        <v>-4.156916365097394</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.383038642550878</v>
+        <v>2.43417471815742</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.6038156325512328</v>
+        <v>0.5368021831846989</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.365792224417189</v>
+        <v>4.419378998420944</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825767093085616</v>
+        <v>3.825767093085618</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.819686841010383</v>
+        <v>3.913481684634059</v>
       </c>
       <c r="D2033" t="n">
-        <v>-3.939663304974956</v>
+        <v>-3.957995942892016</v>
       </c>
       <c r="E2033" t="n">
-        <v>2.243465094706654</v>
+        <v>2.329926883163505</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.7144217726308348</v>
+        <v>0.7357226053900766</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.248339904588884</v>
+        <v>4.354915247868106</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.81909815196194</v>
+        <v>3.833113332332212</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.753859693851584</v>
+        <v>3.915464848498096</v>
       </c>
       <c r="D2034" t="n">
-        <v>-3.939663304974956</v>
+        <v>-3.957995942892016</v>
       </c>
       <c r="E2034" t="n">
-        <v>2.243465094706654</v>
+        <v>2.329926883163505</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.7144217726308348</v>
+        <v>0.7357226053900766</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.746923490837952</v>
+        <v>3.908528645484464</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240723.xlsx
+++ b/tame_output/ON/bt/strategyON_20240723.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -671,17 +671,17 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>28.5%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>87.3%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -829,52 +829,52 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>71.0%</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>31.4%</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>61.6%</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>31.7%</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>79.9%</t>
+          <t>51.3%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.2%</t>
+          <t>-74.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.2%</t>
+          <t>110.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.7%</t>
+          <t>123.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.4%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.4%</t>
+          <t>-48.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.6%</t>
+          <t>-70.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.2%</t>
+          <t>91.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>456.6%</t>
+          <t>453.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-557.4%</t>
+          <t>-555.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.3%</t>
+          <t>-34.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-47.6%</t>
+          <t>-47.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-143.2%</t>
+          <t>-151.7%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>70.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.8%</t>
+          <t>-27.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-109.3%</t>
+          <t>-121.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-150.4%</t>
+          <t>-152.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.0%</t>
+          <t>-22.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-55.2%</t>
+          <t>-83.8%</t>
         </is>
       </c>
     </row>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297743</v>
+        <v>3.458100091297742</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626472</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291814</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785789</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76318224839043</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105953</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607645</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710814</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409206</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098111</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493422</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318093</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057526</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011498</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392986</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.77376522263278</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.821593509367681</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879963</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675936</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.08112177601244</v>
+        <v>-4.262341880119591</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.330762553005899</v>
+        <v>1.258274511363039</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3177215948079991</v>
+        <v>0.1941407303852369</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.154200644609422</v>
+        <v>3.080052125955765</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539948</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.948254086949162</v>
+        <v>-4.129474191056313</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.399803811433034</v>
+        <v>1.327315769790173</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3177215948079991</v>
+        <v>0.1941407303852369</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.170094827411245</v>
+        <v>3.095946308757588</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.828081003584662</v>
+        <v>-4.009301107691814</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.449018889219135</v>
+        <v>1.376530847576275</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.437894678172498</v>
+        <v>0.3143138137497358</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.243344521870247</v>
+        <v>3.169196003216589</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.683408858484925</v>
+        <v>-3.864628962592077</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.51697584982047</v>
+        <v>1.444487808177609</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.5825668232722354</v>
+        <v>0.4589859588494732</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.340235911491529</v>
+        <v>3.266087392837872</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.743283685842617</v>
+        <v>-3.924503789949769</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.479063410278819</v>
+        <v>1.406575368635958</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5226919959145433</v>
+        <v>0.3991111314917811</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.29034850647834</v>
+        <v>3.216199987824682</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.62346345493178</v>
+        <v>-3.804683559038932</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.542280671877363</v>
+        <v>1.469792630234502</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5226919959145433</v>
+        <v>0.3991111314917811</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.305637675712548</v>
+        <v>3.231489157058891</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.625933161393586</v>
+        <v>-3.807153265500738</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.448936988615082</v>
+        <v>1.376448946972221</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5202222894527371</v>
+        <v>0.396641425029975</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.211800051157906</v>
+        <v>3.137651532504249</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.694303347717596</v>
+        <v>-3.875523451824748</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.340850775570779</v>
+        <v>1.268362733927918</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.529497988488952</v>
+        <v>0.4059171240661899</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.136627332064936</v>
+        <v>3.062478813411279</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.708091400564642</v>
+        <v>-3.889311504671794</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.325772263063852</v>
+        <v>1.253284221420991</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.529497988488952</v>
+        <v>0.4059171240661899</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.127064040696828</v>
+        <v>3.05291552204317</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.763611476457232</v>
+        <v>-3.944831580564384</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.440595069399018</v>
+        <v>1.368107027756158</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.529497988488952</v>
+        <v>0.4059171240661899</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.26409487738903</v>
+        <v>3.189946358735373</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.588137216664763</v>
+        <v>-3.769357320771915</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.515352005307794</v>
+        <v>1.442863963664933</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.529497988488952</v>
+        <v>0.4059171240661899</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.268662109380818</v>
+        <v>3.19451359072716</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.699073469306011</v>
+        <v>-3.880293573413163</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.446719533012502</v>
+        <v>1.374231491369641</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.529497988488952</v>
+        <v>0.4059171240661899</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.244404138142025</v>
+        <v>3.170255619488367</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.665409923833729</v>
+        <v>-3.846630027940881</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.388723264602864</v>
+        <v>1.316235222960003</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5631615339612339</v>
+        <v>0.4395806695384717</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.193140578826844</v>
+        <v>3.118992060173186</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.605557304630006</v>
+        <v>-3.786777408737158</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.422836698716486</v>
+        <v>1.350348657073625</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5631615339612339</v>
+        <v>0.4395806695384717</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.203312965258976</v>
+        <v>3.129164446605319</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.519313841603629</v>
+        <v>-3.700533945710781</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.452280354500897</v>
+        <v>1.379792312858036</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5631615339612339</v>
+        <v>0.4395806695384717</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.198259235832837</v>
+        <v>3.124110717179179</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.564620661002609</v>
+        <v>-3.745840765109761</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.425933402185831</v>
+        <v>1.35344536054297</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5223513709520031</v>
+        <v>0.398770506529241</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.165548913471823</v>
+        <v>3.091400394818166</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.59365376570491</v>
+        <v>-3.774873869812062</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.414872033338011</v>
+        <v>1.342383991695151</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5223513709520031</v>
+        <v>0.398770506529241</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.166100786504925</v>
+        <v>3.091952267851268</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.500843284254051</v>
+        <v>-3.682063388361203</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.381268917809721</v>
+        <v>1.30878087616686</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6151618524028625</v>
+        <v>0.4915809879801003</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.151059767266806</v>
+        <v>3.076911248613149</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.545232753583479</v>
+        <v>-3.726452857690631</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.365386606002551</v>
+        <v>1.29289856435969</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.5707723830734348</v>
+        <v>0.4471915186506726</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.126299561593751</v>
+        <v>3.052151042940093</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.432561535347229</v>
+        <v>-3.61378163945438</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.405530801808774</v>
+        <v>1.333042760165913</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.683443601309685</v>
+        <v>0.5598627368869229</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.188978001047224</v>
+        <v>3.114829482393566</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.320184534164556</v>
+        <v>-3.501404638271708</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.45597289811251</v>
+        <v>1.383484856469649</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.683443601309685</v>
+        <v>0.5598627368869229</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.194469296877891</v>
+        <v>3.120320778224233</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.347964932065909</v>
+        <v>-3.529185036173061</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.456357940720508</v>
+        <v>1.383869899077647</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6556632034083318</v>
+        <v>0.5320823389855698</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.189298259905618</v>
+        <v>3.115149741251961</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.466345604796047</v>
+        <v>-3.647565708903199</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.247361391629106</v>
+        <v>1.174873349986245</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5884453512573556</v>
+        <v>0.4648644868345936</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.987323268615686</v>
+        <v>2.913174749962028</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.574959683239379</v>
+        <v>-3.756179787346531</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.324065420970979</v>
+        <v>1.251577379328118</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5884453512573556</v>
+        <v>0.4648644868345936</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.107472929334891</v>
+        <v>3.033324410681234</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.539550644991236</v>
+        <v>-3.720770749098388</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.352742062372559</v>
+        <v>1.280254020729698</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5884453512573556</v>
+        <v>0.4648644868345936</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.121985955437214</v>
+        <v>3.047837436783557</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.501166982433085</v>
+        <v>-3.682387086540237</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.365514968738188</v>
+        <v>1.293026927095327</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6268290138155068</v>
+        <v>0.5032481493927448</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.142435594314474</v>
+        <v>3.068287075660816</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.324050652397919</v>
+        <v>-3.50527075650507</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.433090529597556</v>
+        <v>1.360602487954696</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6268290138155068</v>
+        <v>0.5032481493927448</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.139164623159775</v>
+        <v>3.065016104506118</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.369142897231464</v>
+        <v>-3.550363001338616</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.415737023426051</v>
+        <v>1.343248981783191</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.564932970646117</v>
+        <v>0.441352106223355</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.102710389020055</v>
+        <v>3.028561870366397</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.189767475992697</v>
+        <v>-3.370987580099849</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.481274167227973</v>
+        <v>1.408786125585112</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7217097288168357</v>
+        <v>0.5981288643940736</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.190563419228901</v>
+        <v>3.116414900575243</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.234781689513303</v>
+        <v>-3.416001793620455</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.44407593715132</v>
+        <v>1.371587895508459</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6913608335022311</v>
+        <v>0.567779969079469</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.153161537371727</v>
+        <v>3.07901301871807</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.501786199785738</v>
+        <v>-3.536366706982471</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.342965695381292</v>
+        <v>1.329133492502598</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4969977954592826</v>
+        <v>0.4839460210524354</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.042235276884904</v>
+        <v>3.034404212240795</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.602983981222911</v>
+        <v>-3.637564488419644</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.301690504702924</v>
+        <v>1.287858301824231</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4285889819139634</v>
+        <v>0.4155372075071163</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.000393910654214</v>
+        <v>2.992562846010105</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.596473014608598</v>
+        <v>-3.631053521805331</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.301894852902966</v>
+        <v>1.288062650024272</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4285889819139634</v>
+        <v>0.4155372075071163</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.99799387220853</v>
+        <v>2.990162807564422</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.577434886901301</v>
+        <v>-3.612015394098034</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.306034823194129</v>
+        <v>1.292202620315436</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3704053705827688</v>
+        <v>0.3573535961759217</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.959608424618059</v>
+        <v>2.951777359973951</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.914947071207078</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.608561518051919</v>
+        <v>-3.643142025248652</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.471166039672563</v>
+        <v>1.45733383679387</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3704053705827688</v>
+        <v>0.3573535961759217</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.137190293556739</v>
+        <v>3.129359228912631</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.915780400193211</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.622428279385836</v>
+        <v>-3.65700878658257</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.466452664125129</v>
+        <v>1.452620461246436</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3325474538489459</v>
+        <v>0.3194956794420988</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.115308872502579</v>
+        <v>3.107477807858471</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.921788930590137</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.577624107845907</v>
+        <v>-3.61220461504264</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.490382863138027</v>
+        <v>1.476550660259334</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3325474538489459</v>
+        <v>0.3194956794420988</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.121317402899505</v>
+        <v>3.113486338255397</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.819739151867337</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.429881137610904</v>
+        <v>-3.464461644807638</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.447430272509228</v>
+        <v>1.433598069630534</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5003548110838291</v>
+        <v>0.4873030366769819</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.119952038517634</v>
+        <v>3.112120973873526</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.822532773398818</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.531895820142125</v>
+        <v>-3.566476327338858</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.40941802102822</v>
+        <v>1.395585818149527</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5003548110838291</v>
+        <v>0.4873030366769819</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.122745660049115</v>
+        <v>3.114914595405007</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.916989965414152</v>
+        <v>2.823195121790476</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.623039882840909</v>
+        <v>-3.560323621286074</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.467417587964041</v>
+        <v>1.398709248962299</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4092107483850456</v>
+        <v>0.4934557427297662</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.16251641444518</v>
+        <v>3.119268567428336</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.916070442154262</v>
+        <v>2.822275598530586</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.63984918099141</v>
+        <v>-3.577132919436576</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.459774345443951</v>
+        <v>1.391066006442209</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3924014502345439</v>
+        <v>0.4766464445792646</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.151511312294989</v>
+        <v>3.108263465278145</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.982405995951083</v>
+        <v>2.888611152327407</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.577551182215288</v>
+        <v>-3.514834920660454</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.551029098751221</v>
+        <v>1.482320759749479</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3924014502345439</v>
+        <v>0.4766464445792646</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.21784686609181</v>
+        <v>3.174599019074966</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.78469799766521</v>
+        <v>2.690903154041534</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.37576098455013</v>
+        <v>-3.313044722995296</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.434037179531411</v>
+        <v>1.365328840529669</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5904196424036983</v>
+        <v>0.674664636748419</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.13894978310743</v>
+        <v>3.095701936090586</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.854988229987386</v>
+        <v>2.761193386363709</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.426647697236325</v>
+        <v>-3.36393143568149</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.483972726779108</v>
+        <v>1.415264387777366</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5395329297175038</v>
+        <v>0.6237779240622245</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.178707987817888</v>
+        <v>3.135460140801044</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.869615966103429</v>
+        <v>2.775821122479753</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.5243882418613</v>
+        <v>-3.461671980306465</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.459504245045162</v>
+        <v>1.39079590604342</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5236436515845235</v>
+        <v>0.6078886459292443</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.183802157054143</v>
+        <v>3.1405543100373</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.868151946928101</v>
+        <v>2.774357103304425</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.700726001984229</v>
+        <v>-3.638009740429394</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.387505121820662</v>
+        <v>1.31879678281892</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.3473058914615941</v>
+        <v>0.4315508858063149</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.076535481805058</v>
+        <v>3.033287634788214</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.86664356496803</v>
+        <v>2.772848721344353</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.624303955552302</v>
+        <v>-3.561587693997467</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.416565558433361</v>
+        <v>1.347857219431619</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.3473058914615941</v>
+        <v>0.4315508858063149</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.075027099844986</v>
+        <v>3.031779252828143</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.866506432403466</v>
+        <v>2.77271158877979</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.579930823913733</v>
+        <v>-3.517214562358899</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.434177678524225</v>
+        <v>1.365469339522483</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.3916790231001627</v>
+        <v>0.4759240174448835</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.101513846263563</v>
+        <v>3.05826599924672</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821562117105968</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.860900226542056</v>
+        <v>2.76710538291838</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.457096603026566</v>
+        <v>-3.394380341471731</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.477705161017683</v>
+        <v>1.40899682201594</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.3916790231001627</v>
+        <v>0.4759240174448835</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.095907640402154</v>
+        <v>3.052659793385311</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833011148190326</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.86728198356986</v>
+        <v>2.773487139946185</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.409440872465511</v>
+        <v>-3.346724610910676</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.503149210269909</v>
+        <v>1.434440871268167</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.4393347536612184</v>
+        <v>0.5235797480059392</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.130882835766592</v>
+        <v>3.087634988749748</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.872174356944585</v>
+        <v>2.778379513320909</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.308922713966756</v>
+        <v>-3.246206452411921</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.548248847044136</v>
+        <v>1.479540508042394</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.5398529121599729</v>
+        <v>0.6240979065046938</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.196086104240569</v>
+        <v>3.152838257223726</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828808877557294</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.858929029420457</v>
+        <v>2.765134185796782</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.369589304369145</v>
+        <v>-3.30687304281431</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.510736883359052</v>
+        <v>1.44202854435731</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.4581545954414392</v>
+        <v>0.5423995897861601</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.133821786685321</v>
+        <v>3.090573939668478</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.863026732031086</v>
+        <v>2.76923188840741</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.324750902760747</v>
+        <v>-3.262034641205912</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.53276994661304</v>
+        <v>1.464061607611298</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.4626980283863087</v>
+        <v>0.5469430227310296</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.140645549062872</v>
+        <v>3.097397702046028</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.867187671662164</v>
+        <v>2.773392828038488</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.344249359002755</v>
+        <v>-3.28153309744792</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.529131503747315</v>
+        <v>1.460423164745573</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.4146133871064044</v>
+        <v>0.4988583814511253</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.115955703926007</v>
+        <v>3.072707856909163</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.873067274190001</v>
+        <v>2.779272430566325</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.300046521916855</v>
+        <v>-3.23733026036202</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.552692241109512</v>
+        <v>1.48398390210777</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.4588162241923048</v>
+        <v>0.5430612185370257</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.148357008705384</v>
+        <v>3.105109161688541</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.871477274659249</v>
+        <v>2.777682431035573</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.337025549580298</v>
+        <v>-3.274309288025463</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.536310630513382</v>
+        <v>1.46760229151164</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.4957901259836354</v>
+        <v>0.5800351203283562</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.16895135024943</v>
+        <v>3.125703503232587</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.922725039842288</v>
+        <v>2.828930196218613</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.178734132041026</v>
+        <v>-3.116017870486191</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.650874962712131</v>
+        <v>1.582166623710389</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.4957901259836354</v>
+        <v>0.5800351203283562</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.22019911543247</v>
+        <v>3.176951268415626</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.921165744436542</v>
+        <v>2.827370900812866</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.971092128406549</v>
+        <v>-2.908375866851715</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.732372468760174</v>
+        <v>1.663664129758433</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.7034321296181115</v>
+        <v>0.7876771239628324</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.343225022207409</v>
+        <v>3.299977175190565</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864489842475138</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.916113972674812</v>
+        <v>2.822319129051136</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.920060035684021</v>
+        <v>-2.857343774129187</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.747733534087456</v>
+        <v>1.679025195085714</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.7544642223406395</v>
+        <v>0.8387092166853604</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.368792506079195</v>
+        <v>3.325544659062352</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.933301376767516</v>
+        <v>2.839506533143841</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.854835854556816</v>
+        <v>-2.792119593001981</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.791010610631043</v>
+        <v>1.722302271629301</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.8196884034678451</v>
+        <v>0.903933397812566</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.425114418848224</v>
+        <v>3.381866571831381</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840061186882557</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.929262349066797</v>
+        <v>2.835467505443121</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.817408834485682</v>
+        <v>-2.754692572930848</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.801942390958777</v>
+        <v>1.733234051957035</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.8249399414970268</v>
+        <v>0.9091849358417476</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.424226313965013</v>
+        <v>3.38097846694817</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899266</v>
+        <v>3.845169808992659</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.930519141398037</v>
+        <v>2.836724297774361</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.886151317582024</v>
+        <v>-2.774804228965556</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.77570219005148</v>
+        <v>1.726446181874392</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.8534014165888318</v>
+        <v>0.9202122808391668</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.442559991351336</v>
+        <v>3.388851666277862</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
-        <v>3.091076912419248</v>
+        <v>2.997282068795572</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.832406503154819</v>
+        <v>-2.721059414538351</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.957757886843573</v>
+        <v>1.908501878666484</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.8634647260292938</v>
+        <v>0.9302755902796288</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.609155748036824</v>
+        <v>3.55544742296335</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957625</v>
+        <v>3.813222820957623</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.211189821637065</v>
+        <v>3.117394978013389</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.757624242129807</v>
+        <v>-2.646277153513338</v>
       </c>
       <c r="E1992" t="n">
-        <v>2.107783700471395</v>
+        <v>2.058527692294307</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.9382469870543064</v>
+        <v>1.005057851304641</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.774138013869649</v>
+        <v>3.720429688796175</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998756</v>
+        <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.202897797650924</v>
+        <v>3.109102954027248</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.731540157865999</v>
+        <v>-2.620193069249531</v>
       </c>
       <c r="E1993" t="n">
-        <v>2.109925310190778</v>
+        <v>2.060669302013689</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.9382469870543064</v>
+        <v>1.005057851304641</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.765845989883508</v>
+        <v>3.712137664810033</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896929</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.201090993234704</v>
+        <v>3.107296149611028</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.653408977017052</v>
+        <v>-2.542061888400584</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.139370978114136</v>
+        <v>2.090114969937047</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.012423797937991</v>
+        <v>1.079234662188326</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.808545271997498</v>
+        <v>3.754836946924024</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959857</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.218645398961495</v>
+        <v>3.124850555337819</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.644516515623769</v>
+        <v>-2.533169427007301</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.16048236839824</v>
+        <v>2.111226360221152</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.012423797937991</v>
+        <v>1.079234662188326</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.82609967772429</v>
+        <v>3.772391352650815</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.210500446366079</v>
+        <v>3.116705602742403</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.812992632593647</v>
+        <v>-2.701645543977178</v>
       </c>
       <c r="E1996" t="n">
-        <v>2.084946969014873</v>
+        <v>2.035690960837784</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.9844759622214101</v>
+        <v>1.051286826471745</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.801186023698925</v>
+        <v>3.747477698625451</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.191770143553941</v>
+        <v>3.097975299930265</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.115193103732063</v>
+        <v>-2.003846015115595</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.345336477747368</v>
+        <v>2.296080469570279</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.9141279028509994</v>
+        <v>0.9809387671013345</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.740246885264541</v>
+        <v>3.686538560191066</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632636</v>
+        <v>3.784671345632634</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.182434166050845</v>
+        <v>3.08863932242717</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.092472000048911</v>
+        <v>-1.981124911432443</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.345088941717534</v>
+        <v>2.295832933540445</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.9141279028509994</v>
+        <v>0.9809387671013345</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.730910907761445</v>
+        <v>3.677202582687971</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.341340291902014</v>
+        <v>3.247545448278339</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.221673813342953</v>
+        <v>-2.110326724726485</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.452314342251086</v>
+        <v>2.403058334073997</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.7849260895569572</v>
+        <v>0.8517369538072923</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.812295945636189</v>
+        <v>3.758587620562714</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644412</v>
+        <v>3.77993372564441</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.378418114395661</v>
+        <v>3.284623270771985</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.376454820121209</v>
+        <v>-2.265107731504741</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.42747976203343</v>
+        <v>2.378223753856342</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.751558415502481</v>
+        <v>0.8183692797528161</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.82935316369715</v>
+        <v>3.775644838623675</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799964</v>
+        <v>3.769443619799962</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.375093470385206</v>
+        <v>3.28129862676153</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.369400129906035</v>
+        <v>-2.258053041289567</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.426976994109045</v>
+        <v>2.377720985931956</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.7586131057176548</v>
+        <v>0.8254239699679899</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.830261333815799</v>
+        <v>3.776553008742324</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.385099624029948</v>
+        <v>3.291304780406272</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.342448905579547</v>
+        <v>-2.231101816963079</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.447763637484381</v>
+        <v>2.398507629307293</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.773493451745374</v>
+        <v>0.8403043159957091</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.849195695077172</v>
+        <v>3.795487370003698</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784108</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.569202756174907</v>
+        <v>3.475407912551232</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.478401913635864</v>
+        <v>-2.367054825019395</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.577485566406815</v>
+        <v>2.528229558229726</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.773493451745374</v>
+        <v>0.8403043159957091</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.033298827222132</v>
+        <v>3.979590502148657</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714427</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.5613194510779</v>
+        <v>3.467524607454225</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.500810031440736</v>
+        <v>-2.389462942824268</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.560639014187859</v>
+        <v>2.51138300601077</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.773493451745374</v>
+        <v>0.8403043159957091</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.025415522125125</v>
+        <v>3.97170719705165</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155033</v>
+        <v>3.719118627155031</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.563373450627538</v>
+        <v>3.469578607003862</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.648815798920135</v>
+        <v>-2.537468710303667</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.503490706745737</v>
+        <v>2.454234698568648</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.6867664428818325</v>
+        <v>0.7535773071321676</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.975433316356638</v>
+        <v>3.921724991283163</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161978</v>
+        <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.619627168349385</v>
+        <v>3.525832324725709</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.658256724808665</v>
+        <v>-2.546909636192197</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.555968054112172</v>
+        <v>2.506712045935084</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.8091935604252239</v>
+        <v>0.8760044246755591</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.105143304604519</v>
+        <v>4.051434979531045</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321635</v>
+        <v>3.714941193321633</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.622518262894686</v>
+        <v>3.52872341927101</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.710530332144307</v>
+        <v>-2.599183243527838</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.537949705723216</v>
+        <v>2.488693697546128</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.7569199530895827</v>
+        <v>0.8237308173399178</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.076670234748436</v>
+        <v>4.022961909674962</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347703</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.620630075788461</v>
+        <v>3.526835232164785</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.786860309745212</v>
+        <v>-2.675513221128744</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.505529527576629</v>
+        <v>2.456273519399541</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.7569199530895827</v>
+        <v>0.8237308173399178</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.074782047642211</v>
+        <v>4.021073722568737</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887748</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.615450305391323</v>
+        <v>3.521655461767648</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.898617262360514</v>
+        <v>-2.787270173744045</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.455646976133371</v>
+        <v>2.406390967956282</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.6451630004742817</v>
+        <v>0.7119738647246168</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.002548105675893</v>
+        <v>3.948839780602418</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343066</v>
+        <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.613884315601476</v>
+        <v>3.5200894719778</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.896776243302262</v>
+        <v>-2.785429154685794</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.454817393966824</v>
+        <v>2.405561385789735</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.6464312271457501</v>
+        <v>0.7132420913960852</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.001743051888926</v>
+        <v>3.948034726815451</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647106</v>
+        <v>3.754911907647104</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.626957722467394</v>
+        <v>3.533162878843719</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.029077535399816</v>
+        <v>-2.917730446783347</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.414970283993721</v>
+        <v>2.365714275816632</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.6464312271457501</v>
+        <v>0.7132420913960852</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.014816458754844</v>
+        <v>3.96110813368137</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763533</v>
+        <v>3.749896851763531</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.626957722467394</v>
+        <v>3.533162878843719</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.030639178214676</v>
+        <v>-2.919292089598208</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.414345626867777</v>
+        <v>2.365089618690688</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6464312271457501</v>
+        <v>0.7132420913960852</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.014816458754844</v>
+        <v>3.96110813368137</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392117</v>
+        <v>3.715834055392115</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.625481763594396</v>
+        <v>3.531686919970721</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.058539965324149</v>
+        <v>-2.94719287670768</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.40170935315099</v>
+        <v>2.352453344973901</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6118343030028153</v>
+        <v>0.6786451672531504</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.992582345396086</v>
+        <v>3.938874020322611</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172528</v>
+        <v>3.684909939172526</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.622246207571595</v>
+        <v>3.528451363947919</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.181066068027043</v>
+        <v>-3.069718979410574</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.349463356047031</v>
+        <v>2.300207347869942</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4893082002999214</v>
+        <v>0.5561190645502565</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.915831127751548</v>
+        <v>3.862122802678074</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971079</v>
+        <v>3.619362241971077</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.688952167162099</v>
+        <v>3.595157323538423</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.201127389303549</v>
+        <v>-3.089780300687081</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.408144787126932</v>
+        <v>2.358888778949844</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4692468790234144</v>
+        <v>0.5360577432737494</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.970500294576148</v>
+        <v>3.916791969502673</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199806</v>
+        <v>3.640764248199805</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.829263886163946</v>
+        <v>3.73546904254027</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.457848207298373</v>
+        <v>-3.346501118681905</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.445768178930849</v>
+        <v>2.396512170753761</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3608323048795996</v>
+        <v>0.4276431691299346</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.045763269091706</v>
+        <v>3.992054944018231</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622237</v>
+        <v>3.668303164622235</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.898244155309586</v>
+        <v>3.80444931168591</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.611834625074514</v>
+        <v>-3.500487536458046</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.453153880966033</v>
+        <v>2.403897872788944</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3608323048795996</v>
+        <v>0.4276431691299346</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.114743538237346</v>
+        <v>4.061035213163871</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808529</v>
+        <v>3.619937176808527</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.884295357429707</v>
+        <v>3.790500513806031</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.561312721246848</v>
+        <v>-3.44996563263038</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.45941384461722</v>
+        <v>2.410157836440132</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3608323048795996</v>
+        <v>0.4276431691299346</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.100794740357466</v>
+        <v>4.047086415283992</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994894</v>
+        <v>3.656346893994892</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.896165846485121</v>
+        <v>3.802371002861445</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.813787875254572</v>
+        <v>-3.702440786638104</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.370294272069544</v>
+        <v>2.321038263892456</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3608323048795996</v>
+        <v>0.4276431691299346</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.11266522941288</v>
+        <v>4.058956904339405</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358299</v>
+        <v>3.674042696358297</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.897376381004064</v>
+        <v>3.803581537380389</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.08326067717628</v>
+        <v>-3.971913588559812</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.263715685819805</v>
+        <v>2.214459677642716</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3608323048795996</v>
+        <v>0.4276431691299346</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.113875763931825</v>
+        <v>4.06016743885835</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637087</v>
+        <v>3.663523617637085</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.901498123231386</v>
+        <v>3.80770327960771</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.240804748905722</v>
+        <v>-4.129457660289254</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.20481979935535</v>
+        <v>2.155563791178261</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.2939304997393251</v>
+        <v>0.3607413639896601</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.077856423074981</v>
+        <v>4.024148098001506</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301343</v>
+        <v>3.652163313301341</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.896575975967575</v>
+        <v>3.802781132343899</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.518769144488996</v>
+        <v>-4.407422055872527</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.08871189385823</v>
+        <v>2.039455885681141</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.2043107654538408</v>
+        <v>0.2711216297041759</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.01916243523988</v>
+        <v>3.965454110166405</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215469</v>
+        <v>3.667976467215468</v>
       </c>
       <c r="C2023" t="n">
-        <v>4.058780032666619</v>
+        <v>3.964985189042944</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.635736837127887</v>
+        <v>-4.524389748511418</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.204128873501717</v>
+        <v>2.154872865324629</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.2043107654538408</v>
+        <v>0.2711216297041759</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.181366491938924</v>
+        <v>4.12765816686545</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456692</v>
+        <v>3.69655362845669</v>
       </c>
       <c r="C2024" t="n">
-        <v>4.053626670630433</v>
+        <v>3.959831827006758</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.72045477934884</v>
+        <v>-4.609107690732372</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.16508833457715</v>
+        <v>2.115832326400062</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1191947365257944</v>
+        <v>0.1860056007761295</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.12514351254591</v>
+        <v>4.071435187472436</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253288</v>
+        <v>3.750058176253286</v>
       </c>
       <c r="C2025" t="n">
-        <v>4.063856088198925</v>
+        <v>3.970061244575249</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.802389597617723</v>
+        <v>-4.691042509001255</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.142543824838088</v>
+        <v>2.093287816661</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.1092599909387142</v>
+        <v>0.1760708551890493</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.129412082762154</v>
+        <v>4.075703757688679</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717832</v>
+        <v>3.78364702771783</v>
       </c>
       <c r="C2026" t="n">
-        <v>4.072781726654827</v>
+        <v>3.978986883031151</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.748651424217461</v>
+        <v>-4.637304335600993</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.172964732654095</v>
+        <v>2.123708724477007</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.1629981643389763</v>
+        <v>0.2298090285893114</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.170580625258213</v>
+        <v>4.116872300184738</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616949</v>
+        <v>3.798310944616947</v>
       </c>
       <c r="C2027" t="n">
-        <v>4.064934613899003</v>
+        <v>3.971139770275327</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.638645140740239</v>
+        <v>-4.527298052123771</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.20912013328916</v>
+        <v>2.159864125112072</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1862027362562516</v>
+        <v>0.2530136005065866</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.176656255652754</v>
+        <v>4.122947930579279</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203664</v>
+        <v>3.785578085203662</v>
       </c>
       <c r="C2028" t="n">
-        <v>4.069184624620977</v>
+        <v>3.975389780997301</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.495585564999313</v>
+        <v>-4.384238476382846</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.270593974307505</v>
+        <v>2.221337966130416</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1942161628462308</v>
+        <v>0.2610270270965659</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.185714322328716</v>
+        <v>4.132005997255241</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.77725157243693</v>
+        <v>3.777251572436928</v>
       </c>
       <c r="C2029" t="n">
-        <v>4.076445507503514</v>
+        <v>3.982650663879838</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.194138839527476</v>
+        <v>-4.082791750911008</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.398433547378776</v>
+        <v>2.349177539201687</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.495662888318068</v>
+        <v>0.5624737525684032</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.373843240494355</v>
+        <v>4.32013491542088</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064767</v>
+        <v>3.812650101064765</v>
       </c>
       <c r="C2030" t="n">
-        <v>4.077416685256224</v>
+        <v>3.983621841632548</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.249094035970545</v>
+        <v>-4.137746947354078</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.377422646554258</v>
+        <v>2.328166638377169</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.495662888318068</v>
+        <v>0.5624737525684032</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.374814418247065</v>
+        <v>4.32110609317359</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859301</v>
+        <v>3.821198342859299</v>
       </c>
       <c r="C2031" t="n">
-        <v>4.078259589635979</v>
+        <v>3.984464746012303</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.198055659964025</v>
+        <v>-4.086708571347557</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.398680901336622</v>
+        <v>2.349424893159533</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.495662888318068</v>
+        <v>0.5624737525684032</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.375657322626821</v>
+        <v>4.321948997553346</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354684</v>
+        <v>3.831748677354683</v>
       </c>
       <c r="C2032" t="n">
-        <v>4.097297688510125</v>
+        <v>4.003502844886449</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.156916365097394</v>
+        <v>-4.045569276480927</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.43417471815742</v>
+        <v>2.384918709980331</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5368021831846989</v>
+        <v>0.603613047435034</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.419378998420944</v>
+        <v>4.36567067334747</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825767093085618</v>
+        <v>3.825767093085616</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.913481684634059</v>
+        <v>3.819686841010383</v>
       </c>
       <c r="D2033" t="n">
-        <v>-3.957995942892016</v>
+        <v>-3.934963136401325</v>
       </c>
       <c r="E2033" t="n">
-        <v>2.329926883163505</v>
+        <v>2.245345162136106</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.7357226053900766</v>
+        <v>0.714219187514636</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.354915247868106</v>
+        <v>4.248218353519166</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.833113332332212</v>
+        <v>3.565567531713958</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.915464848498096</v>
+        <v>3.629661384494824</v>
       </c>
       <c r="D2034" t="n">
-        <v>-3.957995942892016</v>
+        <v>-3.934963136401325</v>
       </c>
       <c r="E2034" t="n">
-        <v>2.329926883163505</v>
+        <v>2.245345162136106</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.7357226053900766</v>
+        <v>0.714219187514636</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.908528645484464</v>
+        <v>3.622725181481192</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240723.xlsx
+++ b/tame_output/ON/bt/strategyON_20240723.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -671,17 +671,17 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>50.3%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>84.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,32 +844,32 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>68.6%</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>31.2%</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>61.6%</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>31.7%</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>70.7%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.8%</t>
+          <t>-75.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.1%</t>
+          <t>110.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.7%</t>
+          <t>125.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.7%</t>
+          <t>-48.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.7%</t>
+          <t>-71.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.3%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.5%</t>
+          <t>456.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-555.1%</t>
+          <t>-573.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-47.4%</t>
+          <t>-47.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-151.7%</t>
+          <t>-158.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.3%</t>
+          <t>-26.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-121.7%</t>
+          <t>-85.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-152.6%</t>
+          <t>-157.5%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.6%</t>
+          <t>-22.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>75.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-83.8%</t>
+          <t>-23.8%</t>
         </is>
       </c>
     </row>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297742</v>
+        <v>3.458100091297743</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.262341880119591</v>
+        <v>-4.272928301031499</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.258274511363039</v>
+        <v>1.254039942998276</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.1941407303852369</v>
+        <v>0.1894511192969474</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.080052125955765</v>
+        <v>3.077238359302791</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.129474191056313</v>
+        <v>-4.140060611968221</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.327315769790173</v>
+        <v>1.32308120142541</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.1941407303852369</v>
+        <v>0.1894511192969474</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.095946308757588</v>
+        <v>3.093132542104614</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.009301107691814</v>
+        <v>-4.019887528603722</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.376530847576275</v>
+        <v>1.372296279211511</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.3143138137497358</v>
+        <v>0.3096242026614464</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.169196003216589</v>
+        <v>3.166382236563616</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.864628962592077</v>
+        <v>-3.875215383503985</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.444487808177609</v>
+        <v>1.440253239812846</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.4589859588494732</v>
+        <v>0.4542963477611838</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.266087392837872</v>
+        <v>3.263273626184898</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.924503789949769</v>
+        <v>-3.935090210861677</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.406575368635958</v>
+        <v>1.402340800271195</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.3991111314917811</v>
+        <v>0.3944215204034917</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.216199987824682</v>
+        <v>3.213386221171708</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.804683559038932</v>
+        <v>-3.81526997995084</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.469792630234502</v>
+        <v>1.465558061869739</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.3991111314917811</v>
+        <v>0.3944215204034917</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.231489157058891</v>
+        <v>3.228675390405917</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.807153265500738</v>
+        <v>-3.817739686412646</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.376448946972221</v>
+        <v>1.372214378607458</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.396641425029975</v>
+        <v>0.3919518139416855</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.137651532504249</v>
+        <v>3.134837765851275</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.875523451824748</v>
+        <v>-3.886109872736656</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.268362733927918</v>
+        <v>1.264128165563155</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.4059171240661899</v>
+        <v>0.4012275129779004</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.062478813411279</v>
+        <v>3.059665046758306</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.889311504671794</v>
+        <v>-3.899897925583702</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.253284221420991</v>
+        <v>1.249049653056228</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.4059171240661899</v>
+        <v>0.4012275129779004</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.05291552204317</v>
+        <v>3.050101755390197</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.944831580564384</v>
+        <v>-3.955418001476292</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.368107027756158</v>
+        <v>1.363872459391394</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.4059171240661899</v>
+        <v>0.4012275129779004</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.189946358735373</v>
+        <v>3.187132592082399</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.769357320771915</v>
+        <v>-3.779943741683823</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.442863963664933</v>
+        <v>1.43862939530017</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.4059171240661899</v>
+        <v>0.4012275129779004</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.19451359072716</v>
+        <v>3.191699824074187</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.880293573413163</v>
+        <v>-3.890879994325071</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.374231491369641</v>
+        <v>1.369996923004878</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.4059171240661899</v>
+        <v>0.4012275129779004</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.170255619488367</v>
+        <v>3.167441852835394</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.846630027940881</v>
+        <v>-3.857216448852789</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.316235222960003</v>
+        <v>1.31200065459524</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.4395806695384717</v>
+        <v>0.4348910584501823</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.118992060173186</v>
+        <v>3.116178293520213</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.786777408737158</v>
+        <v>-3.797363829649066</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.350348657073625</v>
+        <v>1.346114088708862</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.4395806695384717</v>
+        <v>0.4348910584501823</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.129164446605319</v>
+        <v>3.126350679952345</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.700533945710781</v>
+        <v>-3.711120366622689</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.379792312858036</v>
+        <v>1.375557744493273</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.4395806695384717</v>
+        <v>0.4348910584501823</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.124110717179179</v>
+        <v>3.121296950526205</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.745840765109761</v>
+        <v>-3.756427186021669</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.35344536054297</v>
+        <v>1.349210792178207</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.398770506529241</v>
+        <v>0.3940808954409515</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.091400394818166</v>
+        <v>3.088586628165193</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.774873869812062</v>
+        <v>-3.78546029072397</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.342383991695151</v>
+        <v>1.338149423330387</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.398770506529241</v>
+        <v>0.3940808954409515</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.091952267851268</v>
+        <v>3.089138501198294</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.682063388361203</v>
+        <v>-3.692649809273111</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.30878087616686</v>
+        <v>1.304546307802097</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.4915809879801003</v>
+        <v>0.4868913768918108</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.076911248613149</v>
+        <v>3.074097481960175</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.726452857690631</v>
+        <v>-3.737039278602539</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.29289856435969</v>
+        <v>1.288663995994927</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.4471915186506726</v>
+        <v>0.4425019075623832</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.052151042940093</v>
+        <v>3.049337276287119</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.61378163945438</v>
+        <v>-3.624368060366288</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.333042760165913</v>
+        <v>1.32880819180115</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.5598627368869229</v>
+        <v>0.5551731257986334</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.114829482393566</v>
+        <v>3.112015715740593</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.501404638271708</v>
+        <v>-3.511991059183616</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.383484856469649</v>
+        <v>1.379250288104886</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.5598627368869229</v>
+        <v>0.5551731257986334</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.120320778224233</v>
+        <v>3.11750701157126</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.529185036173061</v>
+        <v>-3.539771457084969</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.383869899077647</v>
+        <v>1.379635330712884</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.5320823389855698</v>
+        <v>0.5273927278972803</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.115149741251961</v>
+        <v>3.112335974598987</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.647565708903199</v>
+        <v>-3.658152129815107</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.174873349986245</v>
+        <v>1.170638781621482</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4648644868345936</v>
+        <v>0.4601748757463041</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.913174749962028</v>
+        <v>2.910360983309054</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.756179787346531</v>
+        <v>-3.766766208258439</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.251577379328118</v>
+        <v>1.247342810963355</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4648644868345936</v>
+        <v>0.4601748757463041</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.033324410681234</v>
+        <v>3.03051064402826</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.720770749098388</v>
+        <v>-3.731357170010296</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.280254020729698</v>
+        <v>1.276019452364935</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4648644868345936</v>
+        <v>0.4601748757463041</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.047837436783557</v>
+        <v>3.045023670130583</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.682387086540237</v>
+        <v>-3.692973507452145</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.293026927095327</v>
+        <v>1.288792358730564</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.5032481493927448</v>
+        <v>0.4985585383044553</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.068287075660816</v>
+        <v>3.065473309007843</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.50527075650507</v>
+        <v>-3.515857177416978</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.360602487954696</v>
+        <v>1.356367919589933</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.5032481493927448</v>
+        <v>0.4985585383044553</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.065016104506118</v>
+        <v>3.062202337853145</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.550363001338616</v>
+        <v>-3.560949422250524</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.343248981783191</v>
+        <v>1.339014413418427</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.441352106223355</v>
+        <v>0.4366624951350655</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.028561870366397</v>
+        <v>3.025748103713424</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.370987580099849</v>
+        <v>-3.381574001011757</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.408786125585112</v>
+        <v>1.404551557220349</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5981288643940736</v>
+        <v>0.5934392533057842</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.116414900575243</v>
+        <v>3.113601133922269</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.416001793620455</v>
+        <v>-3.426588214532363</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.371587895508459</v>
+        <v>1.367353327143696</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.567779969079469</v>
+        <v>0.5630903579911796</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.07901301871807</v>
+        <v>3.076199252065096</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.536366706982471</v>
+        <v>-3.693592724804798</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.329133492502598</v>
+        <v>1.266243085373667</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4839460210524354</v>
+        <v>0.368727319948231</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.034404212240795</v>
+        <v>2.965272991578273</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.637564488419644</v>
+        <v>-3.794790506241971</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.287858301824231</v>
+        <v>1.2249678946953</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4155372075071163</v>
+        <v>0.3003185064029118</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.992562846010105</v>
+        <v>2.923431625347583</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.631053521805331</v>
+        <v>-3.788279539627658</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.288062650024272</v>
+        <v>1.225172242895342</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4155372075071163</v>
+        <v>0.3003185064029118</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.990162807564422</v>
+        <v>2.9210315869019</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.612015394098034</v>
+        <v>-3.769241411920361</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.292202620315436</v>
+        <v>1.229312213186506</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3573535961759217</v>
+        <v>0.2421348950717173</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.951777359973951</v>
+        <v>2.882646139311428</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.914947071207078</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.643142025248652</v>
+        <v>-3.800368043070979</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.45733383679387</v>
+        <v>1.394443429664939</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3573535961759217</v>
+        <v>0.2421348950717173</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.129359228912631</v>
+        <v>3.060228008250109</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.915780400193211</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.65700878658257</v>
+        <v>-3.814234804404896</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.452620461246436</v>
+        <v>1.389730054117505</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3194956794420988</v>
+        <v>0.2042769783378943</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.107477807858471</v>
+        <v>3.038346587195948</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.921788930590137</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.61220461504264</v>
+        <v>-3.769430632864966</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.476550660259334</v>
+        <v>1.413660253130403</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3194956794420988</v>
+        <v>0.2042769783378943</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.113486338255397</v>
+        <v>3.044355117592874</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.819739151867337</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.464461644807638</v>
+        <v>-3.621687662629964</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.433598069630534</v>
+        <v>1.370707662501604</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4873030366769819</v>
+        <v>0.3720843355727775</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.112120973873526</v>
+        <v>3.042989753211003</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.822532773398818</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.566476327338858</v>
+        <v>-3.723702345161185</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.395585818149527</v>
+        <v>1.332695411020596</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4873030366769819</v>
+        <v>0.3720843355727775</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.114914595405007</v>
+        <v>3.045783374742484</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.823195121790476</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.560323621286074</v>
+        <v>-3.717549639108401</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.398709248962299</v>
+        <v>1.335818841833369</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4934557427297662</v>
+        <v>0.3782370416255618</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.119268567428336</v>
+        <v>3.050137346765813</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.822275598530586</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.577132919436576</v>
+        <v>-3.734358937258902</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.391066006442209</v>
+        <v>1.328175599313278</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4766464445792646</v>
+        <v>0.3614277434750601</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.108263465278145</v>
+        <v>3.039132244615623</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.888611152327407</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.514834920660454</v>
+        <v>-3.67206093848278</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.482320759749479</v>
+        <v>1.419430352620548</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4766464445792646</v>
+        <v>0.3614277434750601</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.174599019074966</v>
+        <v>3.105467798412444</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.690903154041534</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.313044722995296</v>
+        <v>-3.470270740817623</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.365328840529669</v>
+        <v>1.302438433400738</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.674664636748419</v>
+        <v>0.5594459356442145</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.095701936090586</v>
+        <v>3.026570715428063</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.761193386363709</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.36393143568149</v>
+        <v>-3.521157453503817</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.415264387777366</v>
+        <v>1.352373980648435</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.6237779240622245</v>
+        <v>0.50855922295802</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.135460140801044</v>
+        <v>3.066328920138522</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.775821122479753</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.461671980306465</v>
+        <v>-3.618897998128792</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.39079590604342</v>
+        <v>1.327905498914489</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6078886459292443</v>
+        <v>0.4926699448250398</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.1405543100373</v>
+        <v>3.071423089374777</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.774357103304425</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.638009740429394</v>
+        <v>-3.795235758251721</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.31879678281892</v>
+        <v>1.255906375689989</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.4315508858063149</v>
+        <v>0.3163321847021104</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.033287634788214</v>
+        <v>2.964156414125691</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.772848721344353</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.561587693997467</v>
+        <v>-3.718813711819794</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.347857219431619</v>
+        <v>1.284966812302688</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.4315508858063149</v>
+        <v>0.3163321847021104</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.031779252828143</v>
+        <v>2.96264803216562</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.77271158877979</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.517214562358899</v>
+        <v>-3.674440580181225</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.365469339522483</v>
+        <v>1.302578932393552</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.4759240174448835</v>
+        <v>0.360705316340679</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.05826599924672</v>
+        <v>2.989134778584197</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.76710538291838</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.394380341471731</v>
+        <v>-3.551606359294058</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.40899682201594</v>
+        <v>1.346106414887009</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.4759240174448835</v>
+        <v>0.360705316340679</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.052659793385311</v>
+        <v>2.983528572722788</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.773487139946185</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.346724610910676</v>
+        <v>-3.503950628733002</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.434440871268167</v>
+        <v>1.371550464139236</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.5235797480059392</v>
+        <v>0.4083610469017346</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.087634988749748</v>
+        <v>3.018503768087226</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.778379513320909</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.246206452411921</v>
+        <v>-3.403432470234248</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.479540508042394</v>
+        <v>1.416650100913463</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.6240979065046938</v>
+        <v>0.5088792054004891</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.152838257223726</v>
+        <v>3.083707036561203</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.765134185796782</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.30687304281431</v>
+        <v>-3.464099060636637</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.44202854435731</v>
+        <v>1.37913813722838</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.5423995897861601</v>
+        <v>0.4271808886819555</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.090573939668478</v>
+        <v>3.021442719005955</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.76923188840741</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.262034641205912</v>
+        <v>-3.419260659028239</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.464061607611298</v>
+        <v>1.401171200482368</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.5469430227310296</v>
+        <v>0.4317243216268249</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.097397702046028</v>
+        <v>3.028266481383505</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.773392828038488</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.28153309744792</v>
+        <v>-3.438759115270247</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.460423164745573</v>
+        <v>1.397532757616642</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.4988583814511253</v>
+        <v>0.3836396803469206</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.072707856909163</v>
+        <v>3.003576636246641</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.779272430566325</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.23733026036202</v>
+        <v>-3.394556278184346</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.48398390210777</v>
+        <v>1.42109349497884</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.5430612185370257</v>
+        <v>0.4278425174328211</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.105109161688541</v>
+        <v>3.035977941026018</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.777682431035573</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.274309288025463</v>
+        <v>-3.43153530584779</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.46760229151164</v>
+        <v>1.40471188438271</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.5800351203283562</v>
+        <v>0.4648164192241516</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.125703503232587</v>
+        <v>3.056572282570064</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.828930196218613</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.116017870486191</v>
+        <v>-3.273243888308517</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.582166623710389</v>
+        <v>1.519276216581458</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.5800351203283562</v>
+        <v>0.4648164192241516</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.176951268415626</v>
+        <v>3.107820047753104</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.827370900812866</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.908375866851715</v>
+        <v>-3.065601884674041</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.663664129758433</v>
+        <v>1.600773722629502</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.7876771239628324</v>
+        <v>0.6724584228586278</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.299977175190565</v>
+        <v>3.230845954528043</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.822319129051136</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.857343774129187</v>
+        <v>-3.014569791951513</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.679025195085714</v>
+        <v>1.616134787956783</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.8387092166853604</v>
+        <v>0.7234905155811557</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.325544659062352</v>
+        <v>3.25641343839983</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.839506533143841</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.792119593001981</v>
+        <v>-2.949345610824308</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.722302271629301</v>
+        <v>1.65941186450037</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.903933397812566</v>
+        <v>0.7887146967083614</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.381866571831381</v>
+        <v>3.312735351168858</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.835467505443121</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.754692572930848</v>
+        <v>-2.911918590753174</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.733234051957035</v>
+        <v>1.670343644828104</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.9091849358417476</v>
+        <v>0.793966234737543</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.38097846694817</v>
+        <v>3.311847246285647</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.836724297774361</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.774804228965556</v>
+        <v>-2.932030246787882</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.726446181874392</v>
+        <v>1.663555774745461</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.9202122808391668</v>
+        <v>0.8049935797349622</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.388851666277862</v>
+        <v>3.319720445615339</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.997282068795572</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.721059414538351</v>
+        <v>-2.878285432360677</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.908501878666484</v>
+        <v>1.845611471537554</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9302755902796288</v>
+        <v>0.8150568891754242</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.55544742296335</v>
+        <v>3.486316202300827</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.117394978013389</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.646277153513338</v>
+        <v>-2.803503171335665</v>
       </c>
       <c r="E1992" t="n">
-        <v>2.058527692294307</v>
+        <v>1.995637285165376</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.005057851304641</v>
+        <v>0.8898391502004368</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.720429688796175</v>
+        <v>3.651298468133652</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.109102954027248</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.620193069249531</v>
+        <v>-2.777419087071857</v>
       </c>
       <c r="E1993" t="n">
-        <v>2.060669302013689</v>
+        <v>1.997778894884759</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.005057851304641</v>
+        <v>0.8898391502004368</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.712137664810033</v>
+        <v>3.643006444147511</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.107296149611028</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.542061888400584</v>
+        <v>-2.69928790622291</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.090114969937047</v>
+        <v>2.027224562808117</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.079234662188326</v>
+        <v>0.9640159610841214</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.754836946924024</v>
+        <v>3.685705726261501</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.124850555337819</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.533169427007301</v>
+        <v>-2.690395444829627</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.111226360221152</v>
+        <v>2.048335953092221</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.079234662188326</v>
+        <v>0.9640159610841214</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.772391352650815</v>
+        <v>3.703260131988293</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.116705602742403</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.701645543977178</v>
+        <v>-2.858871561799505</v>
       </c>
       <c r="E1996" t="n">
-        <v>2.035690960837784</v>
+        <v>1.972800553708854</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.051286826471745</v>
+        <v>0.9360681253675406</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.747477698625451</v>
+        <v>3.678346477962928</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.097975299930265</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.003846015115595</v>
+        <v>-2.161072032937922</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.296080469570279</v>
+        <v>2.233190062441349</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.9809387671013345</v>
+        <v>0.8657200659971298</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.686538560191066</v>
+        <v>3.617407339528543</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.08863932242717</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.981124911432443</v>
+        <v>-2.138350929254769</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.295832933540445</v>
+        <v>2.232942526411515</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.9809387671013345</v>
+        <v>0.8657200659971298</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.677202582687971</v>
+        <v>3.608071362025448</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.247545448278339</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.110326724726485</v>
+        <v>-2.267552742548812</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.403058334073997</v>
+        <v>2.340167926945067</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.8517369538072923</v>
+        <v>0.7365182527030876</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.758587620562714</v>
+        <v>3.689456399900191</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.284623270771985</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.265107731504741</v>
+        <v>-2.422333749327067</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.378223753856342</v>
+        <v>2.315333346727411</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.8183692797528161</v>
+        <v>0.7031505786486114</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.775644838623675</v>
+        <v>3.706513617961152</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.28129862676153</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.258053041289567</v>
+        <v>-2.415279059111894</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.377720985931956</v>
+        <v>2.314830578803026</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.8254239699679899</v>
+        <v>0.7102052688637852</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.776553008742324</v>
+        <v>3.707421788079801</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.291304780406272</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.231101816963079</v>
+        <v>-2.388327834785406</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.398507629307293</v>
+        <v>2.335617222178362</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.8403043159957091</v>
+        <v>0.7250856148915044</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.795487370003698</v>
+        <v>3.726356149341175</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.475407912551232</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.367054825019395</v>
+        <v>-2.524280842841722</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.528229558229726</v>
+        <v>2.465339151100796</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.8403043159957091</v>
+        <v>0.7250856148915044</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.979590502148657</v>
+        <v>3.910459281486134</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.467524607454225</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.389462942824268</v>
+        <v>-2.546688960646594</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.51138300601077</v>
+        <v>2.44849259888184</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.8403043159957091</v>
+        <v>0.7250856148915044</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.97170719705165</v>
+        <v>3.902575976389127</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.469578607003862</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.537468710303667</v>
+        <v>-2.694694728125993</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.454234698568648</v>
+        <v>2.391344291439718</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.7535773071321676</v>
+        <v>0.6383586060279629</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.921724991283163</v>
+        <v>3.85259377062064</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.525832324725709</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.546909636192197</v>
+        <v>-2.704135654014523</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.506712045935084</v>
+        <v>2.443821638806153</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.8760044246755591</v>
+        <v>0.7607857235713543</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.051434979531045</v>
+        <v>3.982303758868522</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.52872341927101</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.599183243527838</v>
+        <v>-2.756409261350165</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.488693697546128</v>
+        <v>2.425803290417197</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.8237308173399178</v>
+        <v>0.7085121162357131</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.022961909674962</v>
+        <v>3.953830689012438</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.526835232164785</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.675513221128744</v>
+        <v>-2.832739238951071</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.456273519399541</v>
+        <v>2.39338311227061</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.8237308173399178</v>
+        <v>0.7085121162357131</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.021073722568737</v>
+        <v>3.951942501906213</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.521655461767648</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.787270173744045</v>
+        <v>-2.944496191566372</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.406390967956282</v>
+        <v>2.343500560827352</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.7119738647246168</v>
+        <v>0.596755163620412</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.948839780602418</v>
+        <v>3.879708559939895</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.5200894719778</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.785429154685794</v>
+        <v>-2.94265517250812</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.405561385789735</v>
+        <v>2.342670978660805</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7132420913960852</v>
+        <v>0.5980233902918805</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.948034726815451</v>
+        <v>3.878903506152929</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.533162878843719</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.917730446783347</v>
+        <v>-3.074956464605674</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.365714275816632</v>
+        <v>2.302823868687702</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7132420913960852</v>
+        <v>0.5980233902918805</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.96110813368137</v>
+        <v>3.891976913018847</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.533162878843719</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.919292089598208</v>
+        <v>-3.076518107420534</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.365089618690688</v>
+        <v>2.302199211561758</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7132420913960852</v>
+        <v>0.5980233902918805</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.96110813368137</v>
+        <v>3.891976913018847</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.531686919970721</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.94719287670768</v>
+        <v>-3.104418894530007</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.352453344973901</v>
+        <v>2.289562937844971</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6786451672531504</v>
+        <v>0.5634264661489456</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.938874020322611</v>
+        <v>3.869742799660088</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.528451363947919</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.069718979410574</v>
+        <v>-3.226944997232901</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.300207347869942</v>
+        <v>2.237316940741012</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5561190645502565</v>
+        <v>0.4409003634460518</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.862122802678074</v>
+        <v>3.792991582015551</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.595157323538423</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.089780300687081</v>
+        <v>-3.247006318509408</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.358888778949844</v>
+        <v>2.295998371820913</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5360577432737494</v>
+        <v>0.4208390421695448</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.916791969502673</v>
+        <v>3.84766074884015</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.73546904254027</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.346501118681905</v>
+        <v>-3.503727136504232</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.396512170753761</v>
+        <v>2.33362176362483</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4276431691299346</v>
+        <v>0.3124244680257299</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.992054944018231</v>
+        <v>3.922923723355709</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.80444931168591</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.500487536458046</v>
+        <v>-3.657713554280372</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.403897872788944</v>
+        <v>2.341007465660014</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4276431691299346</v>
+        <v>0.3124244680257299</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.061035213163871</v>
+        <v>3.991903992501348</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.790500513806031</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.44996563263038</v>
+        <v>-3.607191650452706</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.410157836440132</v>
+        <v>2.347267429311201</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.4276431691299346</v>
+        <v>0.3124244680257299</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.047086415283992</v>
+        <v>3.977955194621469</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.802371002861445</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.702440786638104</v>
+        <v>-3.859666804460431</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.321038263892456</v>
+        <v>2.258147856763525</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.4276431691299346</v>
+        <v>0.3124244680257299</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.058956904339405</v>
+        <v>3.989825683676883</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.803581537380389</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.971913588559812</v>
+        <v>-4.129139606382139</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.214459677642716</v>
+        <v>2.151569270513786</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.4276431691299346</v>
+        <v>0.3124244680257299</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.06016743885835</v>
+        <v>3.991036218195827</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.80770327960771</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.129457660289254</v>
+        <v>-4.28668367811158</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.155563791178261</v>
+        <v>2.092673384049331</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.3607413639896601</v>
+        <v>0.2455226628854554</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.024148098001506</v>
+        <v>3.955016877338983</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301341</v>
+        <v>3.652163313301342</v>
       </c>
       <c r="C2022" t="n">
         <v>3.802781132343899</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.407422055872527</v>
+        <v>-4.564648073694854</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.039455885681141</v>
+        <v>1.976565478552211</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.2711216297041759</v>
+        <v>0.1559029285999712</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.965454110166405</v>
+        <v>3.896322889503882</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.964985189042944</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.524389748511418</v>
+        <v>-4.769916396609738</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.154872865324629</v>
+        <v>2.056662206085301</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.2711216297041759</v>
+        <v>0.1559029285999712</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.12765816686545</v>
+        <v>4.058526946202926</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.959831827006758</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.609107690732372</v>
+        <v>-4.854634338830691</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.115832326400062</v>
+        <v>2.017621667160734</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1860056007761295</v>
+        <v>0.07078689967192481</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.071435187472436</v>
+        <v>4.002303966809913</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.970061244575249</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.691042509001255</v>
+        <v>-4.936569157099575</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.093287816661</v>
+        <v>1.995077157421672</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.1760708551890493</v>
+        <v>0.06085215408484462</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.075703757688679</v>
+        <v>4.006572537026156</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.978986883031151</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.637304335600993</v>
+        <v>-4.882830983699312</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.123708724477007</v>
+        <v>2.025498065237679</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.2298090285893114</v>
+        <v>0.1145903274851067</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.116872300184738</v>
+        <v>4.047741079522216</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.971139770275327</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.527298052123771</v>
+        <v>-4.772824700222091</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.159864125112072</v>
+        <v>2.061653465872744</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.2530136005065866</v>
+        <v>0.1377948994023819</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.122947930579279</v>
+        <v>4.053816709916757</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.975389780997301</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.384238476382846</v>
+        <v>-4.629765124481166</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.221337966130416</v>
+        <v>2.123127306891088</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.2610270270965659</v>
+        <v>0.1458083259923612</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.132005997255241</v>
+        <v>4.062874776592718</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.982650663879838</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.082791750911008</v>
+        <v>-4.328318399009328</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.349177539201687</v>
+        <v>2.250966879962359</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.5624737525684032</v>
+        <v>0.4472550514641985</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.32013491542088</v>
+        <v>4.251003694758357</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.983621841632548</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.137746947354078</v>
+        <v>-4.383273595452398</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.328166638377169</v>
+        <v>2.229955979137841</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.5624737525684032</v>
+        <v>0.4472550514641985</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.32110609317359</v>
+        <v>4.251974872511068</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.984464746012303</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.086708571347557</v>
+        <v>-4.332235219445877</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.349424893159533</v>
+        <v>2.251214233920205</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.5624737525684032</v>
+        <v>0.4472550514641985</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.321948997553346</v>
+        <v>4.252817776890823</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>4.003502844886449</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.045569276480927</v>
+        <v>-4.291095924579246</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.384918709980331</v>
+        <v>2.286708050741003</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.603613047435034</v>
+        <v>0.4883943463308293</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.36567067334747</v>
+        <v>4.296539452684947</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.819686841010383</v>
       </c>
       <c r="D2033" t="n">
-        <v>-3.934963136401325</v>
+        <v>-4.180489784499644</v>
       </c>
       <c r="E2033" t="n">
-        <v>2.245345162136106</v>
+        <v>2.147134502896778</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.714219187514636</v>
+        <v>0.5990004864104312</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.248218353519166</v>
+        <v>4.179087132856642</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.565567531713958</v>
+        <v>3.784087470807517</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.629661384494824</v>
+        <v>3.823188885084347</v>
       </c>
       <c r="D2034" t="n">
-        <v>-3.934963136401325</v>
+        <v>-4.114228150273493</v>
       </c>
       <c r="E2034" t="n">
-        <v>2.245345162136106</v>
+        <v>2.177141200661203</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.714219187514636</v>
+        <v>0.6652621206365824</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.622725181481192</v>
+        <v>4.222346157466297</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240723.xlsx
+++ b/tame_output/ON/bt/strategyON_20240723.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>48.0%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.8%</t>
+          <t>-74.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.0%</t>
+          <t>124.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>96.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.8%</t>
+          <t>-48.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.4%</t>
+          <t>-70.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>456.0%</t>
+          <t>456.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-573.0%</t>
+          <t>-550.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.6%</t>
+          <t>-34.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-47.5%</t>
+          <t>-47.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-158.5%</t>
+          <t>-149.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-10.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>70.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-85.7%</t>
+          <t>-124.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-157.5%</t>
+          <t>-143.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>85.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>75.2%</t>
+          <t>77.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-15.6%</t>
         </is>
       </c>
     </row>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131761</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341307</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.272928301031499</v>
+        <v>-4.08112177601244</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.254039942998276</v>
+        <v>1.330762553005899</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.1894511192969474</v>
+        <v>0.3177215948079991</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.077238359302791</v>
+        <v>3.154200644609422</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.140060611968221</v>
+        <v>-4.032826700810138</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.32308120142541</v>
+        <v>1.365974765888643</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.1894511192969474</v>
+        <v>0.3177215948079991</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.093132542104614</v>
+        <v>3.170094827411245</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.019887528603722</v>
+        <v>-3.912653617445639</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.372296279211511</v>
+        <v>1.415189843674745</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.3096242026614464</v>
+        <v>0.437894678172498</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.166382236563616</v>
+        <v>3.243344521870247</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.875215383503985</v>
+        <v>-3.767981472345902</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.440253239812846</v>
+        <v>1.48314680427608</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.4542963477611838</v>
+        <v>0.5825668232722354</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.263273626184898</v>
+        <v>3.340235911491529</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.935090210861677</v>
+        <v>-3.827856299703594</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.402340800271195</v>
+        <v>1.445234364734428</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.3944215204034917</v>
+        <v>0.5226919959145433</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.213386221171708</v>
+        <v>3.29034850647834</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.81526997995084</v>
+        <v>-3.708036068792757</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.465558061869739</v>
+        <v>1.508451626332972</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.3944215204034917</v>
+        <v>0.5226919959145433</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.228675390405917</v>
+        <v>3.305637675712548</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.817739686412646</v>
+        <v>-3.710505775254563</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.372214378607458</v>
+        <v>1.415107943070691</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.3919518139416855</v>
+        <v>0.5202222894527371</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.134837765851275</v>
+        <v>3.211800051157906</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.886109872736656</v>
+        <v>-3.778875961578573</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.264128165563155</v>
+        <v>1.307021730026388</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.4012275129779004</v>
+        <v>0.529497988488952</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.059665046758306</v>
+        <v>3.136627332064936</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.899897925583702</v>
+        <v>-3.792664014425619</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.249049653056228</v>
+        <v>1.291943217519461</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.4012275129779004</v>
+        <v>0.529497988488952</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.050101755390197</v>
+        <v>3.127064040696828</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.955418001476292</v>
+        <v>-3.848184090318209</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.363872459391394</v>
+        <v>1.406766023854628</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.4012275129779004</v>
+        <v>0.529497988488952</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.187132592082399</v>
+        <v>3.26409487738903</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.779943741683823</v>
+        <v>-3.67270983052574</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.43862939530017</v>
+        <v>1.481522959763403</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.4012275129779004</v>
+        <v>0.529497988488952</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.191699824074187</v>
+        <v>3.268662109380818</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502432322544</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.890879994325071</v>
+        <v>-3.783646083166988</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.369996923004878</v>
+        <v>1.412890487468111</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.4012275129779004</v>
+        <v>0.529497988488952</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.167441852835394</v>
+        <v>3.244404138142025</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.857216448852789</v>
+        <v>-3.749982537694706</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.31200065459524</v>
+        <v>1.354894219058473</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.4348910584501823</v>
+        <v>0.5631615339612339</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.116178293520213</v>
+        <v>3.193140578826844</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.797363829649066</v>
+        <v>-3.690129918490983</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.346114088708862</v>
+        <v>1.389007653172095</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.4348910584501823</v>
+        <v>0.5631615339612339</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.126350679952345</v>
+        <v>3.203312965258976</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.711120366622689</v>
+        <v>-3.603886455464606</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.375557744493273</v>
+        <v>1.418451308956506</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.4348910584501823</v>
+        <v>0.5631615339612339</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.121296950526205</v>
+        <v>3.198259235832837</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.756427186021669</v>
+        <v>-3.649193274863586</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.349210792178207</v>
+        <v>1.39210435664144</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.3940808954409515</v>
+        <v>0.5223513709520031</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.088586628165193</v>
+        <v>3.165548913471823</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.78546029072397</v>
+        <v>-3.678226379565887</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.338149423330387</v>
+        <v>1.381042987793621</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.3940808954409515</v>
+        <v>0.5223513709520031</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.089138501198294</v>
+        <v>3.166100786504925</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.692649809273111</v>
+        <v>-3.585415898115028</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.304546307802097</v>
+        <v>1.34743987226533</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.4868913768918108</v>
+        <v>0.6151618524028625</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.074097481960175</v>
+        <v>3.151059767266806</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.737039278602539</v>
+        <v>-3.629805367444455</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.288663995994927</v>
+        <v>1.33155756045816</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.4425019075623832</v>
+        <v>0.5707723830734348</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.049337276287119</v>
+        <v>3.126299561593751</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.624368060366288</v>
+        <v>-3.517134149208205</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.32880819180115</v>
+        <v>1.371701756264383</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.5551731257986334</v>
+        <v>0.683443601309685</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.112015715740593</v>
+        <v>3.188978001047224</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.511991059183616</v>
+        <v>-3.404757148025533</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.379250288104886</v>
+        <v>1.422143852568119</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.5551731257986334</v>
+        <v>0.683443601309685</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.11750701157126</v>
+        <v>3.194469296877891</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.539771457084969</v>
+        <v>-3.432537545926886</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.379635330712884</v>
+        <v>1.422528895176117</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.5273927278972803</v>
+        <v>0.6556632034083318</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.112335974598987</v>
+        <v>3.189298259905618</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705323</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.658152129815107</v>
+        <v>-3.550918218657024</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.170638781621482</v>
+        <v>1.213532346084715</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4601748757463041</v>
+        <v>0.5884453512573556</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.910360983309054</v>
+        <v>2.987323268615686</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729267</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.766766208258439</v>
+        <v>-3.659532297100355</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.247342810963355</v>
+        <v>1.290236375426588</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4601748757463041</v>
+        <v>0.5884453512573556</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.03051064402826</v>
+        <v>3.107472929334891</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.731357170010296</v>
+        <v>-3.624123258852213</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.276019452364935</v>
+        <v>1.318913016828168</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4601748757463041</v>
+        <v>0.5884453512573556</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.045023670130583</v>
+        <v>3.121985955437214</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.692973507452145</v>
+        <v>-3.585739596294061</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.288792358730564</v>
+        <v>1.331685923193797</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4985585383044553</v>
+        <v>0.6268290138155068</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.065473309007843</v>
+        <v>3.142435594314474</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.515857177416978</v>
+        <v>-3.408623266258895</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.356367919589933</v>
+        <v>1.399261484053166</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4985585383044553</v>
+        <v>0.6268290138155068</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.062202337853145</v>
+        <v>3.139164623159775</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.560949422250524</v>
+        <v>-3.453715511092441</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.339014413418427</v>
+        <v>1.381907977881661</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.4366624951350655</v>
+        <v>0.564932970646117</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.025748103713424</v>
+        <v>3.102710389020055</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.381574001011757</v>
+        <v>-3.274340089853673</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.404551557220349</v>
+        <v>1.447445121683582</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5934392533057842</v>
+        <v>0.7217097288168357</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.113601133922269</v>
+        <v>3.190563419228901</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.426588214532363</v>
+        <v>-3.31935430337428</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.367353327143696</v>
+        <v>1.410246891606929</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.5630903579911796</v>
+        <v>0.6913608335022311</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.076199252065096</v>
+        <v>3.153161537371727</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509535</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.693592724804798</v>
+        <v>-3.586358813646715</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.266243085373667</v>
+        <v>1.309136649836901</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.368727319948231</v>
+        <v>0.4969977954592826</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.965272991578273</v>
+        <v>3.042235276884904</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.702309454760813</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.794790506241971</v>
+        <v>-3.687556595083888</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.2249678946953</v>
+        <v>1.267861459158533</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.3003185064029118</v>
+        <v>0.4285889819139634</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.923431625347583</v>
+        <v>3.000393910654214</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.788279539627658</v>
+        <v>-3.681045628469575</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.225172242895342</v>
+        <v>1.268065807358575</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.3003185064029118</v>
+        <v>0.4285889819139634</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.9210315869019</v>
+        <v>2.99799387220853</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.769241411920361</v>
+        <v>-3.662007500762278</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.229312213186506</v>
+        <v>1.272205777649739</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2421348950717173</v>
+        <v>0.3704053705827688</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.882646139311428</v>
+        <v>2.959608424618059</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.914947071207078</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.800368043070979</v>
+        <v>-3.693134131912896</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.394443429664939</v>
+        <v>1.437336994128172</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2421348950717173</v>
+        <v>0.3704053705827688</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.060228008250109</v>
+        <v>3.137190293556739</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.915780400193211</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.814234804404896</v>
+        <v>-3.707000893246813</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.389730054117505</v>
+        <v>1.432623618580739</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.2042769783378943</v>
+        <v>0.3325474538489459</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.038346587195948</v>
+        <v>3.115308872502579</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.921788930590137</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.769430632864966</v>
+        <v>-3.662196721706883</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.413660253130403</v>
+        <v>1.456553817593637</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.2042769783378943</v>
+        <v>0.3325474538489459</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.044355117592874</v>
+        <v>3.121317402899505</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.819739151867337</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.621687662629964</v>
+        <v>-3.514453751471881</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.370707662501604</v>
+        <v>1.413601226964837</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3720843355727775</v>
+        <v>0.5003548110838291</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.042989753211003</v>
+        <v>3.119952038517634</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.822532773398818</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.723702345161185</v>
+        <v>-3.616468434003102</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.332695411020596</v>
+        <v>1.37558897548383</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3720843355727775</v>
+        <v>0.5003548110838291</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.045783374742484</v>
+        <v>3.122745660049115</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
         <v>2.823195121790476</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.717549639108401</v>
+        <v>-3.610315727950318</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.335818841833369</v>
+        <v>1.378712406296602</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3782370416255618</v>
+        <v>0.5065075171366133</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.050137346765813</v>
+        <v>3.127099632072444</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.822275598530586</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.734358937258902</v>
+        <v>-3.627125026100819</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.328175599313278</v>
+        <v>1.371069163776511</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3614277434750601</v>
+        <v>0.4896982189861117</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.039132244615623</v>
+        <v>3.116094529922254</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.888611152327407</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.67206093848278</v>
+        <v>-3.564827027324697</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.419430352620548</v>
+        <v>1.462323917083781</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3614277434750601</v>
+        <v>0.4896982189861117</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.105467798412444</v>
+        <v>3.182430083719074</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.690903154041534</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.470270740817623</v>
+        <v>-3.363036829659539</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.302438433400738</v>
+        <v>1.345331997863971</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5594459356442145</v>
+        <v>0.687716411155266</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.026570715428063</v>
+        <v>3.103533000734694</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.761193386363709</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.521157453503817</v>
+        <v>-3.413923542345734</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.352373980648435</v>
+        <v>1.395267545111669</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.50855922295802</v>
+        <v>0.6368296984690716</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.066328920138522</v>
+        <v>3.143291205445153</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.775821122479753</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.618897998128792</v>
+        <v>-3.511664086970709</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.327905498914489</v>
+        <v>1.370799063377723</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.4926699448250398</v>
+        <v>0.6209404203360913</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.071423089374777</v>
+        <v>3.148385374681408</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.774357103304425</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.795235758251721</v>
+        <v>-3.688001847093638</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.255906375689989</v>
+        <v>1.298799940153222</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.3163321847021104</v>
+        <v>0.4446026602131619</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.964156414125691</v>
+        <v>3.041118699432322</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.772848721344353</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.718813711819794</v>
+        <v>-3.611579800661711</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.284966812302688</v>
+        <v>1.327860376765922</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.3163321847021104</v>
+        <v>0.4446026602131619</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.96264803216562</v>
+        <v>3.039610317472251</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.77271158877979</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.674440580181225</v>
+        <v>-3.567206669023142</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.302578932393552</v>
+        <v>1.345472496856785</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.360705316340679</v>
+        <v>0.4889757918517306</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.989134778584197</v>
+        <v>3.066097063890828</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.76710538291838</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.551606359294058</v>
+        <v>-3.444372448135975</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.346106414887009</v>
+        <v>1.388999979350243</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.360705316340679</v>
+        <v>0.4889757918517306</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.983528572722788</v>
+        <v>3.060490858029419</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.773487139946185</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.503950628733002</v>
+        <v>-3.396716717574919</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.371550464139236</v>
+        <v>1.41444402860247</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.4083610469017346</v>
+        <v>0.5366315224127862</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.018503768087226</v>
+        <v>3.095466053393856</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.778379513320909</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.403432470234248</v>
+        <v>-3.296198559076164</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.416650100913463</v>
+        <v>1.459543665376696</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.5088792054004891</v>
+        <v>0.6371496809115408</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.083707036561203</v>
+        <v>3.160669321867834</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.765134185796782</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.464099060636637</v>
+        <v>-3.356865149478554</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.37913813722838</v>
+        <v>1.422031701691613</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.4271808886819555</v>
+        <v>0.5554513641930071</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.021442719005955</v>
+        <v>3.098405004312586</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.76923188840741</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.419260659028239</v>
+        <v>-3.312026747870155</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.401171200482368</v>
+        <v>1.444064764945601</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.4317243216268249</v>
+        <v>0.5599947971378766</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.028266481383505</v>
+        <v>3.105228766690137</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.773392828038488</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.438759115270247</v>
+        <v>-3.331525204112164</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.397532757616642</v>
+        <v>1.440426322079876</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.3836396803469206</v>
+        <v>0.5119101558579723</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.003576636246641</v>
+        <v>3.080538921553272</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.779272430566325</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.394556278184346</v>
+        <v>-3.287322367026263</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.42109349497884</v>
+        <v>1.463987059442073</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.4278425174328211</v>
+        <v>0.5561129929438727</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.035977941026018</v>
+        <v>3.11294022633265</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.777682431035573</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.43153530584779</v>
+        <v>-3.324301394689706</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.40471188438271</v>
+        <v>1.447605448845943</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.4648164192241516</v>
+        <v>0.5930868947352033</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.056572282570064</v>
+        <v>3.133534567876695</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.828930196218613</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.273243888308517</v>
+        <v>-3.166009977150434</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.519276216581458</v>
+        <v>1.562169781044692</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.4648164192241516</v>
+        <v>0.5930868947352033</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.107820047753104</v>
+        <v>3.184782333059735</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.827370900812866</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.065601884674041</v>
+        <v>-2.958367973515958</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.600773722629502</v>
+        <v>1.643667287092735</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.6724584228586278</v>
+        <v>0.8007288983696794</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.230845954528043</v>
+        <v>3.307808239834674</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.822319129051136</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.014569791951513</v>
+        <v>-2.90733588079343</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.616134787956783</v>
+        <v>1.659028352420017</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.7234905155811557</v>
+        <v>0.8517609910922074</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.25641343839983</v>
+        <v>3.33337572370646</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.839506533143841</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.949345610824308</v>
+        <v>-2.842111699666225</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.65941186450037</v>
+        <v>1.702305428963604</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.7887146967083614</v>
+        <v>0.916985172219413</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.312735351168858</v>
+        <v>3.389697636475489</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.835467505443121</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.911918590753174</v>
+        <v>-2.804684679595091</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.670343644828104</v>
+        <v>1.713237209291337</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.793966234737543</v>
+        <v>0.9222367102485947</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.311847246285647</v>
+        <v>3.388809531592278</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992659</v>
+        <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
         <v>2.836724297774361</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.932030246787882</v>
+        <v>-2.824796335629799</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.663555774745461</v>
+        <v>1.706449339208695</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.8049935797349622</v>
+        <v>0.9332640552460139</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.319720445615339</v>
+        <v>3.39668273092197</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.997282068795572</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.878285432360677</v>
+        <v>-2.771051521202594</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.845611471537554</v>
+        <v>1.888505036000787</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.8150568891754242</v>
+        <v>0.9433273646864758</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.486316202300827</v>
+        <v>3.563278487607458</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957623</v>
+        <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
         <v>3.117394978013389</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.803503171335665</v>
+        <v>-2.696269260177582</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.995637285165376</v>
+        <v>2.038530849628609</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.8898391502004368</v>
+        <v>1.018109625711488</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.651298468133652</v>
+        <v>3.728260753440283</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998754</v>
+        <v>3.814230727998755</v>
       </c>
       <c r="C1993" t="n">
         <v>3.109102954027248</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.777419087071857</v>
+        <v>-2.670185175913774</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.997778894884759</v>
+        <v>2.040672459347991</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.8898391502004368</v>
+        <v>1.018109625711488</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.643006444147511</v>
+        <v>3.719968729454142</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.107296149611028</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.69928790622291</v>
+        <v>-2.592053995064827</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.027224562808117</v>
+        <v>2.07011812727135</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.9640159610841214</v>
+        <v>1.092286436595173</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.685705726261501</v>
+        <v>3.762668011568132</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
         <v>3.124850555337819</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.690395444829627</v>
+        <v>-2.583161533671544</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.048335953092221</v>
+        <v>2.091229517555455</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.9640159610841214</v>
+        <v>1.092286436595173</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.703260131988293</v>
+        <v>3.780222417294923</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
         <v>3.116705602742403</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.858871561799505</v>
+        <v>-2.751637650641422</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.972800553708854</v>
+        <v>2.015694118172087</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.9360681253675406</v>
+        <v>1.064338600878592</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.678346477962928</v>
+        <v>3.755308763269559</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
         <v>3.097975299930265</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.161072032937922</v>
+        <v>-2.053838121779838</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.233190062441349</v>
+        <v>2.276083626904582</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.8657200659971298</v>
+        <v>0.9939905415081816</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.617407339528543</v>
+        <v>3.694369624835174</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632634</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
         <v>3.08863932242717</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.138350929254769</v>
+        <v>-2.031117018096686</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.232942526411515</v>
+        <v>2.275836090874748</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.8657200659971298</v>
+        <v>0.9939905415081816</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.608071362025448</v>
+        <v>3.685033647332079</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777671</v>
+        <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
         <v>3.247545448278339</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.267552742548812</v>
+        <v>-2.160318831390728</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.340167926945067</v>
+        <v>2.3830614914083</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.7365182527030876</v>
+        <v>0.8647887282141393</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.689456399900191</v>
+        <v>3.766418685206823</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.77993372564441</v>
+        <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
         <v>3.284623270771985</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.422333749327067</v>
+        <v>-2.296588597244003</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.315333346727411</v>
+        <v>2.365631407560636</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.7031505786486114</v>
+        <v>0.8438326173089794</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.706513617961152</v>
+        <v>3.790922841157373</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799962</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
         <v>3.28129862676153</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.415279059111894</v>
+        <v>-2.28953390702883</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.314830578803026</v>
+        <v>2.365128639636251</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.7102052688637852</v>
+        <v>0.8508873075241532</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.707421788079801</v>
+        <v>3.791831011276023</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331115</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
         <v>3.291304780406272</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.388327834785406</v>
+        <v>-2.262582682702342</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.335617222178362</v>
+        <v>2.385915283011588</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.7250856148915044</v>
+        <v>0.8657676535518724</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.726356149341175</v>
+        <v>3.810765372537396</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.475407912551232</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.524280842841722</v>
+        <v>-2.398535690758658</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.465339151100796</v>
+        <v>2.515637211934021</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.7250856148915044</v>
+        <v>0.8657676535518724</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.910459281486134</v>
+        <v>3.994868504682355</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.467524607454225</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.546688960646594</v>
+        <v>-2.42094380856353</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.44849259888184</v>
+        <v>2.498790659715065</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.7250856148915044</v>
+        <v>0.8657676535518724</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.902575976389127</v>
+        <v>3.986985199585348</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.469578607003862</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.694694728125993</v>
+        <v>-2.56894957604293</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.391344291439718</v>
+        <v>2.441642352272943</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.6383586060279629</v>
+        <v>0.7790406446883309</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.85259377062064</v>
+        <v>3.937002993816861</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.525832324725709</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.704135654014523</v>
+        <v>-2.57839050193146</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.443821638806153</v>
+        <v>2.494119699639378</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.7607857235713543</v>
+        <v>0.9014677622317223</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.982303758868522</v>
+        <v>4.066712982064743</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.52872341927101</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.756409261350165</v>
+        <v>-2.630664109267101</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.425803290417197</v>
+        <v>2.476101351250422</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.7085121162357131</v>
+        <v>0.8491941548960811</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.953830689012438</v>
+        <v>4.038239912208659</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.526835232164785</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.832739238951071</v>
+        <v>-2.706994086868007</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.39338311227061</v>
+        <v>2.443681173103835</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.7085121162357131</v>
+        <v>0.8491941548960811</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.951942501906213</v>
+        <v>4.036351725102434</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.521655461767648</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.944496191566372</v>
+        <v>-2.818751039483308</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.343500560827352</v>
+        <v>2.393798621660578</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.596755163620412</v>
+        <v>0.73743720228078</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.879708559939895</v>
+        <v>3.964117783136116</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.5200894719778</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.94265517250812</v>
+        <v>-2.816910020425057</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.342670978660805</v>
+        <v>2.39296903949403</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.5980233902918805</v>
+        <v>0.7387054289522484</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.878903506152929</v>
+        <v>3.963312729349149</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.533162878843719</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.074956464605674</v>
+        <v>-2.94921131252261</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.302823868687702</v>
+        <v>2.353121929520928</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.5980233902918805</v>
+        <v>0.7387054289522484</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.891976913018847</v>
+        <v>3.976386136215068</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.533162878843719</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.076518107420534</v>
+        <v>-2.95077295533747</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.302199211561758</v>
+        <v>2.352497272394984</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.5980233902918805</v>
+        <v>0.7387054289522484</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.891976913018847</v>
+        <v>3.976386136215068</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.531686919970721</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.104418894530007</v>
+        <v>-2.978673742446943</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.289562937844971</v>
+        <v>2.339860998678196</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.5634264661489456</v>
+        <v>0.7041085048093136</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.869742799660088</v>
+        <v>3.954152022856309</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.528451363947919</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.226944997232901</v>
+        <v>-3.101199845149837</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.237316940741012</v>
+        <v>2.287615001574237</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4409003634460518</v>
+        <v>0.5815824021064198</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.792991582015551</v>
+        <v>3.877400805211772</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.595157323538423</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.247006318509408</v>
+        <v>-3.121261166426344</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.295998371820913</v>
+        <v>2.346296432654138</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4208390421695448</v>
+        <v>0.5615210808299127</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.84766074884015</v>
+        <v>3.932069972036371</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.73546904254027</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.503727136504232</v>
+        <v>-3.377981984421168</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.33362176362483</v>
+        <v>2.383919824458056</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3124244680257299</v>
+        <v>0.4531065066860979</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.922923723355709</v>
+        <v>4.007332946551929</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.80444931168591</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.657713554280372</v>
+        <v>-3.531968402197308</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.341007465660014</v>
+        <v>2.391305526493239</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3124244680257299</v>
+        <v>0.4531065066860979</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.991903992501348</v>
+        <v>4.076313215697569</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.790500513806031</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.607191650452706</v>
+        <v>-3.481446498369642</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.347267429311201</v>
+        <v>2.397565490144427</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3124244680257299</v>
+        <v>0.4531065066860979</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.977955194621469</v>
+        <v>4.062364417817689</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.802371002861445</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.859666804460431</v>
+        <v>-3.733921652377367</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.258147856763525</v>
+        <v>2.308445917596751</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3124244680257299</v>
+        <v>0.4531065066860979</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.989825683676883</v>
+        <v>4.074234906873103</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.803581537380389</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.129139606382139</v>
+        <v>-4.003394454299075</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.151569270513786</v>
+        <v>2.201867331347011</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3124244680257299</v>
+        <v>0.4531065066860979</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.991036218195827</v>
+        <v>4.075445441392048</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.80770327960771</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.28668367811158</v>
+        <v>-4.160938526028517</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.092673384049331</v>
+        <v>2.142971444882556</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.2455226628854554</v>
+        <v>0.3862047015458234</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.955016877338983</v>
+        <v>4.039426100535204</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.802781132343899</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.564648073694854</v>
+        <v>-4.43890292161179</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.976565478552211</v>
+        <v>2.026863539385436</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.1559029285999712</v>
+        <v>0.2965849672603391</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.896322889503882</v>
+        <v>3.980732112700103</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.964985189042944</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.769916396609738</v>
+        <v>-4.555870614250681</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.056662206085301</v>
+        <v>2.142280519028924</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.1559029285999712</v>
+        <v>0.2965849672603391</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.058526946202926</v>
+        <v>4.142936169399147</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.959831827006758</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.854634338830691</v>
+        <v>-4.640588556471634</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.017621667160734</v>
+        <v>2.103239980104357</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.07078689967192481</v>
+        <v>0.2114689383322927</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.002303966809913</v>
+        <v>4.086713190006133</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.970061244575249</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.936569157099575</v>
+        <v>-4.722523374740518</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.995077157421672</v>
+        <v>2.080695470365295</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.06085215408484462</v>
+        <v>0.2015341927452126</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.006572537026156</v>
+        <v>4.090981760222377</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.978986883031151</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.882830983699312</v>
+        <v>-4.668785201340255</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.025498065237679</v>
+        <v>2.111116378181302</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.1145903274851067</v>
+        <v>0.2552723661454747</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.047741079522216</v>
+        <v>4.132150302718436</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.971139770275327</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.772824700222091</v>
+        <v>-4.558778917863034</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.061653465872744</v>
+        <v>2.147271778816366</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1377948994023819</v>
+        <v>0.2784769380627499</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.053816709916757</v>
+        <v>4.138225933112977</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.975389780997301</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.629765124481166</v>
+        <v>-4.415719342122108</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.123127306891088</v>
+        <v>2.208745619834711</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1458083259923612</v>
+        <v>0.2864903646527291</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.062874776592718</v>
+        <v>4.147283999788939</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.982650663879838</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.328318399009328</v>
+        <v>-4.11427261665027</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.250966879962359</v>
+        <v>2.336585192905982</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4472550514641985</v>
+        <v>0.5879370901245664</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.251003694758357</v>
+        <v>4.335412917954578</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.983621841632548</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.383273595452398</v>
+        <v>-4.16922781309334</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.229955979137841</v>
+        <v>2.315574292081465</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4472550514641985</v>
+        <v>0.5879370901245664</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.251974872511068</v>
+        <v>4.336384095707288</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.984464746012303</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.332235219445877</v>
+        <v>-4.118189437086819</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.251214233920205</v>
+        <v>2.336832546863828</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4472550514641985</v>
+        <v>0.5879370901245664</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.252817776890823</v>
+        <v>4.337227000087044</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>4.003502844886449</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.291095924579246</v>
+        <v>-4.077050142220188</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.286708050741003</v>
+        <v>2.372326363684627</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.4883943463308293</v>
+        <v>0.6290763849911972</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.296539452684947</v>
+        <v>4.380948675881167</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.819686841010383</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.180489784499644</v>
+        <v>-3.966444002140586</v>
       </c>
       <c r="E2033" t="n">
-        <v>2.147134502896778</v>
+        <v>2.232752815840402</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5990004864104312</v>
+        <v>0.7396825250707992</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.179087132856642</v>
+        <v>4.263496356052864</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.784087470807517</v>
+        <v>3.760557066939241</v>
       </c>
       <c r="C2034" t="n">
         <v>3.823188885084347</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.114228150273493</v>
+        <v>-3.884244692536091</v>
       </c>
       <c r="E2034" t="n">
-        <v>2.177141200661203</v>
+        <v>2.269134583756164</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.6652621206365824</v>
+        <v>0.801017550129217</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.222346157466297</v>
+        <v>4.303799415161878</v>
       </c>
     </row>
   </sheetData>
